--- a/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
+++ b/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ34"/>
+  <dimension ref="A1:AQ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,10 +695,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>22665767</v>
+        <v>22670530</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>23473659</v>
+        <v>23477463</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>45870.67501157407</v>
+        <v>45871.50821759259</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>45870.6760300926</v>
+        <v>45871.51726851852</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>DIKGCV</t>
+          <t>IIONJH</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>MAGALHAES/DANIELLA</t>
+          <t>MARCELO LESSA MOREIRA/PAULO</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>45870.17361111111</v>
+        <v>45871.5</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
@@ -766,12 +766,12 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão AMEX</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>Primo Arquitetura e Urbanismo</t>
+          <t>Solutis Tecnologias Ltda</t>
         </is>
       </c>
       <c r="W2" s="5" t="inlineStr">
@@ -801,11 +801,11 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>2243890798</v>
+        <v>2142557937</v>
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>0.1</v>
+        <v>799.1</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>0</v>
+        <v>34.11</v>
       </c>
       <c r="AD2" s="5" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>0</v>
+        <v>55.94</v>
       </c>
       <c r="AI2" s="5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>Validação do documento: Valor dever ser maior que zero !</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
         </is>
       </c>
       <c r="AK2" s="5" t="inlineStr">
@@ -886,10 +886,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>22665087</v>
+        <v>22670439</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23473060</v>
+        <v>23477392</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45870.57103009259</v>
+        <v>45871.49023148148</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>45870.57363425926</v>
+        <v>45871.50456018518</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>GCIAOH</t>
+          <t>UNCWBS</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Pereira de Brito/Odomar</t>
+          <t>MARCELO LESSA MOREIRA/PAULO</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>45870.04236111111</v>
+        <v>45871.46736111111</v>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão AMEX</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>Ntsec - Network Security</t>
+          <t>Solutis Tecnologias Ltda</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>2142496551</v>
+        <v>2142555895</v>
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>1301.2</v>
+        <v>589.8</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>58.89</v>
+        <v>60.62</v>
       </c>
       <c r="AD3" s="5" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>91.08</v>
+        <v>41.29</v>
       </c>
       <c r="AI3" s="5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AJ3" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
         </is>
       </c>
       <c r="AK3" s="5" t="inlineStr">
@@ -1077,10 +1077,10 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>22665072</v>
+        <v>22666040</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>23473040</v>
+        <v>23473906</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45870.56806712963</v>
+        <v>45870.71111111111</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>45870.56925925926</v>
+        <v>45870.72925925926</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>LPYFTK</t>
+          <t>JEIGSB</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>de Brito/Odomar</t>
+          <t>MARCOS DOS SANTOS/ANTONIO</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>45870.53472222222</v>
+        <v>45870.16944444444</v>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>Ntsec - Network Security</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>2142496529</v>
+        <v>2142512480</v>
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>555</v>
+        <v>1330.32</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>30.95</v>
+        <v>60.62</v>
       </c>
       <c r="AD4" s="5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>38.85</v>
+        <v>239.46</v>
       </c>
       <c r="AI4" s="5" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>22665408</v>
+        <v>22666040</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>23473325</v>
+        <v>23473907</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45870.6249537037</v>
+        <v>45870.71111111111</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>45870.62709490741</v>
+        <v>45870.72925925926</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>LA9575734SHTS</t>
+          <t>JEIGSB</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>ZOLFAGHARI/CHAHRAM</t>
+          <t>FLOREANO/ANGELO</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>45870.08402777778</v>
+        <v>45870.16944444444</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>Brazil Tower, Cessao de Infra-estruturas</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W5" s="5" t="inlineStr">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="X5" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>2243879847</v>
+        <v>2142512481</v>
       </c>
       <c r="Z5" s="5" t="inlineStr">
         <is>
@@ -1391,16 +1391,16 @@
         </is>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>1956.64</v>
+        <v>1330.32</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>94.18000000000001</v>
+        <v>60.62</v>
       </c>
       <c r="AD5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>195.66</v>
+        <v>0</v>
       </c>
       <c r="AF5" s="5" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>129.14</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="5" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>22665509</v>
+        <v>22666104</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>23473413</v>
+        <v>23473964</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45870.63643518519</v>
+        <v>45870.71695601852</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>45870.63826388889</v>
+        <v>45870.73171296297</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>LA9576129IBIV</t>
+          <t>SIMZJC</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>DIAS/NATASHA</t>
+          <t>Nobre/Luis</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>45870.09791666667</v>
+        <v>45869.13888888889</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>Opportunity Gestora</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W6" s="5" t="inlineStr">
@@ -1565,11 +1565,11 @@
       </c>
       <c r="X6" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>2243881949</v>
+        <v>286243421</v>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>1009.9</v>
+        <v>1217.85</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>33.56</v>
+        <v>86.14</v>
       </c>
       <c r="AD6" s="5" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>131.29</v>
+        <v>107.03</v>
       </c>
       <c r="AI6" s="5" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AJ6" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
         </is>
       </c>
       <c r="AK6" s="5" t="inlineStr">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>22664300</v>
+        <v>22663695</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>23472308</v>
+        <v>23471719</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>45870.50688657408</v>
+        <v>45870.44738425926</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45870.50887731482</v>
+        <v>45870.45027777777</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>UGPS6V</t>
+          <t>LA9578225DGWN</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Antônio de Souza Rebello/Victor</t>
+          <t>Vignoli dos Santos/Lua</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>45870.48194444444</v>
+        <v>45870.37708333333</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
@@ -1756,11 +1756,11 @@
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>738546404</v>
+        <v>2243839157</v>
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>1985.74</v>
+        <v>1023.29</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>79.84999999999999</v>
+        <v>59.95</v>
       </c>
       <c r="AD7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>0</v>
+        <v>102.32</v>
       </c>
       <c r="AF7" s="5" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>198.57</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="AI7" s="5" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>22664931</v>
+        <v>22665072</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>23472901</v>
+        <v>23473040</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45870.54740740741</v>
+        <v>45870.56806712963</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>45870.54853009259</v>
+        <v>45870.56925925926</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>UPY53K</t>
+          <t>LPYFTK</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>SILBERGLEID/DANIELLE</t>
+          <t>de Brito/Odomar</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>45870.04236111111</v>
+        <v>45870.53472222222</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Ntsec - Network Security</t>
         </is>
       </c>
       <c r="W8" s="5" t="inlineStr">
@@ -1947,11 +1947,11 @@
       </c>
       <c r="X8" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>709661853</v>
+        <v>2142496529</v>
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>749.92</v>
+        <v>555</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>33.56</v>
+        <v>30.95</v>
       </c>
       <c r="AD8" s="5" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>74.98999999999999</v>
+        <v>38.85</v>
       </c>
       <c r="AI8" s="5" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>22664959</v>
+        <v>22665087</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>23472921</v>
+        <v>23473060</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>45870.55277777778</v>
+        <v>45870.57103009259</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>45870.55474537037</v>
+        <v>45870.57363425926</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>UPY53K</t>
+          <t>GCIAOH</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>SILBERGLEID/DANIELLE</t>
+          <t>Pereira de Brito/Odomar</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>45870.04722222222</v>
+        <v>45870.04236111111</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>Opportunity Gestora</t>
+          <t>Ntsec - Network Security</t>
         </is>
       </c>
       <c r="W9" s="5" t="inlineStr">
@@ -2138,11 +2138,11 @@
       </c>
       <c r="X9" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>219676703</v>
+        <v>2142496551</v>
       </c>
       <c r="Z9" s="5" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AB9" s="5" t="n">
-        <v>993.38</v>
+        <v>1301.2</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>33.56</v>
+        <v>58.89</v>
       </c>
       <c r="AD9" s="5" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>71.2</v>
+        <v>91.08</v>
       </c>
       <c r="AI9" s="5" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>22664845</v>
+        <v>22659024</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>23472831</v>
+        <v>23467809</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45870.53333333333</v>
+        <v>45869.66074074074</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>45870.53405092593</v>
+        <v>45869.66322916667</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>HHTHNM</t>
+          <t>QGY74X</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Lima/Giovana</t>
+          <t>MONTEIRO PAULINO PAULINO/WILLIAM</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>45870.53125</v>
+        <v>45869.53541666667</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>Life Impact Brasil</t>
+          <t>R3ciclo Gestao de Residuos</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2329,11 +2329,11 @@
       </c>
       <c r="X10" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>2243856488</v>
+        <v>631205766</v>
       </c>
       <c r="Z10" s="5" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="AB10" s="5" t="n">
-        <v>304</v>
+        <v>818.5</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>450</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="AD10" s="5" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="5" t="n">
-        <v>40</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="AI10" s="5" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AJ10" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
         </is>
       </c>
       <c r="AK10" s="5" t="inlineStr">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>22665000</v>
+        <v>22651101</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23472958</v>
+        <v>23460675</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>45870.55975694444</v>
+        <v>45868.52986111111</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>45870.56107638889</v>
+        <v>45869.4131712963</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>LPSUXK</t>
+          <t>MQU7YH01</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>WERBSTER GOMES DE SOUZA/FRANCISCO</t>
+          <t>GONÇALVES/GUSTAVO</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>45870.39097222222</v>
+        <v>45867.26875</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>?</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>?</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Nossa Engenharia e Servicos</t>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
         </is>
       </c>
       <c r="W11" s="5" t="inlineStr">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>523384159</v>
+        <v>980419988</v>
       </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>828.67</v>
+        <v>713.2</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>50.92</v>
+        <v>36.67</v>
       </c>
       <c r="AD11" s="5" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>165.73</v>
+        <v>92.72</v>
       </c>
       <c r="AI11" s="5" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AJ11" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
         </is>
       </c>
       <c r="AK11" s="5" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="AL11" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Forma de Pagamento indevida</t>
         </is>
       </c>
       <c r="AM11" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Forma PG. e REC.</t>
         </is>
       </c>
       <c r="AN11" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO11" s="5" t="inlineStr">
@@ -2605,45 +2605,45 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>22665000</v>
+        <v>22649789</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>23472959</v>
+        <v>23459302</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>45870.55975694444</v>
+        <v>45868.39388888889</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>45870.56107638889</v>
+        <v>45868.39738425926</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>LPSUXK</t>
+          <t>5F7691</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>EBOOKING</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>RENAN FERNANDES DO NASCIMENTO/FRANCISCO</t>
+          <t>VINICIUS SILVA/LEONARDO</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>45870.39097222222</v>
+        <v>45845.42916666667</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Faturado</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U12" s="5" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>Nossa Engenharia e Servicos</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W12" s="5" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="X12" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>424231405</v>
+        <v>2240111841</v>
       </c>
       <c r="Z12" s="5" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="AB12" s="5" t="n">
-        <v>828.67</v>
+        <v>1336.02</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>50.92</v>
+        <v>468.89</v>
       </c>
       <c r="AD12" s="5" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="5" t="n">
-        <v>0</v>
+        <v>45.69</v>
       </c>
       <c r="AI12" s="5" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AJ12" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Verificação de bilhetes: Bilhete 2240111841 já sendo utilizado para este fornecedor.</t>
         </is>
       </c>
       <c r="AK12" s="5" t="inlineStr">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="AL12" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Bilhete duplicado</t>
         </is>
       </c>
       <c r="AM12" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Bilhete Já Contabilizado</t>
         </is>
       </c>
       <c r="AN12" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO12" s="5" t="inlineStr">
@@ -2796,45 +2796,45 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>22663687</v>
+        <v>22649789</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>23471712</v>
+        <v>23459303</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>45870.4444212963</v>
+        <v>45868.39388888889</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>45870.44729166666</v>
+        <v>45868.39738425926</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>HM9CJT</t>
+          <t>5F7691</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>EBOOKING</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Vignoli dos Santos/Lua</t>
+          <t>FELIPE ARCOVERDE/ROBERTA</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>45870.375</v>
+        <v>45845.42916666667</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Faturado</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W13" s="5" t="inlineStr">
@@ -2902,11 +2902,11 @@
       </c>
       <c r="X13" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>570934348</v>
+        <v>2240111842</v>
       </c>
       <c r="Z13" s="5" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>773.48</v>
+        <v>1336.02</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>34.6</v>
+        <v>468.89</v>
       </c>
       <c r="AD13" s="5" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>77.34999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="5" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AJ13" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Verificação de bilhetes: Bilhete 2240111841 já sendo utilizado para este fornecedor.</t>
         </is>
       </c>
       <c r="AK13" s="5" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="AL13" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Bilhete duplicado</t>
         </is>
       </c>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Bilhete Já Contabilizado</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO13" s="5" t="inlineStr">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>22663692</v>
+        <v>22680202</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23471714</v>
+        <v>23484639</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -2998,24 +2998,24 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>45870.44722222222</v>
+        <v>45873.73334490741</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>45870.45116898148</v>
+        <v>45873.7425</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>UDNCKR</t>
+          <t>LA9570609WFVC</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Vignoli dos Santos/Lua</t>
+          <t>DE AZEVEDO BATISTA/CARLA</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>45870.38541666666</v>
+        <v>45871.425</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Daten Tecnologia</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="X14" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>976233947</v>
+        <v>2244256929</v>
       </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="AB14" s="5" t="n">
-        <v>1142.17</v>
+        <v>824.34</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>47.91</v>
+        <v>98.72</v>
       </c>
       <c r="AD14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE14" s="5" t="n">
-        <v>0</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="AF14" s="5" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="5" t="n">
-        <v>114.22</v>
+        <v>54.41</v>
       </c>
       <c r="AI14" s="5" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AJ14" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
         </is>
       </c>
       <c r="AK14" s="5" t="inlineStr">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>22663695</v>
+        <v>22679735</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>23471719</v>
+        <v>23484196</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -3189,24 +3189,24 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>45870.44738425926</v>
+        <v>45873.68053240741</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>45870.45027777777</v>
+        <v>45873.6818287037</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>LA9578225DGWN</t>
+          <t>LA9576133CCPW</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Vignoli dos Santos/Lua</t>
+          <t>Marcos Andrade/Antonio</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>45870.37708333333</v>
+        <v>45873.09583333333</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W15" s="5" t="inlineStr">
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>2243839157</v>
+        <v>2244241726</v>
       </c>
       <c r="Z15" s="5" t="inlineStr">
         <is>
@@ -3301,16 +3301,16 @@
         </is>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>1023.29</v>
+        <v>668.02</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>59.95</v>
+        <v>48.16</v>
       </c>
       <c r="AD15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>102.32</v>
+        <v>66.8</v>
       </c>
       <c r="AF15" s="5" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>67.54000000000001</v>
+        <v>44.09</v>
       </c>
       <c r="AI15" s="5" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AJ15" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK15" s="5" t="inlineStr">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>22668111</v>
+        <v>22679744</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>23475861</v>
+        <v>23484203</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -3380,24 +3380,24 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>45870.87238425926</v>
+        <v>45873.68329861111</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>45870.9047337963</v>
+        <v>45873.68420138889</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>QL4RHJ</t>
+          <t>LA9570240ACXE</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Erilton Xavier Rabelo/Jose</t>
+          <t>ZUBIOLI/FABIO</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>45870.36458333334</v>
+        <v>45873.08819444444</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>Mv Power Engenharia e Servicos</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W16" s="5" t="inlineStr">
@@ -3475,11 +3475,11 @@
       </c>
       <c r="X16" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>356765646</v>
+        <v>2244242639</v>
       </c>
       <c r="Z16" s="5" t="inlineStr">
         <is>
@@ -3492,16 +3492,16 @@
         </is>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>1063.42</v>
+        <v>738.65</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>31.44</v>
+        <v>48.16</v>
       </c>
       <c r="AD16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>0</v>
+        <v>73.86</v>
       </c>
       <c r="AF16" s="5" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="5" t="n">
-        <v>106.34</v>
+        <v>97.5</v>
       </c>
       <c r="AI16" s="5" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AJ16" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK16" s="5" t="inlineStr">
@@ -3560,21 +3560,21 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>22670530</v>
+        <v>22679744</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>23477463</v>
+        <v>23484204</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>45871.50821759259</v>
+        <v>45873.68329861111</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>45871.51726851852</v>
+        <v>45873.68420138889</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>IIONJH</t>
+          <t>LA9570240ACXE</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>MARCELO LESSA MOREIRA/PAULO</t>
+          <t>BARBOSA/MAURICIO</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>45871.5</v>
+        <v>45873.08819444444</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>Solutis Tecnologias Ltda</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W17" s="5" t="inlineStr">
@@ -3666,11 +3666,11 @@
       </c>
       <c r="X17" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>2142557937</v>
+        <v>2244242640</v>
       </c>
       <c r="Z17" s="5" t="inlineStr">
         <is>
@@ -3683,16 +3683,16 @@
         </is>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>799.1</v>
+        <v>738.65</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>34.11</v>
+        <v>48.16</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>0</v>
+        <v>73.86</v>
       </c>
       <c r="AF17" s="5" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>55.94</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="5" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AJ17" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK17" s="5" t="inlineStr">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>22670399</v>
+        <v>22679780</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>23477371</v>
+        <v>23484235</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45871.47912037037</v>
+        <v>45873.68884259259</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>45871.47982638889</v>
+        <v>45873.68983796296</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>LJV3RM</t>
+          <t>STISOR</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Catalani/Rodrigo</t>
+          <t>SANTOS DE AQUINO/LUCAS</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>45871.47777777778</v>
+        <v>45873.12777777778</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>Melissa Ramos Antoniolli</t>
+          <t>Tittanium Engenharia</t>
         </is>
       </c>
       <c r="W18" s="5" t="inlineStr">
@@ -3857,11 +3857,11 @@
       </c>
       <c r="X18" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>955105639</v>
+        <v>2142685659</v>
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>183.5</v>
+        <v>1983.7</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>450</v>
+        <v>46.36</v>
       </c>
       <c r="AD18" s="5" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>80</v>
+        <v>178.53</v>
       </c>
       <c r="AI18" s="5" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AJ18" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK18" s="5" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="AL18" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM18" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN18" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO18" s="5" t="inlineStr">
@@ -3942,21 +3942,21 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>22670399</v>
+        <v>22681373</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>23477372</v>
+        <v>23485843</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>45871.47912037037</v>
+        <v>45873.78310185186</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>45871.47982638889</v>
+        <v>45873.78375</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>LJV3RM</t>
+          <t>LA9572246NXFN</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Catalani/Cezar</t>
+          <t>Paulino Da Silva Neto/Pedro</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>45871.47777777778</v>
+        <v>45873.24305555555</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -4013,12 +4013,12 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>Melissa Ramos Antoniolli</t>
+          <t>Mv Power Engenharia e Servicos</t>
         </is>
       </c>
       <c r="W19" s="5" t="inlineStr">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>314382208</v>
+        <v>2244270527</v>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>183.5</v>
+        <v>700.72</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>450</v>
+        <v>48.16</v>
       </c>
       <c r="AD19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>0</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="AF19" s="5" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>0</v>
+        <v>46.25</v>
       </c>
       <c r="AI19" s="5" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AJ19" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK19" s="5" t="inlineStr">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="AL19" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM19" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN19" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO19" s="5" t="inlineStr">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>22670439</v>
+        <v>22677959</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23477392</v>
+        <v>23482549</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>45871.49023148148</v>
+        <v>45873.49859953704</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>45871.50456018518</v>
+        <v>45873.50304398148</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>UNCWBS</t>
+          <t>LA9578335FBYP</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>MARCELO LESSA MOREIRA/PAULO</t>
+          <t>Alves Moura/Hugo</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>45871.46736111111</v>
+        <v>45873.46666666667</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>Solutis Tecnologias Ltda</t>
+          <t>Dox Planejamento, Gestao e Desenvolvimento Imobiliario</t>
         </is>
       </c>
       <c r="W20" s="5" t="inlineStr">
@@ -4239,11 +4239,11 @@
       </c>
       <c r="X20" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>2142555895</v>
+        <v>2244198652</v>
       </c>
       <c r="Z20" s="5" t="inlineStr">
         <is>
@@ -4256,16 +4256,16 @@
         </is>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>589.8</v>
+        <v>1391.44</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>60.62</v>
+        <v>476.92</v>
       </c>
       <c r="AD20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AF20" s="5" t="n">
         <v>0</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="AH20" s="5" t="n">
-        <v>41.29</v>
+        <v>89.33</v>
       </c>
       <c r="AI20" s="5" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AJ20" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK20" s="5" t="inlineStr">
@@ -4324,10 +4324,10 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>22659024</v>
+        <v>22677960</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>23467809</v>
+        <v>23482550</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -4335,24 +4335,24 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>45869.66074074074</v>
+        <v>45873.49861111111</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45869.66322916667</v>
+        <v>45873.50090277778</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>QGY74X</t>
+          <t>LA9570610UTDW</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>MONTEIRO PAULINO PAULINO/WILLIAM</t>
+          <t>Alves Moura/Hugo</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>45869.53541666667</v>
+        <v>45873.46666666667</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>R3ciclo Gestao de Residuos</t>
+          <t>Dox Planejamento, Gestao e Desenvolvimento Imobiliario</t>
         </is>
       </c>
       <c r="W21" s="5" t="inlineStr">
@@ -4430,11 +4430,11 @@
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>631205766</v>
+        <v>2244198164</v>
       </c>
       <c r="Z21" s="5" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
         </is>
       </c>
       <c r="AB21" s="5" t="n">
-        <v>818.5</v>
+        <v>1990.15</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>93.45999999999999</v>
+        <v>59.54</v>
       </c>
       <c r="AD21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>0</v>
+        <v>139.31</v>
       </c>
       <c r="AF21" s="5" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="5" t="n">
-        <v>81.84999999999999</v>
+        <v>127.77</v>
       </c>
       <c r="AI21" s="5" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="AJ21" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK21" s="5" t="inlineStr">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>22659083</v>
+        <v>22677696</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>23467866</v>
+        <v>23482290</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -4526,24 +4526,24 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>45869.66584490741</v>
+        <v>45873.46398148148</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>45870.67759259259</v>
+        <v>45873.46565972222</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>AXVCDI</t>
+          <t>LA9570512YXBQ</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>MATHEUS MARTINS DE SOUSA/LUCAS</t>
+          <t>DOS SANTOS GOMES/VAGNER</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>45869.16180555556</v>
+        <v>45873.40625</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S22" s="5" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>Ecoplan Engenharia Ltda</t>
+          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
         </is>
       </c>
       <c r="W22" s="5" t="inlineStr">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="X22" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>2142434993</v>
+        <v>2244192126</v>
       </c>
       <c r="Z22" s="5" t="inlineStr">
         <is>
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="AB22" s="5" t="n">
-        <v>2048.31</v>
+        <v>1497.82</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>30.95</v>
+        <v>77.97</v>
       </c>
       <c r="AD22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE22" s="5" t="n">
-        <v>0</v>
+        <v>149.78</v>
       </c>
       <c r="AF22" s="5" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AH22" s="5" t="n">
-        <v>0</v>
+        <v>296.57</v>
       </c>
       <c r="AI22" s="5" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AJ22" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK22" s="5" t="inlineStr">
@@ -4675,17 +4675,17 @@
       </c>
       <c r="AL22" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM22" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN22" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO22" s="5" t="inlineStr">
@@ -4706,35 +4706,35 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>22651101</v>
+        <v>22677696</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>23460675</v>
+        <v>23482291</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>45868.52986111111</v>
+        <v>45873.46398148148</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>45869.4131712963</v>
+        <v>45873.46565972222</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>MQU7YH01</t>
+          <t>LA9570512YXBQ</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>GONÇALVES/GUSTAVO</t>
+          <t>DE ARAUJO PEREIRA/LUCAS</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>45867.26875</v>
+        <v>45873.40625</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -4777,12 +4777,12 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V23" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
         </is>
       </c>
       <c r="W23" s="5" t="inlineStr">
@@ -4812,11 +4812,11 @@
       </c>
       <c r="X23" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>980419988</v>
+        <v>2244192127</v>
       </c>
       <c r="Z23" s="5" t="inlineStr">
         <is>
@@ -4829,16 +4829,16 @@
         </is>
       </c>
       <c r="AB23" s="5" t="n">
-        <v>713.2</v>
+        <v>1497.82</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>36.67</v>
+        <v>77.97</v>
       </c>
       <c r="AD23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE23" s="5" t="n">
-        <v>0</v>
+        <v>149.78</v>
       </c>
       <c r="AF23" s="5" t="n">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="AH23" s="5" t="n">
-        <v>92.72</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="5" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AJ23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK23" s="5" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AL23" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM23" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN23" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO23" s="5" t="inlineStr">
@@ -4897,45 +4897,45 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>22649789</v>
+        <v>22677696</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>23459302</v>
+        <v>23482292</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC03</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>45868.39388888889</v>
+        <v>45873.46398148148</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>45868.39738425926</v>
+        <v>45873.46565972222</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>5F7691</t>
+          <t>LA9570512YXBQ</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>VINICIUS SILVA/LEONARDO</t>
+          <t>SAMPAIO DOS SANTOS/HIAGO</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>45845.42916666667</v>
+        <v>45873.40625</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R24" s="5" t="inlineStr">
         <is>
-          <t>Faturado</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S24" s="5" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="T24" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U24" s="5" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="V24" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
         </is>
       </c>
       <c r="W24" s="5" t="inlineStr">
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>2240111841</v>
+        <v>2244192128</v>
       </c>
       <c r="Z24" s="5" t="inlineStr">
         <is>
@@ -5020,16 +5020,16 @@
         </is>
       </c>
       <c r="AB24" s="5" t="n">
-        <v>1336.02</v>
+        <v>1497.82</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>468.89</v>
+        <v>77.97</v>
       </c>
       <c r="AD24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE24" s="5" t="n">
-        <v>0</v>
+        <v>149.78</v>
       </c>
       <c r="AF24" s="5" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="5" t="n">
-        <v>45.69</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="5" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AJ24" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 2240111841 já sendo utilizado para este fornecedor.</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK24" s="5" t="inlineStr">
@@ -5057,17 +5057,17 @@
       </c>
       <c r="AL24" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM24" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN24" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO24" s="5" t="inlineStr">
@@ -5088,45 +5088,45 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>22649789</v>
+        <v>22677737</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>23459303</v>
+        <v>23482330</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>45868.39388888889</v>
+        <v>45873.469375</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>45868.39738425926</v>
+        <v>45873.47137731482</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>5F7691</t>
+          <t>LA9576694QSMK</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>FELIPE ARCOVERDE/ROBERTA</t>
+          <t>DE ALMEIDA/EDER</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>45845.42916666667</v>
+        <v>45873.38055555556</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>Faturado</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S25" s="5" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="T25" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U25" s="5" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="V25" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
         </is>
       </c>
       <c r="W25" s="5" t="inlineStr">
@@ -5198,7 +5198,7 @@
         </is>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>2240111842</v>
+        <v>2244193305</v>
       </c>
       <c r="Z25" s="5" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="AB25" s="5" t="n">
-        <v>1336.02</v>
+        <v>1196.22</v>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>468.89</v>
+        <v>77.97</v>
       </c>
       <c r="AD25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE25" s="5" t="n">
-        <v>0</v>
+        <v>119.62</v>
       </c>
       <c r="AF25" s="5" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AH25" s="5" t="n">
-        <v>0</v>
+        <v>157.9</v>
       </c>
       <c r="AI25" s="5" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AJ25" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 2240111841 já sendo utilizado para este fornecedor.</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK25" s="5" t="inlineStr">
@@ -5248,17 +5248,17 @@
       </c>
       <c r="AL25" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM25" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN25" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO25" s="5" t="inlineStr">
@@ -5279,35 +5279,35 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>22666753</v>
+        <v>22677737</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>23474591</v>
+        <v>23482331</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>45870.76394675926</v>
+        <v>45873.469375</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>45870.76523148148</v>
+        <v>45873.47137731482</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>NLR2FG</t>
+          <t>LA9576694QSMK</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>ALVES MENDES COSTA/WELBER</t>
+          <t>HENRIQUE WINGERT/LUIS</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>45870.24097222222</v>
+        <v>45873.38055555556</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="V26" s="5" t="inlineStr">
         <is>
-          <t>Tittanium Engenharia</t>
+          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
         </is>
       </c>
       <c r="W26" s="5" t="inlineStr">
@@ -5385,11 +5385,11 @@
       </c>
       <c r="X26" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>251146736</v>
+        <v>2244193306</v>
       </c>
       <c r="Z26" s="5" t="inlineStr">
         <is>
@@ -5402,16 +5402,16 @@
         </is>
       </c>
       <c r="AB26" s="5" t="n">
-        <v>1157.57</v>
+        <v>1196.22</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>33.56</v>
+        <v>77.97</v>
       </c>
       <c r="AD26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE26" s="5" t="n">
-        <v>0</v>
+        <v>119.62</v>
       </c>
       <c r="AF26" s="5" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="AH26" s="5" t="n">
-        <v>231.51</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="5" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AJ26" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK26" s="5" t="inlineStr">
@@ -5470,35 +5470,35 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>22666753</v>
+        <v>22677741</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>23474592</v>
+        <v>23482340</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45870.76394675926</v>
+        <v>45873.47215277778</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>45870.76523148148</v>
+        <v>45873.47341435185</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>NLR2FG</t>
+          <t>QI8USS</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>BARBOSA DOS SANTOS/CRISTIANO</t>
+          <t>CARLOS VIEIRA NETO/ANTONIO</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>45870.24097222222</v>
+        <v>45873.32083333333</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>591913092</v>
+        <v>945619142</v>
       </c>
       <c r="Z27" s="5" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="AB27" s="5" t="n">
-        <v>1157.57</v>
+        <v>936.4</v>
       </c>
       <c r="AC27" s="5" t="n">
         <v>33.56</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="AH27" s="5" t="n">
-        <v>0</v>
+        <v>280.92</v>
       </c>
       <c r="AI27" s="5" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AJ27" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK27" s="5" t="inlineStr">
@@ -5661,35 +5661,35 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>22666170</v>
+        <v>22677741</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>23474030</v>
+        <v>23482341</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>45870.72355324074</v>
+        <v>45873.47215277778</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>45870.73298611111</v>
+        <v>45873.47341435185</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>MM8JRG</t>
+          <t>QI8USS</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>DIAS/GABRIEL</t>
+          <t>COSTA DA SILVA/TIAGO</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="M28" s="6" t="n">
-        <v>45870.11111111111</v>
+        <v>45873.32083333333</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
+          <t>Tittanium Engenharia</t>
         </is>
       </c>
       <c r="W28" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>364000117</v>
+        <v>769974560</v>
       </c>
       <c r="Z28" s="5" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="AB28" s="5" t="n">
-        <v>740.84</v>
+        <v>936.4</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>93.48999999999999</v>
+        <v>33.56</v>
       </c>
       <c r="AD28" s="5" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="AH28" s="5" t="n">
-        <v>74.08</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="5" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ28" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK28" s="5" t="inlineStr">
@@ -5852,35 +5852,35 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>22666312</v>
+        <v>22677741</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>23474162</v>
+        <v>23482342</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC03</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>45870.74306712963</v>
+        <v>45873.47215277778</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>45870.74434027778</v>
+        <v>45873.47341435185</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>ULVCJW</t>
+          <t>QI8USS</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>RODRIGUES/GABRIEL</t>
+          <t>BENTO VIEIRA LEONIDIO/JULIO</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>45870.21736111111</v>
+        <v>45873.32083333333</v>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="V29" s="5" t="inlineStr">
         <is>
-          <t>Cqcs</t>
+          <t>Tittanium Engenharia</t>
         </is>
       </c>
       <c r="W29" s="5" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>129667076</v>
+        <v>547265770</v>
       </c>
       <c r="Z29" s="5" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="AB29" s="5" t="n">
-        <v>1025.92</v>
+        <v>936.4</v>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>44.27</v>
+        <v>33.56</v>
       </c>
       <c r="AD29" s="5" t="n">
         <v>0</v>
@@ -5993,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="AH29" s="5" t="n">
-        <v>102.59</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="5" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AJ29" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK29" s="5" t="inlineStr">
@@ -6043,10 +6043,10 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>22666003</v>
+        <v>22679284</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>23473870</v>
+        <v>23483750</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -6054,24 +6054,24 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>45870.7055787037</v>
+        <v>45873.62524305555</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>45870.72726851852</v>
+        <v>45873.62605324074</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>BGZ7UI</t>
+          <t>LA9577901VMYJ</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>TUNU/Jusiel</t>
+          <t>Shie/Petra</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="M30" s="6" t="n">
-        <v>45870.49861111111</v>
+        <v>45873.11527777778</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>Cogny Solutions Ltda</t>
+          <t>Sq Quimica Importadora Distribuidora de Produtos Quimicos Ltda</t>
         </is>
       </c>
       <c r="W30" s="5" t="inlineStr">
@@ -6149,11 +6149,11 @@
       </c>
       <c r="X30" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>459227779</v>
+        <v>2244227635</v>
       </c>
       <c r="Z30" s="5" t="inlineStr">
         <is>
@@ -6166,16 +6166,16 @@
         </is>
       </c>
       <c r="AB30" s="5" t="n">
-        <v>762.55</v>
+        <v>845.4400000000001</v>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>120.57</v>
+        <v>111.54</v>
       </c>
       <c r="AD30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
-        <v>0</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AF30" s="5" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="AH30" s="5" t="n">
-        <v>76.26000000000001</v>
+        <v>49.2</v>
       </c>
       <c r="AI30" s="5" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AJ30" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK30" s="5" t="inlineStr">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>22666040</v>
+        <v>22678683</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>23473906</v>
+        <v>23483247</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -6245,24 +6245,24 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>45870.71111111111</v>
+        <v>45873.52908564815</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45870.72925925926</v>
+        <v>45873.52951388889</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>JEIGSB</t>
+          <t>QQDYYX</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>MARCOS DOS SANTOS/ANTONIO</t>
+          <t>NARCISO TAVARES/GILBERTO</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="M31" s="6" t="n">
-        <v>45870.16944444444</v>
+        <v>45873.31944444445</v>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="V31" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
         </is>
       </c>
       <c r="W31" s="5" t="inlineStr">
@@ -6340,11 +6340,11 @@
       </c>
       <c r="X31" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>2142512480</v>
+        <v>649805726</v>
       </c>
       <c r="Z31" s="5" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="AB31" s="5" t="n">
-        <v>1330.32</v>
+        <v>1889.84</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>60.62</v>
+        <v>95.02</v>
       </c>
       <c r="AD31" s="5" t="n">
         <v>0</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="AH31" s="5" t="n">
-        <v>239.46</v>
+        <v>245.68</v>
       </c>
       <c r="AI31" s="5" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AJ31" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK31" s="5" t="inlineStr">
@@ -6425,35 +6425,35 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>22666040</v>
+        <v>22678767</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>23473907</v>
+        <v>23483320</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>45870.71111111111</v>
+        <v>45873.53740740741</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45870.72925925926</v>
+        <v>45873.53815972222</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>JEIGSB</t>
+          <t>LA9578331IVVO</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>FLOREANO/ANGELO</t>
+          <t>Henrique Bonfim Aguero/Caio</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>45870.16944444444</v>
+        <v>45873.31527777778</v>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="V32" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
         </is>
       </c>
       <c r="W32" s="5" t="inlineStr">
@@ -6531,11 +6531,11 @@
       </c>
       <c r="X32" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y32" s="5" t="n">
-        <v>2142512481</v>
+        <v>2244207216</v>
       </c>
       <c r="Z32" s="5" t="inlineStr">
         <is>
@@ -6548,16 +6548,16 @@
         </is>
       </c>
       <c r="AB32" s="5" t="n">
-        <v>1330.32</v>
+        <v>1372.72</v>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>60.62</v>
+        <v>48.16</v>
       </c>
       <c r="AD32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE32" s="5" t="n">
-        <v>0</v>
+        <v>137.27</v>
       </c>
       <c r="AF32" s="5" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="AH32" s="5" t="n">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AI32" s="5" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AJ32" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK32" s="5" t="inlineStr">
@@ -6616,10 +6616,10 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>22666104</v>
+        <v>22678751</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>23473964</v>
+        <v>23483305</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -6627,24 +6627,24 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>45870.71695601852</v>
+        <v>45873.53327546296</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>45870.73171296297</v>
+        <v>45873.53391203703</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>SIMZJC</t>
+          <t>XWZ7SD</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Nobre/Luis</t>
+          <t>do Nascimento Ribeiro/Sávio</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>45869.13888888889</v>
+        <v>45873.31111111111</v>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="V33" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
         </is>
       </c>
       <c r="W33" s="5" t="inlineStr">
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>286243421</v>
+        <v>598172318</v>
       </c>
       <c r="Z33" s="5" t="inlineStr">
         <is>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="AB33" s="5" t="n">
-        <v>1217.85</v>
+        <v>1661.97</v>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>86.14</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="AD33" s="5" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AH33" s="5" t="n">
-        <v>107.03</v>
+        <v>432.11</v>
       </c>
       <c r="AI33" s="5" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="AJ33" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
         </is>
       </c>
       <c r="AK33" s="5" t="inlineStr">
@@ -6807,190 +6807,572 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>22665674</v>
+        <v>22678751</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>23473565</v>
+        <v>23483306</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
+          <t>ACC02</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>45873.53327546296</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>45873.53391203703</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>XWZ7SD</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>de Souza Coelho/Felipe</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>45873.31111111111</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="inlineStr">
+        <is>
+          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X34" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>289916362</v>
+      </c>
+      <c r="Z34" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA34" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" s="5" t="n">
+        <v>1661.97</v>
+      </c>
+      <c r="AC34" s="5" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="AD34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ34" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+        </is>
+      </c>
+      <c r="AK34" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL34" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM34" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN34" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO34" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP34" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ34" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>22679406</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>23483900</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>45873.64061342592</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>45873.64673611111</v>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>GZLCXT</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>DANIELLE SILBERGLEID</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>45873.64027777778</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="inlineStr">
+        <is>
+          <t>Cartão convênio</t>
+        </is>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>Opportunity Gestora</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X35" s="5" t="inlineStr">
+        <is>
+          <t>Gol Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>2142657530</v>
+      </c>
+      <c r="Z35" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB35" s="5" t="n">
+        <v>730.8</v>
+      </c>
+      <c r="AC35" s="5" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AD35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ35" s="5" t="inlineStr">
+        <is>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+        </is>
+      </c>
+      <c r="AK35" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL35" s="5" t="inlineStr">
+        <is>
+          <t>Falta de informação Gerencial</t>
+        </is>
+      </c>
+      <c r="AM35" s="5" t="inlineStr">
+        <is>
+          <t>Rateio de centro de custo/projeto</t>
+        </is>
+      </c>
+      <c r="AN35" s="5" t="inlineStr">
+        <is>
+          <t>Dados Gerenciais</t>
+        </is>
+      </c>
+      <c r="AO35" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP35" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ35" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>22677911</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>23482505</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t>ACC01</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
-        <v>45870.66546296296</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>45870.66743055556</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>LA9577579UMMS</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="D36" s="6" t="n">
+        <v>45873.49025462963</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>45873.49657407407</v>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>VJCPHP</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>EBOOKING</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>GARCIA/HENRIQUE</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Andressa Vallini/Nathalie</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Kontrip</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>Kontrip</t>
         </is>
       </c>
-      <c r="M34" s="6" t="n">
-        <v>45869.18611111111</v>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="M36" s="6" t="n">
+        <v>45873.47986111111</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>OFF LINE</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>Cartão de crédito</t>
         </is>
       </c>
-      <c r="R34" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t>Cartão AMEX</t>
+        </is>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
         <is>
           <t>Aéreo</t>
         </is>
       </c>
-      <c r="T34" s="5" t="inlineStr">
+      <c r="T36" s="5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Merb</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>Mebr Varejo de Joias</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X34" s="5" t="inlineStr">
-        <is>
-          <t>Latam Airlines Brasil</t>
-        </is>
-      </c>
-      <c r="Y34" s="5" t="n">
-        <v>2243889987</v>
-      </c>
-      <c r="Z34" s="5" t="inlineStr">
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>Independente</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>Ideia 3</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X36" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>219715631</v>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
         <is>
           <t>KONTRIP</t>
         </is>
       </c>
-      <c r="AA34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB34" s="5" t="n">
-        <v>1150.24</v>
-      </c>
-      <c r="AC34" s="5" t="n">
-        <v>68.11</v>
-      </c>
-      <c r="AD34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="5" t="n">
-        <v>115.02</v>
-      </c>
-      <c r="AF34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="5" t="n">
-        <v>75.92</v>
-      </c>
-      <c r="AI34" s="5" t="inlineStr">
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="n">
+        <v>981.01</v>
+      </c>
+      <c r="AC36" s="5" t="n">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="AD36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="5" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="AI36" s="5" t="inlineStr">
         <is>
           <t>obs</t>
         </is>
       </c>
-      <c r="AJ34" s="5" t="inlineStr">
-        <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
-        </is>
-      </c>
-      <c r="AK34" s="5" t="inlineStr">
+      <c r="AJ36" s="5" t="inlineStr">
+        <is>
+          <t>Centro de custo não preenchido! (ACC01) Solicitante não preenchido! (ACC01)</t>
+        </is>
+      </c>
+      <c r="AK36" s="5" t="inlineStr">
         <is>
           <t>KONTRIP</t>
         </is>
       </c>
-      <c r="AL34" s="5" t="inlineStr">
-        <is>
-          <t>Não identificado</t>
-        </is>
-      </c>
-      <c r="AM34" s="5" t="inlineStr">
-        <is>
-          <t>Análise Benner</t>
-        </is>
-      </c>
-      <c r="AN34" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="AO34" s="5" t="inlineStr">
+      <c r="AL36" s="5" t="inlineStr">
+        <is>
+          <t>Mais de um campo não preenchido</t>
+        </is>
+      </c>
+      <c r="AM36" s="5" t="inlineStr">
+        <is>
+          <t>Falta de informação Gerencial</t>
+        </is>
+      </c>
+      <c r="AN36" s="5" t="inlineStr">
+        <is>
+          <t>Dados do Fornecedor</t>
+        </is>
+      </c>
+      <c r="AO36" s="5" t="inlineStr">
         <is>
           <t>Qualidade dos dados</t>
         </is>
       </c>
-      <c r="AP34" s="5" t="inlineStr">
+      <c r="AP36" s="5" t="inlineStr">
         <is>
           <t>KONTRIP VIAGENS</t>
         </is>
       </c>
-      <c r="AQ34" s="5" t="inlineStr">
+      <c r="AQ36" s="5" t="inlineStr">
         <is>
           <t>Operações - KONTRIP</t>
         </is>

--- a/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
+++ b/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ36"/>
+  <dimension ref="A1:AQ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,10 +695,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>22670530</v>
+        <v>22701489</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>23477463</v>
+        <v>23503652</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
@@ -706,24 +706,24 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>45871.50821759259</v>
+        <v>45876.61974537037</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>45871.51726851852</v>
+        <v>45876.62252314815</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>IIONJH</t>
+          <t>LA9575542VFFO</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>MARCELO LESSA MOREIRA/PAULO</t>
+          <t>Hiroyama/Rodrigo</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>45871.5</v>
+        <v>45876.54027777778</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S2" s="5" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="U2" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>Solutis Tecnologias Ltda</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W2" s="5" t="inlineStr">
@@ -801,11 +801,11 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>2142557937</v>
+        <v>2244704214</v>
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>799.1</v>
+        <v>399.8</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>34.11</v>
+        <v>67.75</v>
       </c>
       <c r="AD2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE2" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF2" s="5" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>55.94</v>
+        <v>26.39</v>
       </c>
       <c r="AI2" s="5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK2" s="5" t="inlineStr">
@@ -886,10 +886,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>22670439</v>
+        <v>22701526</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23477392</v>
+        <v>23503679</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -897,24 +897,24 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45871.49023148148</v>
+        <v>45876.62355324074</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>45871.50456018518</v>
+        <v>45876.62640046296</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>UNCWBS</t>
+          <t>YINS5C</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>MARCELO LESSA MOREIRA/PAULO</t>
+          <t>Boelter/Joel</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>45871.46736111111</v>
+        <v>45876.52847222222</v>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>Solutis Tecnologias Ltda</t>
+          <t>Felice Automoveis Ltda</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
@@ -992,11 +992,11 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>2142555895</v>
+        <v>721127445</v>
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>589.8</v>
+        <v>2030.81</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>60.62</v>
+        <v>116.64</v>
       </c>
       <c r="AD3" s="5" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>41.29</v>
+        <v>203.08</v>
       </c>
       <c r="AI3" s="5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AJ3" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK3" s="5" t="inlineStr">
@@ -1077,10 +1077,10 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>22666040</v>
+        <v>22704257</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>23473906</v>
+        <v>23506291</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -1088,24 +1088,24 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45870.71111111111</v>
+        <v>45876.85268518519</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>45870.72925925926</v>
+        <v>45876.85496527778</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>JEIGSB</t>
+          <t>SP4F5K</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>MARCOS DOS SANTOS/ANTONIO</t>
+          <t>SANTOS/SUELLEN</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>45870.16944444444</v>
+        <v>45876.22638888889</v>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>2142512480</v>
+        <v>259866459</v>
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>1330.32</v>
+        <v>2272.06</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>60.62</v>
+        <v>101.17</v>
       </c>
       <c r="AD4" s="5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>239.46</v>
+        <v>113.6</v>
       </c>
       <c r="AI4" s="5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AJ4" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK4" s="5" t="inlineStr">
@@ -1268,35 +1268,35 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>22666040</v>
+        <v>22704264</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>23473907</v>
+        <v>23506303</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45870.71111111111</v>
+        <v>45876.8544212963</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>45870.72925925926</v>
+        <v>45876.85671296297</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>JEIGSB</t>
+          <t>VMYRHG</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>FLOREANO/ANGELO</t>
+          <t>VALENTE/KEILA</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>45870.16944444444</v>
+        <v>45876.23958333334</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W5" s="5" t="inlineStr">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="X5" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>2142512481</v>
+        <v>384657625</v>
       </c>
       <c r="Z5" s="5" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>1330.32</v>
+        <v>2272.06</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>60.62</v>
+        <v>101.17</v>
       </c>
       <c r="AD5" s="5" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>0</v>
+        <v>113.6</v>
       </c>
       <c r="AI5" s="5" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AJ5" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK5" s="5" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>22666104</v>
+        <v>22704266</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>23473964</v>
+        <v>23506306</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -1470,24 +1470,24 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45870.71695601852</v>
+        <v>45876.85545138889</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>45870.73171296297</v>
+        <v>45876.85675925926</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>SIMZJC</t>
+          <t>LLL72T</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Nobre/Luis</t>
+          <t>OLIVEIRA/ADRIANA</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>45869.13888888889</v>
+        <v>45876.24583333333</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W6" s="5" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>286243421</v>
+        <v>968746609</v>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>1217.85</v>
+        <v>2272.06</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>86.14</v>
+        <v>101.17</v>
       </c>
       <c r="AD6" s="5" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>107.03</v>
+        <v>113.6</v>
       </c>
       <c r="AI6" s="5" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AJ6" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK6" s="5" t="inlineStr">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>22663695</v>
+        <v>22704366</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>23471719</v>
+        <v>23506390</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1661,24 +1661,24 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>45870.44738425926</v>
+        <v>45876.87491898148</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45870.45027777777</v>
+        <v>45876.87604166667</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>LA9578225DGWN</t>
+          <t>YPRQYN</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Vignoli dos Santos/Lua</t>
+          <t>Borba/Felipe</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>45870.37708333333</v>
+        <v>45876.37291666667</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Galera Gaming Jogos Eletronicos</t>
         </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
@@ -1756,11 +1756,11 @@
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>2243839157</v>
+        <v>553122361</v>
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>1023.29</v>
+        <v>824.25</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>59.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>102.32</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="5" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>67.54000000000001</v>
+        <v>40</v>
       </c>
       <c r="AI7" s="5" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AJ7" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK7" s="5" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>22665072</v>
+        <v>22703064</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>23473040</v>
+        <v>23505173</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -1852,24 +1852,24 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45870.56806712963</v>
+        <v>45876.76805555556</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>45870.56925925926</v>
+        <v>45876.76949074074</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>LPYFTK</t>
+          <t>BPP6HH</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>de Brito/Odomar</t>
+          <t>Alexandre Frosini Evangelista/Carlos</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>45870.53472222222</v>
+        <v>45876.26736111111</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>Ntsec - Network Security</t>
+          <t>Associacao Brasileira de Geracao Distribuida - Abgd</t>
         </is>
       </c>
       <c r="W8" s="5" t="inlineStr">
@@ -1947,11 +1947,11 @@
       </c>
       <c r="X8" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>2142496529</v>
+        <v>530146970</v>
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>555</v>
+        <v>1435.99</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>30.95</v>
+        <v>450</v>
       </c>
       <c r="AD8" s="5" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>38.85</v>
+        <v>40</v>
       </c>
       <c r="AI8" s="5" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AJ8" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK8" s="5" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="AL8" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM8" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN8" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO8" s="5" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>22665087</v>
+        <v>22703095</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>23473060</v>
+        <v>23505205</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -2043,24 +2043,24 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>45870.57103009259</v>
+        <v>45876.76944444444</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>45870.57363425926</v>
+        <v>45876.77215277778</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>GCIAOH</t>
+          <t>KQRSAC</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Pereira de Brito/Odomar</t>
+          <t>Sampaio/Bergsan</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>45870.04236111111</v>
+        <v>45876.24097222222</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>2142496551</v>
+        <v>2142916171</v>
       </c>
       <c r="Z9" s="5" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AB9" s="5" t="n">
-        <v>1301.2</v>
+        <v>1450.44</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>58.89</v>
+        <v>36.67</v>
       </c>
       <c r="AD9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>0</v>
+        <v>145.04</v>
       </c>
       <c r="AF9" s="5" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>91.08</v>
+        <v>111.68</v>
       </c>
       <c r="AI9" s="5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AJ9" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 01/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK9" s="5" t="inlineStr">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>22659024</v>
+        <v>22703175</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>23467809</v>
+        <v>23505287</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -2234,24 +2234,24 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45869.66074074074</v>
+        <v>45876.77498842592</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>45869.66322916667</v>
+        <v>45876.77726851852</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>QGY74X</t>
+          <t>IRPIKD</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>MONTEIRO PAULINO PAULINO/WILLIAM</t>
+          <t>Sampaio/Bergsan</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>45869.53541666667</v>
+        <v>45876.23819444444</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>R3ciclo Gestao de Residuos</t>
+          <t>Ntsec - Network Security</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2329,11 +2329,11 @@
       </c>
       <c r="X10" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>631205766</v>
+        <v>2142916962</v>
       </c>
       <c r="Z10" s="5" t="inlineStr">
         <is>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="AB10" s="5" t="n">
-        <v>818.5</v>
+        <v>1698.87</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>93.45999999999999</v>
+        <v>51.07</v>
       </c>
       <c r="AD10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>0</v>
+        <v>169.88</v>
       </c>
       <c r="AF10" s="5" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="5" t="n">
-        <v>81.84999999999999</v>
+        <v>130.81</v>
       </c>
       <c r="AI10" s="5" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AJ10" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 31/07/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK10" s="5" t="inlineStr">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>22651101</v>
+        <v>22686963</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23460675</v>
+        <v>23490647</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -2425,24 +2425,24 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>45868.52986111111</v>
+        <v>45874.65428240741</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>45869.4131712963</v>
+        <v>45875.7694675926</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
           <t>03 a 05 dias</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>06 a 08 dias</t>
-        </is>
-      </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>MQU7YH01</t>
+          <t>YOVNRQ</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>GONÇALVES/GUSTAVO</t>
+          <t>ALMEIDA/LUIZ</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>45867.26875</v>
+        <v>45874.15208333333</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Araforros Ind e Comercio de Perfilados Ltda Em Recuperacao Judicial</t>
         </is>
       </c>
       <c r="W11" s="5" t="inlineStr">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>980419988</v>
+        <v>3023498529</v>
       </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>713.2</v>
+        <v>0.01</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>36.67</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="5" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>92.72</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="5" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AJ11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Validação do documento: Valor dever ser maior que zero !</t>
         </is>
       </c>
       <c r="AK11" s="5" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="AL11" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM11" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN11" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO11" s="5" t="inlineStr">
@@ -2605,10 +2605,10 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>22649789</v>
+        <v>22693553</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>23459302</v>
+        <v>23496484</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -2616,34 +2616,34 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>45868.39388888889</v>
+        <v>45875.53638888889</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>45868.39738425926</v>
+        <v>45875.53846064815</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>5F7691</t>
+          <t>EFCSHY</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>VINICIUS SILVA/LEONARDO</t>
+          <t>ROGERIO DE FRANÇA/PAULO</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>45845.42916666667</v>
+        <v>45875.53541666667</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
-          <t>Faturado</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S12" s="5" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="T12" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U12" s="5" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Mei Instalacao Industrial Ltda</t>
         </is>
       </c>
       <c r="W12" s="5" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="X12" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>2240111841</v>
+        <v>442777606</v>
       </c>
       <c r="Z12" s="5" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="AB12" s="5" t="n">
-        <v>1336.02</v>
+        <v>71.8</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>468.89</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="5" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="5" t="n">
-        <v>45.69</v>
+        <v>40</v>
       </c>
       <c r="AI12" s="5" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AJ12" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 2240111841 já sendo utilizado para este fornecedor.</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK12" s="5" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="AL12" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM12" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN12" s="5" t="inlineStr">
@@ -2796,35 +2796,35 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>22649789</v>
+        <v>22692401</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>23459303</v>
+        <v>23495383</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>45868.39388888889</v>
+        <v>45875.45380787037</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>45868.39738425926</v>
+        <v>45875.45554398148</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>5F7691</t>
+          <t>NRFVAS</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>FELIPE ARCOVERDE/ROBERTA</t>
+          <t>Cardoso/Felipe</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>45845.42916666667</v>
+        <v>45869.04861111111</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -2867,12 +2867,12 @@
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
-          <t>Faturado</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S13" s="5" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W13" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>2240111842</v>
+        <v>2243683469</v>
       </c>
       <c r="Z13" s="5" t="inlineStr">
         <is>
@@ -2919,16 +2919,16 @@
         </is>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>1336.02</v>
+        <v>590.3200000000001</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>468.89</v>
+        <v>30.95</v>
       </c>
       <c r="AD13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>0</v>
+        <v>59.03</v>
       </c>
       <c r="AF13" s="5" t="n">
         <v>0</v>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="AI13" s="5" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>obsCancelamento VOID do pax FELIPE CARDOSO</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 2240111841 já sendo utilizado para este fornecedor.</t>
+          <t>Verificação de bilhetes: Bilhete 2243683469 já sendo utilizado para este fornecedor.</t>
         </is>
       </c>
       <c r="AK13" s="5" t="inlineStr">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>22680202</v>
+        <v>22700765</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23484639</v>
+        <v>23502981</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>45873.73334490741</v>
+        <v>45876.5291087963</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>45873.7425</v>
+        <v>45876.53026620371</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>LA9570609WFVC</t>
+          <t>CME1UD</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>DE AZEVEDO BATISTA/CARLA</t>
+          <t>MARIO MOUTINHO/LUIZ</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>45871.425</v>
+        <v>45876.52777777778</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Daten Tecnologia</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="X14" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>2244256929</v>
+        <v>781870213</v>
       </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="AB14" s="5" t="n">
-        <v>824.34</v>
+        <v>1893.59</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>98.72</v>
+        <v>119.51</v>
       </c>
       <c r="AD14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE14" s="5" t="n">
-        <v>82.43000000000001</v>
+        <v>201.31</v>
       </c>
       <c r="AF14" s="5" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="5" t="n">
-        <v>54.41</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="AI14" s="5" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AJ14" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 02/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK14" s="5" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="AL14" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM14" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN14" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO14" s="5" t="inlineStr">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>22679735</v>
+        <v>22700473</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>23484196</v>
+        <v>23502703</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>45873.68053240741</v>
+        <v>45876.51666666667</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>45873.6818287037</v>
+        <v>45876.51966435185</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>LA9576133CCPW</t>
+          <t>WAQULI</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Marcos Andrade/Antonio</t>
+          <t>Santos Junior/Roberto</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>45873.09583333333</v>
+        <v>45876.51597222222</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Memora</t>
         </is>
       </c>
       <c r="W15" s="5" t="inlineStr">
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>2244241726</v>
+        <v>2244411354</v>
       </c>
       <c r="Z15" s="5" t="inlineStr">
         <is>
@@ -3301,16 +3301,16 @@
         </is>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>668.02</v>
+        <v>1260</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>48.16</v>
+        <v>80.69</v>
       </c>
       <c r="AD15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>66.8</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="5" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>44.09</v>
+        <v>88.19</v>
       </c>
       <c r="AI15" s="5" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AJ15" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK15" s="5" t="inlineStr">
@@ -3338,17 +3338,17 @@
       </c>
       <c r="AL15" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM15" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN15" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO15" s="5" t="inlineStr">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>22679744</v>
+        <v>22700624</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>23484203</v>
+        <v>23502845</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>45873.68329861111</v>
+        <v>45876.52388888889</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>45873.68420138889</v>
+        <v>45876.52570601852</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>LA9570240ACXE</t>
+          <t>UHQOPY</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>ZUBIOLI/FABIO</t>
+          <t>Powell/Alexandre</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>45873.08819444444</v>
+        <v>45876.52152777778</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Powell Consultoria</t>
         </is>
       </c>
       <c r="W16" s="5" t="inlineStr">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>2244242639</v>
+        <v>2244375759</v>
       </c>
       <c r="Z16" s="5" t="inlineStr">
         <is>
@@ -3492,16 +3492,16 @@
         </is>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>738.65</v>
+        <v>128.79</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>48.16</v>
+        <v>450</v>
       </c>
       <c r="AD16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>73.86</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="5" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="5" t="n">
-        <v>97.5</v>
+        <v>40</v>
       </c>
       <c r="AI16" s="5" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AJ16" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Verificação de bilhetes: Bilhete 2244375759 já sendo utilizado para este fornecedor.</t>
         </is>
       </c>
       <c r="AK16" s="5" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="AL16" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Bilhete duplicado</t>
         </is>
       </c>
       <c r="AM16" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Bilhete Já Contabilizado</t>
         </is>
       </c>
       <c r="AN16" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO16" s="5" t="inlineStr">
@@ -3560,21 +3560,21 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>22679744</v>
+        <v>22700741</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>23484204</v>
+        <v>23502957</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>45873.68329861111</v>
+        <v>45876.52784722222</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>45873.68420138889</v>
+        <v>45876.52979166667</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>LA9570240ACXE</t>
+          <t>LA9579303WVLK</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>BARBOSA/MAURICIO</t>
+          <t>KERTZMAN/IVAN</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>45873.08819444444</v>
+        <v>45875.30763888889</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Imadec</t>
         </is>
       </c>
       <c r="W17" s="5" t="inlineStr">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>2244242640</v>
+        <v>2244684148</v>
       </c>
       <c r="Z17" s="5" t="inlineStr">
         <is>
@@ -3683,16 +3683,16 @@
         </is>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>738.65</v>
+        <v>600.72</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>48.16</v>
+        <v>43.65</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>73.86</v>
+        <v>60.07</v>
       </c>
       <c r="AF17" s="5" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>0</v>
+        <v>39.65</v>
       </c>
       <c r="AI17" s="5" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AJ17" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
         </is>
       </c>
       <c r="AK17" s="5" t="inlineStr">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>22679780</v>
+        <v>22696940</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>23484235</v>
+        <v>23499770</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45873.68884259259</v>
+        <v>45875.87490740741</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>45873.68983796296</v>
+        <v>45875.8759375</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>STISOR</t>
+          <t>LA9578941SQLG</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>SANTOS DE AQUINO/LUCAS</t>
+          <t>Elizabeth Guilarte/Dayana</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>45873.12777777778</v>
+        <v>45875.24027777778</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>Tittanium Engenharia</t>
+          <t>Zubale Brasil Tecnologia Ltda.</t>
         </is>
       </c>
       <c r="W18" s="5" t="inlineStr">
@@ -3857,11 +3857,11 @@
       </c>
       <c r="X18" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>2142685659</v>
+        <v>2244613800</v>
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
@@ -3874,16 +3874,16 @@
         </is>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>1983.7</v>
+        <v>1805.52</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46.36</v>
+        <v>60.62</v>
       </c>
       <c r="AD18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE18" s="5" t="n">
-        <v>0</v>
+        <v>180.55</v>
       </c>
       <c r="AF18" s="5" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>178.53</v>
+        <v>119.16</v>
       </c>
       <c r="AI18" s="5" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AJ18" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
         </is>
       </c>
       <c r="AK18" s="5" t="inlineStr">
@@ -3942,10 +3942,10 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>22681373</v>
+        <v>22696941</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>23485843</v>
+        <v>23499771</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>45873.78310185186</v>
+        <v>45875.87491898148</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>45873.78375</v>
+        <v>45875.8771875</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>LA9572246NXFN</t>
+          <t>LA9578787ETLE</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Paulino Da Silva Neto/Pedro</t>
+          <t>Elizabeth Guilarte/Dayana</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>45873.24305555555</v>
+        <v>45875.24027777778</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>Mv Power Engenharia e Servicos</t>
+          <t>Zubale Brasil Tecnologia Ltda.</t>
         </is>
       </c>
       <c r="W19" s="5" t="inlineStr">
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>2244270527</v>
+        <v>2244613732</v>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>700.72</v>
+        <v>2083.12</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>48.16</v>
+        <v>52.56</v>
       </c>
       <c r="AD19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>70.06999999999999</v>
+        <v>208.31</v>
       </c>
       <c r="AF19" s="5" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>46.25</v>
+        <v>137.49</v>
       </c>
       <c r="AI19" s="5" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AJ19" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
         </is>
       </c>
       <c r="AK19" s="5" t="inlineStr">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>22677959</v>
+        <v>22699617</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23482549</v>
+        <v>23501892</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>45873.49859953704</v>
+        <v>45876.43893518519</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>45873.50304398148</v>
+        <v>45876.44039351852</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>LA9578335FBYP</t>
+          <t>XNK8WT</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Alves Moura/Hugo</t>
+          <t>SILVA/ABEL</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>45873.46666666667</v>
+        <v>45876.4375</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>Dox Planejamento, Gestao e Desenvolvimento Imobiliario</t>
+          <t>Topocart Topografia Engenharia e Aerolevantamentos</t>
         </is>
       </c>
       <c r="W20" s="5" t="inlineStr">
@@ -4239,11 +4239,11 @@
       </c>
       <c r="X20" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>2244198652</v>
+        <v>778248674</v>
       </c>
       <c r="Z20" s="5" t="inlineStr">
         <is>
@@ -4256,16 +4256,16 @@
         </is>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>1391.44</v>
+        <v>166.75</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>476.92</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>97.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="5" t="n">
         <v>0</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="AH20" s="5" t="n">
-        <v>89.33</v>
+        <v>40</v>
       </c>
       <c r="AI20" s="5" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AJ20" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK20" s="5" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="AL20" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM20" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN20" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO20" s="5" t="inlineStr">
@@ -4324,10 +4324,10 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>22677960</v>
+        <v>22700023</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>23482550</v>
+        <v>23502265</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>45873.49861111111</v>
+        <v>45876.48756944444</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45873.50090277778</v>
+        <v>45876.48841435185</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>LA9570610UTDW</t>
+          <t>RQYD9H</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Alves Moura/Hugo</t>
+          <t>Leguizamón/Iolanda</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>45873.46666666667</v>
+        <v>45876.47638888889</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>Dox Planejamento, Gestao e Desenvolvimento Imobiliario</t>
+          <t>Iolanda de Almeida Leguizamon Ltda</t>
         </is>
       </c>
       <c r="W21" s="5" t="inlineStr">
@@ -4430,11 +4430,11 @@
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>2244198164</v>
+        <v>545138544</v>
       </c>
       <c r="Z21" s="5" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
         </is>
       </c>
       <c r="AB21" s="5" t="n">
-        <v>1990.15</v>
+        <v>409.41</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>59.54</v>
+        <v>93.59</v>
       </c>
       <c r="AD21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>139.31</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="5" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="5" t="n">
-        <v>127.77</v>
+        <v>81.88</v>
       </c>
       <c r="AI21" s="5" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="AJ21" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK21" s="5" t="inlineStr">
@@ -4515,21 +4515,21 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>22677696</v>
+        <v>22700023</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>23482290</v>
+        <v>23502266</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>45873.46398148148</v>
+        <v>45876.48756944444</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>45873.46565972222</v>
+        <v>45876.48841435185</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>LA9570512YXBQ</t>
+          <t>RQYD9H</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>DOS SANTOS GOMES/VAGNER</t>
+          <t>Leguizamón/Jorge</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>45873.40625</v>
+        <v>45876.47638888889</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
+          <t>Iolanda de Almeida Leguizamon Ltda</t>
         </is>
       </c>
       <c r="W22" s="5" t="inlineStr">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="X22" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>2244192126</v>
+        <v>380351125</v>
       </c>
       <c r="Z22" s="5" t="inlineStr">
         <is>
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="AB22" s="5" t="n">
-        <v>1497.82</v>
+        <v>409.41</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>77.97</v>
+        <v>93.59</v>
       </c>
       <c r="AD22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE22" s="5" t="n">
-        <v>149.78</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="5" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AH22" s="5" t="n">
-        <v>296.57</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="5" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AJ22" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK22" s="5" t="inlineStr">
@@ -4706,21 +4706,21 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>22677696</v>
+        <v>22700070</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>23482291</v>
+        <v>23502309</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>45873.46398148148</v>
+        <v>45876.49452546296</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>45873.46565972222</v>
+        <v>45876.49780092593</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>LA9570512YXBQ</t>
+          <t>YM1U2G</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>DE ARAUJO PEREIRA/LUCAS</t>
+          <t>ESTEVAO PERDIGAO DE MIRANDA/LUIZ</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>45873.40625</v>
+        <v>45876.49166666667</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V23" s="5" t="inlineStr">
         <is>
-          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W23" s="5" t="inlineStr">
@@ -4812,11 +4812,11 @@
       </c>
       <c r="X23" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>2244192127</v>
+        <v>743416547</v>
       </c>
       <c r="Z23" s="5" t="inlineStr">
         <is>
@@ -4829,16 +4829,16 @@
         </is>
       </c>
       <c r="AB23" s="5" t="n">
-        <v>1497.82</v>
+        <v>1147.84</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>77.97</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="AD23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE23" s="5" t="n">
-        <v>149.78</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="5" t="n">
         <v>0</v>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AJ23" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK23" s="5" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AL23" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM23" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN23" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO23" s="5" t="inlineStr">
@@ -4897,21 +4897,21 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>22677696</v>
+        <v>22695090</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>23482292</v>
+        <v>23497957</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>ACC03</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>45873.46398148148</v>
+        <v>45875.73756944444</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>45873.46565972222</v>
+        <v>45875.7380787037</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>LA9570512YXBQ</t>
+          <t>QIGHPS</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>SAMPAIO DOS SANTOS/HIAGO</t>
+          <t>FERREIRA/ISABELLE</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>45873.40625</v>
+        <v>45875.23680555556</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="V24" s="5" t="inlineStr">
         <is>
-          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
+          <t>Tailler</t>
         </is>
       </c>
       <c r="W24" s="5" t="inlineStr">
@@ -5003,11 +5003,11 @@
       </c>
       <c r="X24" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>2244192128</v>
+        <v>408236868</v>
       </c>
       <c r="Z24" s="5" t="inlineStr">
         <is>
@@ -5020,16 +5020,16 @@
         </is>
       </c>
       <c r="AB24" s="5" t="n">
-        <v>1497.82</v>
+        <v>365.4</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>77.97</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="AD24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE24" s="5" t="n">
-        <v>149.78</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="5" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="5" t="n">
-        <v>0</v>
+        <v>40.92</v>
       </c>
       <c r="AI24" s="5" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AJ24" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
         </is>
       </c>
       <c r="AK24" s="5" t="inlineStr">
@@ -5088,10 +5088,10 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>22677737</v>
+        <v>22695192</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>23482330</v>
+        <v>23498043</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>45873.469375</v>
+        <v>45875.74878472222</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>45873.47137731482</v>
+        <v>45875.75137731482</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>LA9576694QSMK</t>
+          <t>YJD2PC</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>DE ALMEIDA/EDER</t>
+          <t>FERREIRA/ISABELLE</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>45873.38055555556</v>
+        <v>45875.24722222222</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="V25" s="5" t="inlineStr">
         <is>
-          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
+          <t>Tailler</t>
         </is>
       </c>
       <c r="W25" s="5" t="inlineStr">
@@ -5194,11 +5194,11 @@
       </c>
       <c r="X25" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>2244193305</v>
+        <v>267448399</v>
       </c>
       <c r="Z25" s="5" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="AB25" s="5" t="n">
-        <v>1196.22</v>
+        <v>1055.6</v>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>77.97</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="AD25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE25" s="5" t="n">
-        <v>119.62</v>
+        <v>0</v>
       </c>
       <c r="AF25" s="5" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AH25" s="5" t="n">
-        <v>157.9</v>
+        <v>40.92</v>
       </c>
       <c r="AI25" s="5" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AJ25" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
         </is>
       </c>
       <c r="AK25" s="5" t="inlineStr">
@@ -5279,21 +5279,21 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>22677737</v>
+        <v>22694293</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>23482331</v>
+        <v>23497154</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>45873.469375</v>
+        <v>45875.64717592593</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>45873.47137731482</v>
+        <v>45875.64989583333</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -5307,17 +5307,17 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>LA9576694QSMK</t>
+          <t>PLKSQW</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>EBOOKING</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>HENRIQUE WINGERT/LUIS</t>
+          <t>ELIZABETH SILVA</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>45873.38055555556</v>
+        <v>45870.64652777778</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="V26" s="5" t="inlineStr">
         <is>
-          <t>Apple Producoes E Locacoes De Equipamentos Ltda</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W26" s="5" t="inlineStr">
@@ -5385,11 +5385,11 @@
       </c>
       <c r="X26" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>2244193306</v>
+        <v>3023497153</v>
       </c>
       <c r="Z26" s="5" t="inlineStr">
         <is>
@@ -5402,16 +5402,16 @@
         </is>
       </c>
       <c r="AB26" s="5" t="n">
-        <v>1196.22</v>
+        <v>1070.25</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>77.97</v>
+        <v>86.14</v>
       </c>
       <c r="AD26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE26" s="5" t="n">
-        <v>119.62</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="5" t="n">
         <v>0</v>
@@ -5420,16 +5420,16 @@
         <v>0</v>
       </c>
       <c r="AH26" s="5" t="n">
-        <v>0</v>
+        <v>107.03</v>
       </c>
       <c r="AI26" s="5" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AJ26" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
         </is>
       </c>
       <c r="AK26" s="5" t="inlineStr">
@@ -5439,17 +5439,17 @@
       </c>
       <c r="AL26" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AM26" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Rateio de centro de custo/projeto</t>
         </is>
       </c>
       <c r="AN26" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados Gerenciais</t>
         </is>
       </c>
       <c r="AO26" s="5" t="inlineStr">
@@ -5470,10 +5470,10 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>22677741</v>
+        <v>22693812</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>23482340</v>
+        <v>23496718</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45873.47215277778</v>
+        <v>45875.57494212963</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>45873.47341435185</v>
+        <v>45875.57653935185</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>QI8USS</t>
+          <t>II9WRC</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>CARLOS VIEIRA NETO/ANTONIO</t>
+          <t>EMILIO BRANDAO DE ARAUJO/CARLOS</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>45873.32083333333</v>
+        <v>45875.07291666666</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="V27" s="5" t="inlineStr">
         <is>
-          <t>Tittanium Engenharia</t>
+          <t>Conorte Servicos Industriais Ltda</t>
         </is>
       </c>
       <c r="W27" s="5" t="inlineStr">
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>945619142</v>
+        <v>863078581</v>
       </c>
       <c r="Z27" s="5" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="AB27" s="5" t="n">
-        <v>936.4</v>
+        <v>548.92</v>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>33.56</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="5" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="AH27" s="5" t="n">
-        <v>280.92</v>
+        <v>40</v>
       </c>
       <c r="AI27" s="5" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AJ27" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK27" s="5" t="inlineStr">
@@ -5630,17 +5630,17 @@
       </c>
       <c r="AL27" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM27" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN27" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO27" s="5" t="inlineStr">
@@ -5661,35 +5661,35 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>22677741</v>
+        <v>22651101</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>23482341</v>
+        <v>23460675</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>45873.47215277778</v>
+        <v>45868.52986111111</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>45873.47341435185</v>
+        <v>45869.4131712963</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>09 a 15 dias</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>QI8USS</t>
+          <t>MQU7YH01</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>COSTA DA SILVA/TIAGO</t>
+          <t>GONÇALVES/GUSTAVO</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="M28" s="6" t="n">
-        <v>45873.32083333333</v>
+        <v>45867.26875</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>?</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>?</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>Tittanium Engenharia</t>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
         </is>
       </c>
       <c r="W28" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>769974560</v>
+        <v>980419988</v>
       </c>
       <c r="Z28" s="5" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="AB28" s="5" t="n">
-        <v>936.4</v>
+        <v>713.2</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>33.56</v>
+        <v>36.67</v>
       </c>
       <c r="AD28" s="5" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="AH28" s="5" t="n">
-        <v>0</v>
+        <v>92.72</v>
       </c>
       <c r="AI28" s="5" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ28" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
         </is>
       </c>
       <c r="AK28" s="5" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="AL28" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Forma de Pagamento indevida</t>
         </is>
       </c>
       <c r="AM28" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Forma PG. e REC.</t>
         </is>
       </c>
       <c r="AN28" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO28" s="5" t="inlineStr">
@@ -5852,21 +5852,21 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>22677741</v>
+        <v>22701761</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>23482342</v>
+        <v>23503924</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ACC03</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>45873.47215277778</v>
+        <v>45876.66204861111</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>45873.47341435185</v>
+        <v>45876.67363425926</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -5880,17 +5880,17 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>QI8USS</t>
+          <t>OMQC5Q</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>EBOOKING</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>BENTO VIEIRA LEONIDIO/JULIO</t>
+          <t>ANA PAULA NERI</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>45873.32083333333</v>
+        <v>45875.66180555556</v>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="V29" s="5" t="inlineStr">
         <is>
-          <t>Tittanium Engenharia</t>
+          <t>Tivita Tecnologia E Servicos Ltda</t>
         </is>
       </c>
       <c r="W29" s="5" t="inlineStr">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>547265770</v>
+        <v>3023503923</v>
       </c>
       <c r="Z29" s="5" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         </is>
       </c>
       <c r="AB29" s="5" t="n">
-        <v>936.4</v>
+        <v>473.92</v>
       </c>
       <c r="AC29" s="5" t="n">
         <v>33.56</v>
@@ -5993,16 +5993,16 @@
         <v>0</v>
       </c>
       <c r="AH29" s="5" t="n">
-        <v>0</v>
+        <v>47.39</v>
       </c>
       <c r="AI29" s="5" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AJ29" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t xml:space="preserve">35Ocorreu a seguinte exceção ao gerar a ordem de venda: Ocorreu a seguinte exceção ao inserir o item da ordem de venda:  Faltou informar rateio de </t>
         </is>
       </c>
       <c r="AK29" s="5" t="inlineStr">
@@ -6012,17 +6012,17 @@
       </c>
       <c r="AL29" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AM29" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Rateio de centro de custo/projeto</t>
         </is>
       </c>
       <c r="AN29" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados Gerenciais</t>
         </is>
       </c>
       <c r="AO29" s="5" t="inlineStr">
@@ -6043,10 +6043,10 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>22679284</v>
+        <v>22702509</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>23483750</v>
+        <v>23504650</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>45873.62524305555</v>
+        <v>45876.74446759259</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>45873.62605324074</v>
+        <v>45876.74635416667</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>LA9577901VMYJ</t>
+          <t>IMMTNW</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Shie/Petra</t>
+          <t>Ribeiro Gomes Amorim/Fernanda</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="M30" s="6" t="n">
-        <v>45873.11527777778</v>
+        <v>45875.12361111111</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>Sq Quimica Importadora Distribuidora de Produtos Quimicos Ltda</t>
+          <t>Vpr Consultoria, Eventos, Servicos e Treinamentos Ltda</t>
         </is>
       </c>
       <c r="W30" s="5" t="inlineStr">
@@ -6149,11 +6149,11 @@
       </c>
       <c r="X30" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>2244227635</v>
+        <v>2142913055</v>
       </c>
       <c r="Z30" s="5" t="inlineStr">
         <is>
@@ -6166,16 +6166,16 @@
         </is>
       </c>
       <c r="AB30" s="5" t="n">
-        <v>845.4400000000001</v>
+        <v>1519.9</v>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>111.54</v>
+        <v>59.95</v>
       </c>
       <c r="AD30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE30" s="5" t="n">
-        <v>74.54000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF30" s="5" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="AH30" s="5" t="n">
-        <v>49.2</v>
+        <v>15.2</v>
       </c>
       <c r="AI30" s="5" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AJ30" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
         </is>
       </c>
       <c r="AK30" s="5" t="inlineStr">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>22678683</v>
+        <v>22702557</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>23483247</v>
+        <v>23504693</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>45873.52908564815</v>
+        <v>45876.75149305556</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45873.52951388889</v>
+        <v>45876.75265046296</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>QQDYYX</t>
+          <t>LN5PJQ</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>NARCISO TAVARES/GILBERTO</t>
+          <t>PROENÇA/JOSE</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="M31" s="6" t="n">
-        <v>45873.31944444445</v>
+        <v>45876.24027777778</v>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="V31" s="5" t="inlineStr">
         <is>
-          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
         </is>
       </c>
       <c r="W31" s="5" t="inlineStr">
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>649805726</v>
+        <v>771850144</v>
       </c>
       <c r="Z31" s="5" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="AB31" s="5" t="n">
-        <v>1889.84</v>
+        <v>803.17</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>95.02</v>
+        <v>48.16</v>
       </c>
       <c r="AD31" s="5" t="n">
         <v>0</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="AH31" s="5" t="n">
-        <v>245.68</v>
+        <v>78.38</v>
       </c>
       <c r="AI31" s="5" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AJ31" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK31" s="5" t="inlineStr">
@@ -6425,10 +6425,10 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>22678767</v>
+        <v>22702290</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>23483320</v>
+        <v>23504426</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>45873.53740740741</v>
+        <v>45876.71539351852</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45873.53815972222</v>
+        <v>45876.72435185185</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>LA9578331IVVO</t>
+          <t>TE2DPR</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Henrique Bonfim Aguero/Caio</t>
+          <t>Ferrari/Vinicius</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>45873.31527777778</v>
+        <v>45876.04305555556</v>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="V32" s="5" t="inlineStr">
         <is>
-          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
+          <t>Neurox</t>
         </is>
       </c>
       <c r="W32" s="5" t="inlineStr">
@@ -6531,11 +6531,11 @@
       </c>
       <c r="X32" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y32" s="5" t="n">
-        <v>2244207216</v>
+        <v>793480309</v>
       </c>
       <c r="Z32" s="5" t="inlineStr">
         <is>
@@ -6548,16 +6548,16 @@
         </is>
       </c>
       <c r="AB32" s="5" t="n">
-        <v>1372.72</v>
+        <v>2550.51</v>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>48.16</v>
+        <v>60.62</v>
       </c>
       <c r="AD32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE32" s="5" t="n">
-        <v>137.27</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="5" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="AH32" s="5" t="n">
-        <v>90.59999999999999</v>
+        <v>255.05</v>
       </c>
       <c r="AI32" s="5" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AJ32" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK32" s="5" t="inlineStr">
@@ -6616,10 +6616,10 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>22678751</v>
+        <v>22702180</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>23483305</v>
+        <v>23504319</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>45873.53327546296</v>
+        <v>45876.70707175926</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>45873.53391203703</v>
+        <v>45876.70912037037</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>XWZ7SD</t>
+          <t>NQUL5E</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>do Nascimento Ribeiro/Sávio</t>
+          <t>de Aguiar Ribeiro/Gustavo</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>45873.31111111111</v>
+        <v>45876.09097222222</v>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="V33" s="5" t="inlineStr">
         <is>
-          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
+          <t>Tributo Devido Contabilidade e Assessoria Tributaria Ltda</t>
         </is>
       </c>
       <c r="W33" s="5" t="inlineStr">
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>598172318</v>
+        <v>663202476</v>
       </c>
       <c r="Z33" s="5" t="inlineStr">
         <is>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="AB33" s="5" t="n">
-        <v>1661.97</v>
+        <v>1360.78</v>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>90.98999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="AD33" s="5" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AH33" s="5" t="n">
-        <v>432.11</v>
+        <v>489.88</v>
       </c>
       <c r="AI33" s="5" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="AJ33" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK33" s="5" t="inlineStr">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>22678751</v>
+        <v>22702180</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>23483306</v>
+        <v>23504320</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>45873.53327546296</v>
+        <v>45876.70707175926</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>45873.53391203703</v>
+        <v>45876.70912037037</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>XWZ7SD</t>
+          <t>NQUL5E</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>de Souza Coelho/Felipe</t>
+          <t>BRANDÃO MAURICIO/Renata</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="M34" s="6" t="n">
-        <v>45873.31111111111</v>
+        <v>45876.09097222222</v>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="V34" s="5" t="inlineStr">
         <is>
-          <t>Agueiro Inox Montagens e Manutencao Industrial Ltda</t>
+          <t>Tributo Devido Contabilidade e Assessoria Tributaria Ltda</t>
         </is>
       </c>
       <c r="W34" s="5" t="inlineStr">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="Y34" s="5" t="n">
-        <v>289916362</v>
+        <v>392102362</v>
       </c>
       <c r="Z34" s="5" t="inlineStr">
         <is>
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="AB34" s="5" t="n">
-        <v>1661.97</v>
+        <v>1360.78</v>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>90.98999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="AD34" s="5" t="n">
         <v>0</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AJ34" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 04/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK34" s="5" t="inlineStr">
@@ -6998,21 +6998,21 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>22679406</v>
+        <v>22702180</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>23483900</v>
+        <v>23504321</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC03</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>45873.64061342592</v>
+        <v>45876.70707175926</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>45873.64673611111</v>
+        <v>45876.70912037037</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -7026,31 +7026,31 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>GZLCXT</t>
+          <t>NQUL5E</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>DANIELLE SILBERGLEID</t>
+          <t>Gustavo Mauricio Ribeiro/Luiz</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Juliana Cardoso</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Juliana Cardoso</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M35" s="6" t="n">
-        <v>45873.64027777778</v>
+        <v>45876.09097222222</v>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S35" s="5" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="V35" s="5" t="inlineStr">
         <is>
-          <t>Opportunity Gestora</t>
+          <t>Tributo Devido Contabilidade e Assessoria Tributaria Ltda</t>
         </is>
       </c>
       <c r="W35" s="5" t="inlineStr">
@@ -7104,11 +7104,11 @@
       </c>
       <c r="X35" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y35" s="5" t="n">
-        <v>2142657530</v>
+        <v>877397275</v>
       </c>
       <c r="Z35" s="5" t="inlineStr">
         <is>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="AB35" s="5" t="n">
-        <v>730.8</v>
+        <v>1360.78</v>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>33.56</v>
+        <v>82.86</v>
       </c>
       <c r="AD35" s="5" t="n">
         <v>0</v>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="AI35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ35" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
         </is>
       </c>
       <c r="AK35" s="5" t="inlineStr">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="AL35" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM35" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN35" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO35" s="5" t="inlineStr">
@@ -7189,10 +7189,10 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>22677911</v>
+        <v>22701858</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>23482505</v>
+        <v>23504017</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>45873.49025462963</v>
+        <v>45876.67097222222</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>45873.49657407407</v>
+        <v>45876.67528935185</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>VJCPHP</t>
+          <t>LA9579834VCKM</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Andressa Vallini/Nathalie</t>
+          <t>TAIRA/PAULA</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>45873.47986111111</v>
+        <v>45876.13055555556</v>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="R36" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S36" s="5" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="U36" s="5" t="inlineStr">
         <is>
-          <t>Independente</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V36" s="5" t="inlineStr">
         <is>
-          <t>Ideia 3</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W36" s="5" t="inlineStr">
@@ -7295,84 +7295,3140 @@
       </c>
       <c r="X36" s="5" t="inlineStr">
         <is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>2244717121</v>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="n">
+        <v>1150.24</v>
+      </c>
+      <c r="AC36" s="5" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="AD36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="5" t="n">
+        <v>115.02</v>
+      </c>
+      <c r="AF36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="5" t="n">
+        <v>227.75</v>
+      </c>
+      <c r="AI36" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ36" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK36" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL36" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM36" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN36" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO36" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP36" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ36" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>22701858</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>23504018</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>ACC02</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>45876.67097222222</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>45876.67528935185</v>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>LA9579834VCKM</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>LI PUMA JUNIOR/MICHELE</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="n">
+        <v>45876.13055555556</v>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q37" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R37" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S37" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V37" s="5" t="inlineStr">
+        <is>
+          <t>Pailon Comunicacao Visual Ltda</t>
+        </is>
+      </c>
+      <c r="W37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X37" s="5" t="inlineStr">
+        <is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>2244717122</v>
+      </c>
+      <c r="Z37" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB37" s="5" t="n">
+        <v>1150.24</v>
+      </c>
+      <c r="AC37" s="5" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="AD37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="5" t="n">
+        <v>115.02</v>
+      </c>
+      <c r="AF37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ37" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK37" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL37" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM37" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN37" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO37" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP37" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ37" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>22701858</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>23504019</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>ACC03</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>45876.67097222222</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>45876.67528935185</v>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>LA9579834VCKM</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>SANTOS/MARIANA</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="n">
+        <v>45876.13055555556</v>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q38" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R38" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U38" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>Pailon Comunicacao Visual Ltda</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X38" s="5" t="inlineStr">
+        <is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <v>2244717123</v>
+      </c>
+      <c r="Z38" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB38" s="5" t="n">
+        <v>1150.24</v>
+      </c>
+      <c r="AC38" s="5" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="AD38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="5" t="n">
+        <v>115.02</v>
+      </c>
+      <c r="AF38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ38" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK38" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL38" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM38" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN38" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO38" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP38" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ38" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>22701923</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>23504074</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>45876.67809027778</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>45876.67987268518</v>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>ZIUBHS</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>NOGUEIRA MARINI/FABRIZIO</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="n">
+        <v>45876.42222222222</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>Fundamentos Sistemas</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X39" s="5" t="inlineStr">
+        <is>
           <t>Azul Linhas Aereas</t>
         </is>
       </c>
-      <c r="Y36" s="5" t="n">
-        <v>219715631</v>
-      </c>
-      <c r="Z36" s="5" t="inlineStr">
+      <c r="Y39" s="5" t="n">
+        <v>625487084</v>
+      </c>
+      <c r="Z39" s="5" t="inlineStr">
         <is>
           <t>KONTRIP</t>
         </is>
       </c>
-      <c r="AA36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB36" s="5" t="n">
-        <v>981.01</v>
-      </c>
-      <c r="AC36" s="5" t="n">
-        <v>69.54000000000001</v>
-      </c>
-      <c r="AD36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="AI36" s="5" t="inlineStr">
+      <c r="AA39" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB39" s="5" t="n">
+        <v>1634.84</v>
+      </c>
+      <c r="AC39" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AD39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="5" t="n">
+        <v>163.48</v>
+      </c>
+      <c r="AI39" s="5" t="inlineStr">
         <is>
           <t>obs</t>
         </is>
       </c>
-      <c r="AJ36" s="5" t="inlineStr">
-        <is>
-          <t>Centro de custo não preenchido! (ACC01) Solicitante não preenchido! (ACC01)</t>
-        </is>
-      </c>
-      <c r="AK36" s="5" t="inlineStr">
+      <c r="AJ39" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK39" s="5" t="inlineStr">
         <is>
           <t>KONTRIP</t>
         </is>
       </c>
-      <c r="AL36" s="5" t="inlineStr">
-        <is>
-          <t>Mais de um campo não preenchido</t>
-        </is>
-      </c>
-      <c r="AM36" s="5" t="inlineStr">
+      <c r="AL39" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM39" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN39" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO39" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP39" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ39" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>22701963</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>23504109</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>45876.68231481482</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>45876.68407407407</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>ONT1UQ</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>SILVEIRA/VINICIUS</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="n">
+        <v>45875.24791666667</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="inlineStr">
+        <is>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+        </is>
+      </c>
+      <c r="W40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X40" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <v>433154923</v>
+      </c>
+      <c r="Z40" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA40" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+        </is>
+      </c>
+      <c r="AK40" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL40" s="5" t="inlineStr">
+        <is>
+          <t>Forma de Pagamento indevida</t>
+        </is>
+      </c>
+      <c r="AM40" s="5" t="inlineStr">
+        <is>
+          <t>Forma PG. e REC.</t>
+        </is>
+      </c>
+      <c r="AN40" s="5" t="inlineStr">
+        <is>
+          <t>Dados do Fornecedor</t>
+        </is>
+      </c>
+      <c r="AO40" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP40" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ40" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>22701963</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>23504110</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>ACC02</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>45876.68231481482</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>45876.68407407407</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>ONT1UQ</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>MARQUES/JONNATA</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>45875.24791666667</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="inlineStr">
+        <is>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+        </is>
+      </c>
+      <c r="W41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X41" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>530336503</v>
+      </c>
+      <c r="Z41" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA41" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+        </is>
+      </c>
+      <c r="AK41" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL41" s="5" t="inlineStr">
+        <is>
+          <t>Forma de Pagamento indevida</t>
+        </is>
+      </c>
+      <c r="AM41" s="5" t="inlineStr">
+        <is>
+          <t>Forma PG. e REC.</t>
+        </is>
+      </c>
+      <c r="AN41" s="5" t="inlineStr">
+        <is>
+          <t>Dados do Fornecedor</t>
+        </is>
+      </c>
+      <c r="AO41" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP41" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ41" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>22701963</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>23504111</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>ACC03</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>45876.68231481482</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>45876.68407407407</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>ONT1UQ</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>SILVA/SUELLEN</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>45875.24791666667</v>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R42" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T42" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U42" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V42" s="5" t="inlineStr">
+        <is>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+        </is>
+      </c>
+      <c r="W42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X42" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y42" s="5" t="n">
+        <v>881669034</v>
+      </c>
+      <c r="Z42" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA42" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+        </is>
+      </c>
+      <c r="AK42" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL42" s="5" t="inlineStr">
+        <is>
+          <t>Forma de Pagamento indevida</t>
+        </is>
+      </c>
+      <c r="AM42" s="5" t="inlineStr">
+        <is>
+          <t>Forma PG. e REC.</t>
+        </is>
+      </c>
+      <c r="AN42" s="5" t="inlineStr">
+        <is>
+          <t>Dados do Fornecedor</t>
+        </is>
+      </c>
+      <c r="AO42" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP42" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ42" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>22701963</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>23504112</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>ACC04</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>45876.68231481482</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>45876.68407407407</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>ONT1UQ</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>SANTOS/MARIA</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>45875.24791666667</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="inlineStr">
+        <is>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+        </is>
+      </c>
+      <c r="W43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X43" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>655926091</v>
+      </c>
+      <c r="Z43" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA43" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+        </is>
+      </c>
+      <c r="AK43" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL43" s="5" t="inlineStr">
+        <is>
+          <t>Forma de Pagamento indevida</t>
+        </is>
+      </c>
+      <c r="AM43" s="5" t="inlineStr">
+        <is>
+          <t>Forma PG. e REC.</t>
+        </is>
+      </c>
+      <c r="AN43" s="5" t="inlineStr">
+        <is>
+          <t>Dados do Fornecedor</t>
+        </is>
+      </c>
+      <c r="AO43" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP43" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ43" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>22701964</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>23504113</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>45876.68236111111</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>45876.68616898148</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>WRYNTH</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Barros da Costa/Marília</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>45876.07430555556</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="inlineStr">
+        <is>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+        </is>
+      </c>
+      <c r="W44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X44" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y44" s="5" t="n">
+        <v>125955518</v>
+      </c>
+      <c r="Z44" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB44" s="5" t="n">
+        <v>947.09</v>
+      </c>
+      <c r="AC44" s="5" t="n">
+        <v>92.53</v>
+      </c>
+      <c r="AD44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="5" t="n">
+        <v>123.12</v>
+      </c>
+      <c r="AI44" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+        </is>
+      </c>
+      <c r="AK44" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL44" s="5" t="inlineStr">
+        <is>
+          <t>Forma de Pagamento indevida</t>
+        </is>
+      </c>
+      <c r="AM44" s="5" t="inlineStr">
+        <is>
+          <t>Forma PG. e REC.</t>
+        </is>
+      </c>
+      <c r="AN44" s="5" t="inlineStr">
+        <is>
+          <t>Dados do Fornecedor</t>
+        </is>
+      </c>
+      <c r="AO44" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP44" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ44" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>22701979</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>23504123</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>45876.68474537037</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>45876.68616898148</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>JIYUSM</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>VICENTE DA SILVA/ELIZABETE</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>45876.18402777778</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T45" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U45" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V45" s="5" t="inlineStr">
+        <is>
+          <t>Nayane</t>
+        </is>
+      </c>
+      <c r="W45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X45" s="5" t="inlineStr">
+        <is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y45" s="5" t="n">
+        <v>2244704749</v>
+      </c>
+      <c r="Z45" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB45" s="5" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="AC45" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="AD45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI45" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ45" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK45" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL45" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM45" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN45" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO45" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP45" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ45" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>22701594</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>23503746</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>45876.63767361111</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>45876.6442824074</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>LA9574257CKOF</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Guerreiro Mason/Ricardo</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>45876.05694444444</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="inlineStr">
+        <is>
+          <t>Fortymil Industria de Plasticos Ltda</t>
+        </is>
+      </c>
+      <c r="W46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X46" s="5" t="inlineStr">
+        <is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y46" s="5" t="n">
+        <v>2244707942</v>
+      </c>
+      <c r="Z46" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB46" s="5" t="n">
+        <v>577.4400000000001</v>
+      </c>
+      <c r="AC46" s="5" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="AD46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="5" t="n">
+        <v>57.74</v>
+      </c>
+      <c r="AF46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="5" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AI46" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ46" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK46" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL46" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM46" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN46" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO46" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP46" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ46" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>22701432</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>23503600</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>45876.60962962963</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>45876.61112268519</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>LA9578799IXZM</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>EBOOKING</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Castelo Branco Mesquita/Ilanna</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>45876.50486111111</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="inlineStr">
+        <is>
+          <t>Cartão de crédito</t>
+        </is>
+      </c>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="inlineStr">
+        <is>
+          <t>Certare Engenharia e Consultoria</t>
+        </is>
+      </c>
+      <c r="W47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X47" s="5" t="inlineStr">
+        <is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>2244701000</v>
+      </c>
+      <c r="Z47" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB47" s="5" t="n">
+        <v>823.84</v>
+      </c>
+      <c r="AC47" s="5" t="n">
+        <v>101.01</v>
+      </c>
+      <c r="AD47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="5" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="AF47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="5" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="AI47" s="5" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
+      <c r="AJ47" s="5" t="inlineStr">
+        <is>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+        </is>
+      </c>
+      <c r="AK47" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL47" s="5" t="inlineStr">
+        <is>
+          <t>Não identificado</t>
+        </is>
+      </c>
+      <c r="AM47" s="5" t="inlineStr">
+        <is>
+          <t>Análise Benner</t>
+        </is>
+      </c>
+      <c r="AN47" s="5" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="AO47" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP47" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ47" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>22702374</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>23504524</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>ACC01</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>45876.72446759259</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>45876.7305787037</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>AEQMHY</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>FERNANDO LEITE</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>45875.72430555556</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="inlineStr">
+        <is>
+          <t>Cartão convênio</t>
+        </is>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip - Vendas Cartao de Credito</t>
+        </is>
+      </c>
+      <c r="W48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X48" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y48" s="5" t="n">
+        <v>3023504523</v>
+      </c>
+      <c r="Z48" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB48" s="5" t="n">
+        <v>665.84</v>
+      </c>
+      <c r="AC48" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AD48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="5" t="n">
+        <v>332.92</v>
+      </c>
+      <c r="AI48" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ48" s="5" t="inlineStr">
+        <is>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+        </is>
+      </c>
+      <c r="AK48" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL48" s="5" t="inlineStr">
         <is>
           <t>Falta de informação Gerencial</t>
         </is>
       </c>
-      <c r="AN36" s="5" t="inlineStr">
-        <is>
-          <t>Dados do Fornecedor</t>
-        </is>
-      </c>
-      <c r="AO36" s="5" t="inlineStr">
+      <c r="AM48" s="5" t="inlineStr">
+        <is>
+          <t>Rateio de centro de custo/projeto</t>
+        </is>
+      </c>
+      <c r="AN48" s="5" t="inlineStr">
+        <is>
+          <t>Dados Gerenciais</t>
+        </is>
+      </c>
+      <c r="AO48" s="5" t="inlineStr">
         <is>
           <t>Qualidade dos dados</t>
         </is>
       </c>
-      <c r="AP36" s="5" t="inlineStr">
+      <c r="AP48" s="5" t="inlineStr">
         <is>
           <t>KONTRIP VIAGENS</t>
         </is>
       </c>
-      <c r="AQ36" s="5" t="inlineStr">
+      <c r="AQ48" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>22702374</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>23504547</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>ACC02</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>45876.72446759259</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>45876.7305787037</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>AEQMHY</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>GILSON SILVA</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>45875.72430555556</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="inlineStr">
+        <is>
+          <t>Cartão convênio</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip - Vendas Cartao de Credito</t>
+        </is>
+      </c>
+      <c r="W49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X49" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y49" s="5" t="n">
+        <v>3023504548</v>
+      </c>
+      <c r="Z49" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB49" s="5" t="n">
+        <v>665.84</v>
+      </c>
+      <c r="AC49" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AD49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ49" s="5" t="inlineStr">
+        <is>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+        </is>
+      </c>
+      <c r="AK49" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL49" s="5" t="inlineStr">
+        <is>
+          <t>Falta de informação Gerencial</t>
+        </is>
+      </c>
+      <c r="AM49" s="5" t="inlineStr">
+        <is>
+          <t>Rateio de centro de custo/projeto</t>
+        </is>
+      </c>
+      <c r="AN49" s="5" t="inlineStr">
+        <is>
+          <t>Dados Gerenciais</t>
+        </is>
+      </c>
+      <c r="AO49" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP49" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ49" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>22702374</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>23504550</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>ACC03</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>45876.72446759259</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>45876.7305787037</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>AEQMHY</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>FLAVIO SANTIAGO RAMOS</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>45875.72430555556</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>Cartão convênio</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip - Vendas Cartao de Credito</t>
+        </is>
+      </c>
+      <c r="W50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X50" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y50" s="5" t="n">
+        <v>3023504555</v>
+      </c>
+      <c r="Z50" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB50" s="5" t="n">
+        <v>665.84</v>
+      </c>
+      <c r="AC50" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AD50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ50" s="5" t="inlineStr">
+        <is>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+        </is>
+      </c>
+      <c r="AK50" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL50" s="5" t="inlineStr">
+        <is>
+          <t>Falta de informação Gerencial</t>
+        </is>
+      </c>
+      <c r="AM50" s="5" t="inlineStr">
+        <is>
+          <t>Rateio de centro de custo/projeto</t>
+        </is>
+      </c>
+      <c r="AN50" s="5" t="inlineStr">
+        <is>
+          <t>Dados Gerenciais</t>
+        </is>
+      </c>
+      <c r="AO50" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP50" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ50" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>22702374</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>23504552</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>ACC04</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>45876.72446759259</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>45876.7305787037</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>AEQMHY</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>GABRIEL ARMOND DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>45875.72430555556</v>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="inlineStr">
+        <is>
+          <t>Cartão convênio</t>
+        </is>
+      </c>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip - Vendas Cartao de Credito</t>
+        </is>
+      </c>
+      <c r="W51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X51" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y51" s="5" t="n">
+        <v>3023504557</v>
+      </c>
+      <c r="Z51" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB51" s="5" t="n">
+        <v>665.84</v>
+      </c>
+      <c r="AC51" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AD51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ51" s="5" t="inlineStr">
+        <is>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+        </is>
+      </c>
+      <c r="AK51" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL51" s="5" t="inlineStr">
+        <is>
+          <t>Falta de informação Gerencial</t>
+        </is>
+      </c>
+      <c r="AM51" s="5" t="inlineStr">
+        <is>
+          <t>Rateio de centro de custo/projeto</t>
+        </is>
+      </c>
+      <c r="AN51" s="5" t="inlineStr">
+        <is>
+          <t>Dados Gerenciais</t>
+        </is>
+      </c>
+      <c r="AO51" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP51" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ51" s="5" t="inlineStr">
+        <is>
+          <t>Operações - KONTRIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>22702374</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>23504554</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>ACC05</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>45876.72446759259</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>45876.7305787037</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>0 a 02 dias</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>AEQMHY</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>MANUAL</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>JOSE LUIS BRITO DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>Juliana Cardoso</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>45875.72430555556</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>OFF LINE</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t>Cartão convênio</t>
+        </is>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>Aéreo</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>Grupo Kontrip</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="inlineStr">
+        <is>
+          <t>Kontrip - Vendas Cartao de Credito</t>
+        </is>
+      </c>
+      <c r="W52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X52" s="5" t="inlineStr">
+        <is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>3023504558</v>
+      </c>
+      <c r="Z52" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AA52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB52" s="5" t="n">
+        <v>665.84</v>
+      </c>
+      <c r="AC52" s="5" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AD52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ52" s="5" t="inlineStr">
+        <is>
+          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+        </is>
+      </c>
+      <c r="AK52" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP</t>
+        </is>
+      </c>
+      <c r="AL52" s="5" t="inlineStr">
+        <is>
+          <t>Falta de informação Gerencial</t>
+        </is>
+      </c>
+      <c r="AM52" s="5" t="inlineStr">
+        <is>
+          <t>Rateio de centro de custo/projeto</t>
+        </is>
+      </c>
+      <c r="AN52" s="5" t="inlineStr">
+        <is>
+          <t>Dados Gerenciais</t>
+        </is>
+      </c>
+      <c r="AO52" s="5" t="inlineStr">
+        <is>
+          <t>Qualidade dos dados</t>
+        </is>
+      </c>
+      <c r="AP52" s="5" t="inlineStr">
+        <is>
+          <t>KONTRIP VIAGENS</t>
+        </is>
+      </c>
+      <c r="AQ52" s="5" t="inlineStr">
         <is>
           <t>Operações - KONTRIP</t>
         </is>

--- a/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
+++ b/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ52"/>
+  <dimension ref="A1:AQ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,10 +695,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>22701489</v>
+        <v>22732183</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>23503652</v>
+        <v>23529631</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>45876.61974537037</v>
+        <v>45881.77253472222</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>45876.62252314815</v>
+        <v>45881.77359953704</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>LA9575542VFFO</t>
+          <t>LA9579436TNIH</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Hiroyama/Rodrigo</t>
+          <t>Kamnitzer/Bernardo</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>45876.54027777778</v>
+        <v>45881.2375</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="U2" s="5" t="inlineStr">
         <is>
-          <t>Independente</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>Tap Air Portugal</t>
+          <t>Orange 2006 Comunicacao Digital Ltda</t>
         </is>
       </c>
       <c r="W2" s="5" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>2244704214</v>
+        <v>2245553084</v>
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>399.8</v>
+        <v>618.3200000000001</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>67.75</v>
+        <v>60.62</v>
       </c>
       <c r="AD2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE2" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="5" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>26.39</v>
+        <v>40.81</v>
       </c>
       <c r="AI2" s="5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK2" s="5" t="inlineStr">
@@ -886,10 +886,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>22701526</v>
+        <v>22732394</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23503679</v>
+        <v>23529831</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45876.62355324074</v>
+        <v>45881.78053240741</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>45876.62640046296</v>
+        <v>45881.78189814815</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>YINS5C</t>
+          <t>YOSDCQ</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Boelter/Joel</t>
+          <t>POLTRONIERI/MARCELLO</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>45876.52847222222</v>
+        <v>45881.27986111111</v>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>Felice Automoveis Ltda</t>
+          <t>Cinesystem S.a.</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
@@ -992,11 +992,11 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>721127445</v>
+        <v>2143317777</v>
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>2030.81</v>
+        <v>2447.73</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>116.64</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="5" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>203.08</v>
+        <v>80</v>
       </c>
       <c r="AI3" s="5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AJ3" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK3" s="5" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="AL3" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM3" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN3" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO3" s="5" t="inlineStr">
@@ -1077,21 +1077,21 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>22704257</v>
+        <v>22732394</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>23506291</v>
+        <v>23529832</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45876.85268518519</v>
+        <v>45881.78053240741</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>45876.85496527778</v>
+        <v>45881.78189814815</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>SP4F5K</t>
+          <t>YOSDCQ</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>SANTOS/SUELLEN</t>
+          <t>FALCÃO DA SILVA/TAMIRIS</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>45876.22638888889</v>
+        <v>45881.27986111111</v>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>M3. Business Group Ltda</t>
+          <t>Cinesystem S.a.</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>259866459</v>
+        <v>2143317787</v>
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>2272.06</v>
+        <v>2447.73</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>101.17</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>113.6</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AJ4" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK4" s="5" t="inlineStr">
@@ -1237,17 +1237,17 @@
       </c>
       <c r="AL4" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM4" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN4" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO4" s="5" t="inlineStr">
@@ -1268,10 +1268,10 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>22704264</v>
+        <v>22731936</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>23506303</v>
+        <v>23529387</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45876.8544212963</v>
+        <v>45881.76438657408</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>45876.85671296297</v>
+        <v>45881.76513888889</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>VMYRHG</t>
+          <t>VHF26F</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>VALENTE/KEILA</t>
+          <t>PAULINO DA SILVA/MARCOS</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>45876.23958333334</v>
+        <v>45881.12013888889</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>M3. Business Group Ltda</t>
+          <t>Pailon Comunicacao Visual Ltda</t>
         </is>
       </c>
       <c r="W5" s="5" t="inlineStr">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>384657625</v>
+        <v>362621474</v>
       </c>
       <c r="Z5" s="5" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>2272.06</v>
+        <v>1869.67</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>101.17</v>
+        <v>48.16</v>
       </c>
       <c r="AD5" s="5" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>113.6</v>
+        <v>224.36</v>
       </c>
       <c r="AI5" s="5" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AJ5" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK5" s="5" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>22704266</v>
+        <v>22732927</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>23506306</v>
+        <v>23530344</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45876.85545138889</v>
+        <v>45881.82221064815</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>45876.85675925926</v>
+        <v>45881.82354166666</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>LLL72T</t>
+          <t>LA9578248RPER</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>OLIVEIRA/ADRIANA</t>
+          <t>GUERRA/BRUNO</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>45876.24583333333</v>
+        <v>45881.25277777778</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>M3. Business Group Ltda</t>
+          <t>Inteligencia de Negocios Sistemas e Informatica Ltda</t>
         </is>
       </c>
       <c r="W6" s="5" t="inlineStr">
@@ -1565,11 +1565,11 @@
       </c>
       <c r="X6" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>968746609</v>
+        <v>2245572251</v>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>2272.06</v>
+        <v>2206.15</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>101.17</v>
+        <v>245.88</v>
       </c>
       <c r="AD6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>0</v>
+        <v>154.43</v>
       </c>
       <c r="AF6" s="5" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>113.6</v>
+        <v>141.63</v>
       </c>
       <c r="AI6" s="5" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AJ6" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK6" s="5" t="inlineStr">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>22704366</v>
+        <v>22733023</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>23506390</v>
+        <v>23530418</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>45876.87491898148</v>
+        <v>45881.86106481482</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45876.87604166667</v>
+        <v>45881.86311342593</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>YPRQYN</t>
+          <t>MODVSL</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Borba/Felipe</t>
+          <t>Luiza Lima dos Santos/Bruna</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>45876.37291666667</v>
+        <v>45881.35694444444</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Galera Gaming Jogos Eletronicos</t>
+          <t>Rcs Tecnologia S/a</t>
         </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
@@ -1756,11 +1756,11 @@
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>553122361</v>
+        <v>2245581911</v>
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>824.25</v>
+        <v>1141.2</v>
       </c>
       <c r="AC7" s="5" t="n">
         <v>0</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AJ7" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK7" s="5" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>22703064</v>
+        <v>22651101</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>23505173</v>
+        <v>23460675</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -1852,24 +1852,24 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45876.76805555556</v>
+        <v>45868.52986111111</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>45876.76949074074</v>
+        <v>45869.4131712963</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>09 a 15 dias</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>09 a 15 dias</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>BPP6HH</t>
+          <t>MQU7YH01</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Alexandre Frosini Evangelista/Carlos</t>
+          <t>GONÇALVES/GUSTAVO</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>45876.26736111111</v>
+        <v>45867.26875</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>?</t>
         </is>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>?</t>
         </is>
       </c>
       <c r="S8" s="5" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>Associacao Brasileira de Geracao Distribuida - Abgd</t>
+          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
         </is>
       </c>
       <c r="W8" s="5" t="inlineStr">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>530146970</v>
+        <v>980419988</v>
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>1435.99</v>
+        <v>713.2</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>450</v>
+        <v>36.67</v>
       </c>
       <c r="AD8" s="5" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>40</v>
+        <v>92.72</v>
       </c>
       <c r="AI8" s="5" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AJ8" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
         </is>
       </c>
       <c r="AK8" s="5" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="AL8" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Forma de Pagamento indevida</t>
         </is>
       </c>
       <c r="AM8" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Forma PG. e REC.</t>
         </is>
       </c>
       <c r="AN8" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO8" s="5" t="inlineStr">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>22703095</v>
+        <v>22686963</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>23505205</v>
+        <v>23490647</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -2043,24 +2043,24 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>45876.76944444444</v>
+        <v>45874.65428240741</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>45876.77215277778</v>
+        <v>45875.7694675926</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>KQRSAC</t>
+          <t>YOVNRQ</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Sampaio/Bergsan</t>
+          <t>ALMEIDA/LUIZ</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>45876.24097222222</v>
+        <v>45874.15208333333</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S9" s="5" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U9" s="5" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>Ntsec - Network Security</t>
+          <t>Araforros Ind e Comercio de Perfilados Ltda Em Recuperacao Judicial</t>
         </is>
       </c>
       <c r="W9" s="5" t="inlineStr">
@@ -2138,11 +2138,11 @@
       </c>
       <c r="X9" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>2142916171</v>
+        <v>3023498529</v>
       </c>
       <c r="Z9" s="5" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AB9" s="5" t="n">
-        <v>1450.44</v>
+        <v>0.01</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>36.67</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>145.04</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="5" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>111.68</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AJ9" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Validação do documento: Valor dever ser maior que zero !</t>
         </is>
       </c>
       <c r="AK9" s="5" t="inlineStr">
@@ -2223,10 +2223,10 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>22703175</v>
+        <v>22692401</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>23505287</v>
+        <v>23495383</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -2234,34 +2234,34 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45876.77498842592</v>
+        <v>45875.45380787037</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>45876.77726851852</v>
+        <v>45875.45554398148</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>IRPIKD</t>
+          <t>NRFVAS</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>EBOOKING</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Sampaio/Bergsan</t>
+          <t>Cardoso/Felipe</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>45876.23819444444</v>
+        <v>45869.04861111111</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="T10" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>Ntsec - Network Security</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2329,11 +2329,11 @@
       </c>
       <c r="X10" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>2142916962</v>
+        <v>2243683469</v>
       </c>
       <c r="Z10" s="5" t="inlineStr">
         <is>
@@ -2346,16 +2346,16 @@
         </is>
       </c>
       <c r="AB10" s="5" t="n">
-        <v>1698.87</v>
+        <v>590.3200000000001</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>51.07</v>
+        <v>30.95</v>
       </c>
       <c r="AD10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>169.88</v>
+        <v>59.03</v>
       </c>
       <c r="AF10" s="5" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="AH10" s="5" t="n">
-        <v>130.81</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="5" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>obsCancelamento VOID do pax FELIPE CARDOSO</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Verificação de bilhetes: Bilhete 2243683469 já sendo utilizado para este fornecedor.</t>
         </is>
       </c>
       <c r="AK10" s="5" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="AL10" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Bilhete duplicado</t>
         </is>
       </c>
       <c r="AM10" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Bilhete Já Contabilizado</t>
         </is>
       </c>
       <c r="AN10" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO10" s="5" t="inlineStr">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>22686963</v>
+        <v>22693812</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23490647</v>
+        <v>23496718</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -2425,24 +2425,24 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>45874.65428240741</v>
+        <v>45875.57494212963</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>45875.7694675926</v>
+        <v>45875.57653935185</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>YOVNRQ</t>
+          <t>II9WRC</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>ALMEIDA/LUIZ</t>
+          <t>EMILIO BRANDAO DE ARAUJO/CARLOS</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>45874.15208333333</v>
+        <v>45875.07291666666</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S11" s="5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Araforros Ind e Comercio de Perfilados Ltda Em Recuperacao Judicial</t>
+          <t>Conorte Servicos Industriais Ltda</t>
         </is>
       </c>
       <c r="W11" s="5" t="inlineStr">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>3023498529</v>
+        <v>863078581</v>
       </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>0.01</v>
+        <v>548.92</v>
       </c>
       <c r="AC11" s="5" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI11" s="5" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AJ11" s="5" t="inlineStr">
         <is>
-          <t>Validação do documento: Valor dever ser maior que zero !</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK11" s="5" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="AL11" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM11" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN11" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO11" s="5" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>22692401</v>
+        <v>22700070</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>23495383</v>
+        <v>23502309</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -2807,34 +2807,34 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>45875.45380787037</v>
+        <v>45876.49452546296</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>45875.45554398148</v>
+        <v>45876.49780092593</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>NRFVAS</t>
+          <t>YM1U2G</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Cardoso/Felipe</t>
+          <t>ESTEVAO PERDIGAO DE MIRANDA/LUIZ</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>45869.04861111111</v>
+        <v>45876.49166666667</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U13" s="5" t="inlineStr">
@@ -2902,11 +2902,11 @@
       </c>
       <c r="X13" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>2243683469</v>
+        <v>743416547</v>
       </c>
       <c r="Z13" s="5" t="inlineStr">
         <is>
@@ -2919,16 +2919,16 @@
         </is>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>590.3200000000001</v>
+        <v>1147.84</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>30.95</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="AD13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>59.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="5" t="n">
         <v>0</v>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="AI13" s="5" t="inlineStr">
         <is>
-          <t>obsCancelamento VOID do pax FELIPE CARDOSO</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 2243683469 já sendo utilizado para este fornecedor.</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK13" s="5" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="AL13" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
@@ -2987,10 +2987,10 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>22700765</v>
+        <v>22700473</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23502981</v>
+        <v>23502703</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -2998,24 +2998,24 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>45876.5291087963</v>
+        <v>45876.51666666667</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>45876.53026620371</v>
+        <v>45876.51966435185</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>CME1UD</t>
+          <t>WAQULI</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>MARIO MOUTINHO/LUIZ</t>
+          <t>Santos Junior/Roberto</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>45876.52777777778</v>
+        <v>45876.51597222222</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Memora</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="X14" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>781870213</v>
+        <v>2244411354</v>
       </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="AB14" s="5" t="n">
-        <v>1893.59</v>
+        <v>1260</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>119.51</v>
+        <v>80.69</v>
       </c>
       <c r="AD14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE14" s="5" t="n">
-        <v>201.31</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="5" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="5" t="n">
-        <v>66.43000000000001</v>
+        <v>88.19</v>
       </c>
       <c r="AI14" s="5" t="inlineStr">
         <is>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>22700473</v>
+        <v>22700765</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>23502703</v>
+        <v>23502981</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -3189,24 +3189,24 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>45876.51666666667</v>
+        <v>45876.5291087963</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>45876.51966435185</v>
+        <v>45876.53026620371</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>WAQULI</t>
+          <t>CME1UD</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Santos Junior/Roberto</t>
+          <t>MARIO MOUTINHO/LUIZ</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>45876.51597222222</v>
+        <v>45876.52777777778</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>Memora</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W15" s="5" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="X15" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>2244411354</v>
+        <v>781870213</v>
       </c>
       <c r="Z15" s="5" t="inlineStr">
         <is>
@@ -3301,16 +3301,16 @@
         </is>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>1260</v>
+        <v>1893.59</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>80.69</v>
+        <v>119.51</v>
       </c>
       <c r="AD15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>0</v>
+        <v>201.31</v>
       </c>
       <c r="AF15" s="5" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>88.19</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="AI15" s="5" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>22700624</v>
+        <v>22730623</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>23502845</v>
+        <v>23528103</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>45876.52388888889</v>
+        <v>45881.64895833333</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>45876.52570601852</v>
+        <v>45881.65071759259</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>UHQOPY</t>
+          <t>FEORVQ</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Powell/Alexandre</t>
+          <t>CARVALHO/KAINAN</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>45876.52152777778</v>
+        <v>45881.14791666667</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -3440,12 +3440,12 @@
       </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S16" s="5" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>Powell Consultoria</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W16" s="5" t="inlineStr">
@@ -3475,11 +3475,11 @@
       </c>
       <c r="X16" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>2244375759</v>
+        <v>2143293256</v>
       </c>
       <c r="Z16" s="5" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>128.79</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="5" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="5" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AJ16" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 2244375759 já sendo utilizado para este fornecedor.</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK16" s="5" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="AL16" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM16" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN16" s="5" t="inlineStr">
@@ -3560,21 +3560,21 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>22700741</v>
+        <v>22730623</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>23502957</v>
+        <v>23528104</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>45876.52784722222</v>
+        <v>45881.64895833333</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>45876.52979166667</v>
+        <v>45881.65071759259</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>LA9579303WVLK</t>
+          <t>FEORVQ</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>KERTZMAN/IVAN</t>
+          <t>Lindolfo Gomes/Luana</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>45875.30763888889</v>
+        <v>45881.14791666667</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>Imadec</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W17" s="5" t="inlineStr">
@@ -3666,11 +3666,11 @@
       </c>
       <c r="X17" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>2244684148</v>
+        <v>2143293257</v>
       </c>
       <c r="Z17" s="5" t="inlineStr">
         <is>
@@ -3683,16 +3683,16 @@
         </is>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>600.72</v>
+        <v>0.01</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>43.65</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>60.07</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="5" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>39.65</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="5" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AJ17" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK17" s="5" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AL17" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM17" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN17" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO17" s="5" t="inlineStr">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>22696940</v>
+        <v>22730693</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>23499770</v>
+        <v>23528171</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45875.87490740741</v>
+        <v>45881.65868055556</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>45875.8759375</v>
+        <v>45881.6608912037</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>LA9578941SQLG</t>
+          <t>LA9570032FKAY</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Guilarte/Dayana</t>
+          <t>Eduardo Monteiro Miranda/José</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>45875.24027777778</v>
+        <v>45881.08263888889</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>Zubale Brasil Tecnologia Ltda.</t>
+          <t>Associacao Renova Br</t>
         </is>
       </c>
       <c r="W18" s="5" t="inlineStr">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>2244613800</v>
+        <v>2245525503</v>
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
@@ -3874,16 +3874,16 @@
         </is>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>1805.52</v>
+        <v>2235.84</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>60.62</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AD18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE18" s="5" t="n">
-        <v>180.55</v>
+        <v>223.58</v>
       </c>
       <c r="AF18" s="5" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>119.16</v>
+        <v>147.57</v>
       </c>
       <c r="AI18" s="5" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AJ18" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK18" s="5" t="inlineStr">
@@ -3942,10 +3942,10 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>22696941</v>
+        <v>22730737</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>23499771</v>
+        <v>23528229</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>45875.87491898148</v>
+        <v>45881.66708333333</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>45875.8771875</v>
+        <v>45881.67012731481</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>LA9578787ETLE</t>
+          <t>YI8EMF</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Elizabeth Guilarte/Dayana</t>
+          <t>RODRIGUES NETO/VASCO</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>45875.24027777778</v>
+        <v>45881.16527777778</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>Zubale Brasil Tecnologia Ltda.</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W19" s="5" t="inlineStr">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>2244613732</v>
+        <v>217902719</v>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>2083.12</v>
+        <v>1837.64</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>52.56</v>
+        <v>120.57</v>
       </c>
       <c r="AD19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>208.31</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="5" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>137.49</v>
+        <v>39.64</v>
       </c>
       <c r="AI19" s="5" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AJ19" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK19" s="5" t="inlineStr">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>22699617</v>
+        <v>22729862</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23501892</v>
+        <v>23527394</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>45876.43893518519</v>
+        <v>45881.53208333333</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>45876.44039351852</v>
+        <v>45881.5340625</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>XNK8WT</t>
+          <t>AQLNTC</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>SILVA/ABEL</t>
+          <t>CORREIA DOS SANTOS BORTOLUZZI/CAROLINA</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>45876.4375</v>
+        <v>45881.49097222222</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>Topocart Topografia Engenharia e Aerolevantamentos</t>
+          <t>Mobiauto Edicao de Anuncios On Line Ltda</t>
         </is>
       </c>
       <c r="W20" s="5" t="inlineStr">
@@ -4239,11 +4239,11 @@
       </c>
       <c r="X20" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>778248674</v>
+        <v>2143287635</v>
       </c>
       <c r="Z20" s="5" t="inlineStr">
         <is>
@@ -4256,16 +4256,16 @@
         </is>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>166.75</v>
+        <v>668.28</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>0</v>
+        <v>108.53</v>
       </c>
       <c r="AD20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>0</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AF20" s="5" t="n">
         <v>0</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="AH20" s="5" t="n">
-        <v>40</v>
+        <v>14.7</v>
       </c>
       <c r="AI20" s="5" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AJ20" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK20" s="5" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="AL20" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM20" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN20" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO20" s="5" t="inlineStr">
@@ -4324,21 +4324,21 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>22700023</v>
+        <v>22729862</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>23502265</v>
+        <v>23527395</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>45876.48756944444</v>
+        <v>45881.53208333333</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45876.48841435185</v>
+        <v>45881.5340625</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>RQYD9H</t>
+          <t>AQLNTC</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Leguizamón/Iolanda</t>
+          <t>Henrique Brugnago/Diogo</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>45876.47638888889</v>
+        <v>45881.49097222222</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>Iolanda de Almeida Leguizamon Ltda</t>
+          <t>Mobiauto Edicao de Anuncios On Line Ltda</t>
         </is>
       </c>
       <c r="W21" s="5" t="inlineStr">
@@ -4430,11 +4430,11 @@
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>545138544</v>
+        <v>2143287636</v>
       </c>
       <c r="Z21" s="5" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
         </is>
       </c>
       <c r="AB21" s="5" t="n">
-        <v>409.41</v>
+        <v>668.28</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>93.59</v>
+        <v>108.53</v>
       </c>
       <c r="AD21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>0</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AF21" s="5" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="5" t="n">
-        <v>81.88</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="5" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="AJ21" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK21" s="5" t="inlineStr">
@@ -4515,21 +4515,21 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>22700023</v>
+        <v>22729877</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>23502266</v>
+        <v>23527407</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>45876.48756944444</v>
+        <v>45881.53746527778</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>45876.48841435185</v>
+        <v>45881.53807870371</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>RQYD9H</t>
+          <t>LLHTHY</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Leguizamón/Jorge</t>
+          <t>SAYER SAVOY/LAURA</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>45876.47638888889</v>
+        <v>45881.48333333333</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>Iolanda de Almeida Leguizamon Ltda</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W22" s="5" t="inlineStr">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="X22" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>380351125</v>
+        <v>2143291826</v>
       </c>
       <c r="Z22" s="5" t="inlineStr">
         <is>
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="AB22" s="5" t="n">
-        <v>409.41</v>
+        <v>444.89</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>93.59</v>
+        <v>50.92</v>
       </c>
       <c r="AD22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE22" s="5" t="n">
-        <v>0</v>
+        <v>44.48</v>
       </c>
       <c r="AF22" s="5" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AH22" s="5" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="AI22" s="5" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AJ22" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK22" s="5" t="inlineStr">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>22700070</v>
+        <v>22729677</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>23502309</v>
+        <v>23527222</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>45876.49452546296</v>
+        <v>45881.5225462963</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>45876.49780092593</v>
+        <v>45881.52762731481</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>YM1U2G</t>
+          <t>HGDGXI</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>ESTEVAO PERDIGAO DE MIRANDA/LUIZ</t>
+          <t>Antonio Ferreira/Marco</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>45876.49166666667</v>
+        <v>45881.5</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V23" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Service Engenharia</t>
         </is>
       </c>
       <c r="W23" s="5" t="inlineStr">
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>743416547</v>
+        <v>935698164</v>
       </c>
       <c r="Z23" s="5" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="AB23" s="5" t="n">
-        <v>1147.84</v>
+        <v>467.92</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>46.72</v>
       </c>
       <c r="AD23" s="5" t="n">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="AH23" s="5" t="n">
-        <v>0</v>
+        <v>56.15</v>
       </c>
       <c r="AI23" s="5" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AJ23" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK23" s="5" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AL23" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM23" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN23" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO23" s="5" t="inlineStr">
@@ -4897,10 +4897,10 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>22695090</v>
+        <v>22729911</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>23497957</v>
+        <v>23527445</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>45875.73756944444</v>
+        <v>45881.54165509259</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>45875.7380787037</v>
+        <v>45881.54458333334</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>QIGHPS</t>
+          <t>DLKJIP</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>FERREIRA/ISABELLE</t>
+          <t>FRANCISCO DE CARVALHO/VINICIUS</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>45875.23680555556</v>
+        <v>45881.53958333333</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="V24" s="5" t="inlineStr">
         <is>
-          <t>Tailler</t>
+          <t>Porto, Miranda, Rocha Sociedade de Advogados</t>
         </is>
       </c>
       <c r="W24" s="5" t="inlineStr">
@@ -5003,11 +5003,11 @@
       </c>
       <c r="X24" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y24" s="5" t="n">
-        <v>408236868</v>
+        <v>2245493659</v>
       </c>
       <c r="Z24" s="5" t="inlineStr">
         <is>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="AB24" s="5" t="n">
-        <v>365.4</v>
+        <v>394.4</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>93.45999999999999</v>
+        <v>450</v>
       </c>
       <c r="AD24" s="5" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="5" t="n">
-        <v>40.92</v>
+        <v>40</v>
       </c>
       <c r="AI24" s="5" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AJ24" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK24" s="5" t="inlineStr">
@@ -5057,17 +5057,17 @@
       </c>
       <c r="AL24" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM24" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN24" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO24" s="5" t="inlineStr">
@@ -5088,10 +5088,10 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>22695192</v>
+        <v>22731320</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>23498043</v>
+        <v>23528797</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>45875.74878472222</v>
+        <v>45881.73645833333</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>45875.75137731482</v>
+        <v>45881.73784722222</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>YJD2PC</t>
+          <t>CPBVLR</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>FERREIRA/ISABELLE</t>
+          <t>RICARDO ALTERIO/JOAO</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>45875.24722222222</v>
+        <v>45881.23402777778</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="V25" s="5" t="inlineStr">
         <is>
-          <t>Tailler</t>
+          <t>Ind de Torrone Nossa Senhora de Montevergine Ltda</t>
         </is>
       </c>
       <c r="W25" s="5" t="inlineStr">
@@ -5194,11 +5194,11 @@
       </c>
       <c r="X25" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>267448399</v>
+        <v>2143313351</v>
       </c>
       <c r="Z25" s="5" t="inlineStr">
         <is>
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="AB25" s="5" t="n">
-        <v>1055.6</v>
+        <v>122.3</v>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>96.56999999999999</v>
+        <v>383.93</v>
       </c>
       <c r="AD25" s="5" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AH25" s="5" t="n">
-        <v>40.92</v>
+        <v>40</v>
       </c>
       <c r="AI25" s="5" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="AJ25" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK25" s="5" t="inlineStr">
@@ -5248,17 +5248,17 @@
       </c>
       <c r="AL25" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM25" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN25" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO25" s="5" t="inlineStr">
@@ -5279,21 +5279,21 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>22694293</v>
+        <v>22731393</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>23497154</v>
+        <v>23528859</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>45875.64717592593</v>
+        <v>45881.74226851852</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>45875.64989583333</v>
+        <v>45881.74431712963</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -5307,17 +5307,17 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>PLKSQW</t>
+          <t>MAZYOQ</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>ELIZABETH SILVA</t>
+          <t>Flavia de Oliveira/Fernanda</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>45870.64652777778</v>
+        <v>45881.23888888889</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
-          <t>Cartão convênio</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S26" s="5" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="V26" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Nina Saude Vitoria Ltda</t>
         </is>
       </c>
       <c r="W26" s="5" t="inlineStr">
@@ -5385,11 +5385,11 @@
       </c>
       <c r="X26" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y26" s="5" t="n">
-        <v>3023497153</v>
+        <v>2143310536</v>
       </c>
       <c r="Z26" s="5" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="AB26" s="5" t="n">
-        <v>1070.25</v>
+        <v>0.1</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>86.14</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="5" t="n">
         <v>0</v>
@@ -5420,16 +5420,16 @@
         <v>0</v>
       </c>
       <c r="AH26" s="5" t="n">
-        <v>107.03</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ26" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK26" s="5" t="inlineStr">
@@ -5439,17 +5439,17 @@
       </c>
       <c r="AL26" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM26" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN26" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO26" s="5" t="inlineStr">
@@ -5470,10 +5470,10 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>22693812</v>
+        <v>22731274</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>23496718</v>
+        <v>23528756</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>45875.57494212963</v>
+        <v>45881.7305787037</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>45875.57653935185</v>
+        <v>45881.7319212963</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>II9WRC</t>
+          <t>WMUJGC</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>EMILIO BRANDAO DE ARAUJO/CARLOS</t>
+          <t>JARDIM/Fábio</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>45875.07291666666</v>
+        <v>45881.22986111111</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="V27" s="5" t="inlineStr">
         <is>
-          <t>Conorte Servicos Industriais Ltda</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W27" s="5" t="inlineStr">
@@ -5576,11 +5576,11 @@
       </c>
       <c r="X27" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>863078581</v>
+        <v>2245547443</v>
       </c>
       <c r="Z27" s="5" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="AB27" s="5" t="n">
-        <v>548.92</v>
+        <v>318.86</v>
       </c>
       <c r="AC27" s="5" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AJ27" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK27" s="5" t="inlineStr">
@@ -5630,17 +5630,17 @@
       </c>
       <c r="AL27" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM27" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN27" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO27" s="5" t="inlineStr">
@@ -5661,10 +5661,10 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>22651101</v>
+        <v>22732767</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>23460675</v>
+        <v>23530192</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -5672,24 +5672,24 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>45868.52986111111</v>
+        <v>45881.79746527778</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>45869.4131712963</v>
+        <v>45881.79961805556</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>MQU7YH01</t>
+          <t>XNLLXT</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>GONÇALVES/GUSTAVO</t>
+          <t>Silva Machado/Joana</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="M28" s="6" t="n">
-        <v>45867.26875</v>
+        <v>45881.29583333333</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S28" s="5" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="T28" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U28" s="5" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="V28" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Cinesystem S.a.</t>
         </is>
       </c>
       <c r="W28" s="5" t="inlineStr">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="Y28" s="5" t="n">
-        <v>980419988</v>
+        <v>817572019</v>
       </c>
       <c r="Z28" s="5" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="AB28" s="5" t="n">
-        <v>713.2</v>
+        <v>1386.24</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>36.67</v>
+        <v>450</v>
       </c>
       <c r="AD28" s="5" t="n">
         <v>0</v>
@@ -5802,7 +5802,7 @@
         <v>0</v>
       </c>
       <c r="AH28" s="5" t="n">
-        <v>92.72</v>
+        <v>40</v>
       </c>
       <c r="AI28" s="5" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK28" s="5" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="AL28" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM28" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN28" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO28" s="5" t="inlineStr">
@@ -5852,21 +5852,21 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>22701761</v>
+        <v>22732582</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>23503924</v>
+        <v>23530008</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>45876.66204861111</v>
+        <v>45881.78934027778</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>45876.67363425926</v>
+        <v>45881.79013888889</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -5880,17 +5880,17 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>OMQC5Q</t>
+          <t>WYLIJR</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>ANA PAULA NERI</t>
+          <t>Silva Bosser/André</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>45875.66180555556</v>
+        <v>45881.28680555556</v>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
@@ -5923,12 +5923,12 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr">
         <is>
-          <t>Cartão de crédito</t>
+          <t>Cartão convênio</t>
         </is>
       </c>
       <c r="S29" s="5" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="V29" s="5" t="inlineStr">
         <is>
-          <t>Tivita Tecnologia E Servicos Ltda</t>
+          <t>Rought Promocoes e Eventos Eireli</t>
         </is>
       </c>
       <c r="W29" s="5" t="inlineStr">
@@ -5958,11 +5958,11 @@
       </c>
       <c r="X29" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y29" s="5" t="n">
-        <v>3023503923</v>
+        <v>2143298447</v>
       </c>
       <c r="Z29" s="5" t="inlineStr">
         <is>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="AB29" s="5" t="n">
-        <v>473.92</v>
+        <v>2255.49</v>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>33.56</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="5" t="n">
         <v>0</v>
@@ -5993,16 +5993,16 @@
         <v>0</v>
       </c>
       <c r="AH29" s="5" t="n">
-        <v>47.39</v>
+        <v>40</v>
       </c>
       <c r="AI29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">35Ocorreu a seguinte exceção ao gerar a ordem de venda: Ocorreu a seguinte exceção ao inserir o item da ordem de venda:  Faltou informar rateio de </t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK29" s="5" t="inlineStr">
@@ -6012,17 +6012,17 @@
       </c>
       <c r="AL29" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM29" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN29" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO29" s="5" t="inlineStr">
@@ -6043,10 +6043,10 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>22702509</v>
+        <v>22732644</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>23504650</v>
+        <v>23530073</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>45876.74446759259</v>
+        <v>45881.79336805556</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>45876.74635416667</v>
+        <v>45881.79483796296</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>IMMTNW</t>
+          <t>XNLLXT</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Ribeiro Gomes Amorim/Fernanda</t>
+          <t>Silva Machado/Joana</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="M30" s="6" t="n">
-        <v>45875.12361111111</v>
+        <v>45881.29166666666</v>
       </c>
       <c r="N30" s="5" t="inlineStr">
         <is>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="V30" s="5" t="inlineStr">
         <is>
-          <t>Vpr Consultoria, Eventos, Servicos e Treinamentos Ltda</t>
+          <t>Cinesystem S.a.</t>
         </is>
       </c>
       <c r="W30" s="5" t="inlineStr">
@@ -6149,11 +6149,11 @@
       </c>
       <c r="X30" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y30" s="5" t="n">
-        <v>2142913055</v>
+        <v>976145215</v>
       </c>
       <c r="Z30" s="5" t="inlineStr">
         <is>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="AB30" s="5" t="n">
-        <v>1519.9</v>
+        <v>1386.24</v>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>59.95</v>
+        <v>450</v>
       </c>
       <c r="AD30" s="5" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="AH30" s="5" t="n">
-        <v>15.2</v>
+        <v>40</v>
       </c>
       <c r="AI30" s="5" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AJ30" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/08/2025</t>
+          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
         </is>
       </c>
       <c r="AK30" s="5" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="AL30" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Duplicidade de RLOC</t>
         </is>
       </c>
       <c r="AM30" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Campo RLOC</t>
         </is>
       </c>
       <c r="AN30" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Duplicidade de Contabilização</t>
         </is>
       </c>
       <c r="AO30" s="5" t="inlineStr">
@@ -6234,10 +6234,10 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>22702557</v>
+        <v>22730884</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>23504693</v>
+        <v>23528388</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -6245,10 +6245,10 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>45876.75149305556</v>
+        <v>45881.68194444444</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>45876.75265046296</v>
+        <v>45881.68407407407</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>LN5PJQ</t>
+          <t>XIWE5P</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>PROENÇA/JOSE</t>
+          <t>PYTERSON CAPELLETTI/IGOR</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="M31" s="6" t="n">
-        <v>45876.24027777778</v>
+        <v>45881.13472222222</v>
       </c>
       <c r="N31" s="5" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="V31" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Tecthane Industria e Comercio de Artefatos Em Poliuretano</t>
         </is>
       </c>
       <c r="W31" s="5" t="inlineStr">
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>771850144</v>
+        <v>309649679</v>
       </c>
       <c r="Z31" s="5" t="inlineStr">
         <is>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="AB31" s="5" t="n">
-        <v>803.17</v>
+        <v>1037.99</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>48.16</v>
+        <v>58.89</v>
       </c>
       <c r="AD31" s="5" t="n">
         <v>0</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="AH31" s="5" t="n">
-        <v>78.38</v>
+        <v>249.12</v>
       </c>
       <c r="AI31" s="5" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="AJ31" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK31" s="5" t="inlineStr">
@@ -6425,21 +6425,21 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>22702290</v>
+        <v>22730884</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>23504426</v>
+        <v>23528389</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>45876.71539351852</v>
+        <v>45881.68194444444</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>45876.72435185185</v>
+        <v>45881.68407407407</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>TE2DPR</t>
+          <t>XIWE5P</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Ferrari/Vinicius</t>
+          <t>Marziane Johann Capelletti/Deise</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>45876.04305555556</v>
+        <v>45881.13472222222</v>
       </c>
       <c r="N32" s="5" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="V32" s="5" t="inlineStr">
         <is>
-          <t>Neurox</t>
+          <t>Tecthane Industria e Comercio de Artefatos Em Poliuretano</t>
         </is>
       </c>
       <c r="W32" s="5" t="inlineStr">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="Y32" s="5" t="n">
-        <v>793480309</v>
+        <v>462835615</v>
       </c>
       <c r="Z32" s="5" t="inlineStr">
         <is>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="AB32" s="5" t="n">
-        <v>2550.51</v>
+        <v>1037.99</v>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>60.62</v>
+        <v>58.89</v>
       </c>
       <c r="AD32" s="5" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="AH32" s="5" t="n">
-        <v>255.05</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="5" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AJ32" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK32" s="5" t="inlineStr">
@@ -6616,10 +6616,10 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>22702180</v>
+        <v>22728064</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>23504319</v>
+        <v>23525707</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>45876.70707175926</v>
+        <v>45881.34165509259</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>45876.70912037037</v>
+        <v>45881.34214120371</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>NQUL5E</t>
+          <t>LA9572863LTDJ</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>de Aguiar Ribeiro/Gustavo</t>
+          <t>Cardoso Ferreira/Walter</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>45876.09097222222</v>
+        <v>45881.3375</v>
       </c>
       <c r="N33" s="5" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="V33" s="5" t="inlineStr">
         <is>
-          <t>Tributo Devido Contabilidade e Assessoria Tributaria Ltda</t>
+          <t>Pessoa e Pessoa Advogados Associados</t>
         </is>
       </c>
       <c r="W33" s="5" t="inlineStr">
@@ -6722,11 +6722,11 @@
       </c>
       <c r="X33" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>663202476</v>
+        <v>2245457846</v>
       </c>
       <c r="Z33" s="5" t="inlineStr">
         <is>
@@ -6739,16 +6739,16 @@
         </is>
       </c>
       <c r="AB33" s="5" t="n">
-        <v>1360.78</v>
+        <v>319.92</v>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>82.86</v>
+        <v>60.62</v>
       </c>
       <c r="AD33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE33" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF33" s="5" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AH33" s="5" t="n">
-        <v>489.88</v>
+        <v>21.6</v>
       </c>
       <c r="AI33" s="5" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="AJ33" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK33" s="5" t="inlineStr">
@@ -6776,17 +6776,17 @@
       </c>
       <c r="AL33" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM33" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN33" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO33" s="5" t="inlineStr">
@@ -6807,21 +6807,21 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>22702180</v>
+        <v>22728612</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>23504320</v>
+        <v>23526178</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>45876.70707175926</v>
+        <v>45881.42814814814</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>45876.70912037037</v>
+        <v>45881.4296875</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>NQUL5E</t>
+          <t>BRSRMB</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>BRANDÃO MAURICIO/Renata</t>
+          <t>Monteiro/André</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="M34" s="6" t="n">
-        <v>45876.09097222222</v>
+        <v>45881.36111111111</v>
       </c>
       <c r="N34" s="5" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="V34" s="5" t="inlineStr">
         <is>
-          <t>Tributo Devido Contabilidade e Assessoria Tributaria Ltda</t>
+          <t>Medcentro To Distribuidora de Produtos Farmaceuticos</t>
         </is>
       </c>
       <c r="W34" s="5" t="inlineStr">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="Y34" s="5" t="n">
-        <v>392102362</v>
+        <v>934956635</v>
       </c>
       <c r="Z34" s="5" t="inlineStr">
         <is>
@@ -6930,10 +6930,10 @@
         </is>
       </c>
       <c r="AB34" s="5" t="n">
-        <v>1360.78</v>
+        <v>387.06</v>
       </c>
       <c r="AC34" s="5" t="n">
-        <v>82.86</v>
+        <v>36.67</v>
       </c>
       <c r="AD34" s="5" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="AH34" s="5" t="n">
-        <v>0</v>
+        <v>46.45</v>
       </c>
       <c r="AI34" s="5" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AJ34" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK34" s="5" t="inlineStr">
@@ -6998,21 +6998,21 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>22702180</v>
+        <v>22728625</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>23504321</v>
+        <v>23526192</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>ACC03</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>45876.70707175926</v>
+        <v>45881.43053240741</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>45876.70912037037</v>
+        <v>45881.43170138889</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>NQUL5E</t>
+          <t>LA9579644LMFE</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Gustavo Mauricio Ribeiro/Luiz</t>
+          <t>Monteiro/André</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="M35" s="6" t="n">
-        <v>45876.09097222222</v>
+        <v>45881.36111111111</v>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="V35" s="5" t="inlineStr">
         <is>
-          <t>Tributo Devido Contabilidade e Assessoria Tributaria Ltda</t>
+          <t>Medcentro To Distribuidora de Produtos Farmaceuticos</t>
         </is>
       </c>
       <c r="W35" s="5" t="inlineStr">
@@ -7104,11 +7104,11 @@
       </c>
       <c r="X35" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y35" s="5" t="n">
-        <v>877397275</v>
+        <v>2245458856</v>
       </c>
       <c r="Z35" s="5" t="inlineStr">
         <is>
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="AB35" s="5" t="n">
-        <v>1360.78</v>
+        <v>491.96</v>
       </c>
       <c r="AC35" s="5" t="n">
-        <v>82.86</v>
+        <v>48.3</v>
       </c>
       <c r="AD35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE35" s="5" t="n">
-        <v>0</v>
+        <v>49.19</v>
       </c>
       <c r="AF35" s="5" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="AH35" s="5" t="n">
-        <v>0</v>
+        <v>32.47</v>
       </c>
       <c r="AI35" s="5" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AJ35" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK35" s="5" t="inlineStr">
@@ -7189,10 +7189,10 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>22701858</v>
+        <v>22728626</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>23504017</v>
+        <v>23526193</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>45876.67097222222</v>
+        <v>45881.43053240741</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>45876.67528935185</v>
+        <v>45881.43186342593</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>LA9579834VCKM</t>
+          <t>CRFZ9B</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>TAIRA/PAULA</t>
+          <t>Monteiro/André</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>45876.13055555556</v>
+        <v>45881.36111111111</v>
       </c>
       <c r="N36" s="5" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="V36" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Medcentro To Distribuidora de Produtos Farmaceuticos</t>
         </is>
       </c>
       <c r="W36" s="5" t="inlineStr">
@@ -7295,11 +7295,11 @@
       </c>
       <c r="X36" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y36" s="5" t="n">
-        <v>2244717121</v>
+        <v>593786344</v>
       </c>
       <c r="Z36" s="5" t="inlineStr">
         <is>
@@ -7312,16 +7312,16 @@
         </is>
       </c>
       <c r="AB36" s="5" t="n">
-        <v>1150.24</v>
+        <v>474.9</v>
       </c>
       <c r="AC36" s="5" t="n">
-        <v>108.78</v>
+        <v>54.45</v>
       </c>
       <c r="AD36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE36" s="5" t="n">
-        <v>115.02</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="5" t="n">
         <v>0</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="AH36" s="5" t="n">
-        <v>227.75</v>
+        <v>56.99</v>
       </c>
       <c r="AI36" s="5" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AJ36" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK36" s="5" t="inlineStr">
@@ -7380,21 +7380,21 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>22701858</v>
+        <v>22730463</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>23504018</v>
+        <v>23527953</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>45876.67097222222</v>
+        <v>45881.62353009259</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>45876.67528935185</v>
+        <v>45881.62606481482</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>LA9579834VCKM</t>
+          <t>QGMSXY</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>LI PUMA JUNIOR/MICHELE</t>
+          <t>LIMA SODRÉ/EDUARDO</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="M37" s="6" t="n">
-        <v>45876.13055555556</v>
+        <v>45881.12291666667</v>
       </c>
       <c r="N37" s="5" t="inlineStr">
         <is>
@@ -7471,12 +7471,12 @@
       </c>
       <c r="U37" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>-</t>
         </is>
       </c>
       <c r="V37" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Didier, Sodre e Rosa Advocacia e Consultoria</t>
         </is>
       </c>
       <c r="W37" s="5" t="inlineStr">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="X37" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y37" s="5" t="n">
-        <v>2244717122</v>
+        <v>862062498</v>
       </c>
       <c r="Z37" s="5" t="inlineStr">
         <is>
@@ -7503,16 +7503,16 @@
         </is>
       </c>
       <c r="AB37" s="5" t="n">
-        <v>1150.24</v>
+        <v>1306.74</v>
       </c>
       <c r="AC37" s="5" t="n">
-        <v>108.78</v>
+        <v>0</v>
       </c>
       <c r="AD37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE37" s="5" t="n">
-        <v>115.02</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="5" t="n">
         <v>0</v>
@@ -7521,7 +7521,7 @@
         <v>0</v>
       </c>
       <c r="AH37" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI37" s="5" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="AJ37" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK37" s="5" t="inlineStr">
@@ -7571,21 +7571,21 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>22701858</v>
+        <v>22730220</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>23504019</v>
+        <v>23527745</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>ACC03</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>45876.67097222222</v>
+        <v>45881.58753472222</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>45876.67528935185</v>
+        <v>45881.58921296296</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>LA9579834VCKM</t>
+          <t>CQ6HWH</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>SANTOS/MARIANA</t>
+          <t>DOS SANTOS/RAUL</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -7623,7 +7623,7 @@
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>45876.13055555556</v>
+        <v>45881.06597222222</v>
       </c>
       <c r="N38" s="5" t="inlineStr">
         <is>
@@ -7662,12 +7662,12 @@
       </c>
       <c r="U38" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V38" s="5" t="inlineStr">
         <is>
-          <t>Pailon Comunicacao Visual Ltda</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W38" s="5" t="inlineStr">
@@ -7677,11 +7677,11 @@
       </c>
       <c r="X38" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y38" s="5" t="n">
-        <v>2244717123</v>
+        <v>402053694</v>
       </c>
       <c r="Z38" s="5" t="inlineStr">
         <is>
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="AB38" s="5" t="n">
-        <v>1150.24</v>
+        <v>1002.6</v>
       </c>
       <c r="AC38" s="5" t="n">
-        <v>108.78</v>
+        <v>108.02</v>
       </c>
       <c r="AD38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE38" s="5" t="n">
-        <v>115.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" s="5" t="n">
         <v>0</v>
@@ -7712,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="AH38" s="5" t="n">
-        <v>0</v>
+        <v>120.31</v>
       </c>
       <c r="AI38" s="5" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="AJ38" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK38" s="5" t="inlineStr">
@@ -7762,10 +7762,10 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>22701923</v>
+        <v>22730293</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>23504074</v>
+        <v>23527806</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>45876.67809027778</v>
+        <v>45881.59584490741</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>45876.67987268518</v>
+        <v>45881.5966087963</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>ZIUBHS</t>
+          <t>WGCOWU</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>NOGUEIRA MARINI/FABRIZIO</t>
+          <t>OLIVEIRA/MIZAEL</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>45876.42222222222</v>
+        <v>45881.08194444444</v>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
@@ -7853,12 +7853,12 @@
       </c>
       <c r="U39" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V39" s="5" t="inlineStr">
         <is>
-          <t>Fundamentos Sistemas</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W39" s="5" t="inlineStr">
@@ -7868,11 +7868,11 @@
       </c>
       <c r="X39" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y39" s="5" t="n">
-        <v>625487084</v>
+        <v>2143297236</v>
       </c>
       <c r="Z39" s="5" t="inlineStr">
         <is>
@@ -7885,16 +7885,16 @@
         </is>
       </c>
       <c r="AB39" s="5" t="n">
-        <v>1634.84</v>
+        <v>1432.71</v>
       </c>
       <c r="AC39" s="5" t="n">
-        <v>91.56999999999999</v>
+        <v>97.84</v>
       </c>
       <c r="AD39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE39" s="5" t="n">
-        <v>0</v>
+        <v>143.27</v>
       </c>
       <c r="AF39" s="5" t="n">
         <v>0</v>
@@ -7903,7 +7903,7 @@
         <v>0</v>
       </c>
       <c r="AH39" s="5" t="n">
-        <v>163.48</v>
+        <v>15.76</v>
       </c>
       <c r="AI39" s="5" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="AJ39" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK39" s="5" t="inlineStr">
@@ -7953,10 +7953,10 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>22701963</v>
+        <v>22730805</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>23504109</v>
+        <v>23528293</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>45876.68231481482</v>
+        <v>45881.67541666667</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>45876.68407407407</v>
+        <v>45881.67638888889</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>ONT1UQ</t>
+          <t>IJUNUY</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>SILVEIRA/VINICIUS</t>
+          <t>OLIVEIRA/MIZAEL</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="M40" s="6" t="n">
-        <v>45875.24791666667</v>
+        <v>45881.09097222222</v>
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S40" s="5" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="U40" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V40" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W40" s="5" t="inlineStr">
@@ -8059,11 +8059,11 @@
       </c>
       <c r="X40" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y40" s="5" t="n">
-        <v>433154923</v>
+        <v>2143305823</v>
       </c>
       <c r="Z40" s="5" t="inlineStr">
         <is>
@@ -8076,16 +8076,16 @@
         </is>
       </c>
       <c r="AB40" s="5" t="n">
-        <v>0</v>
+        <v>531.04</v>
       </c>
       <c r="AC40" s="5" t="n">
-        <v>0</v>
+        <v>53.57</v>
       </c>
       <c r="AD40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE40" s="5" t="n">
-        <v>0</v>
+        <v>53.1</v>
       </c>
       <c r="AF40" s="5" t="n">
         <v>0</v>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="AH40" s="5" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="AI40" s="5" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="AJ40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK40" s="5" t="inlineStr">
@@ -8113,17 +8113,17 @@
       </c>
       <c r="AL40" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM40" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN40" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO40" s="5" t="inlineStr">
@@ -8144,21 +8144,21 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>22701963</v>
+        <v>22730806</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>23504110</v>
+        <v>23528294</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>45876.68231481482</v>
+        <v>45881.67545138889</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>45876.68407407407</v>
+        <v>45881.67796296296</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>ONT1UQ</t>
+          <t>LA9576369METC</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>MARQUES/JONNATA</t>
+          <t>OLIVEIRA/MIZAEL</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="M41" s="6" t="n">
-        <v>45875.24791666667</v>
+        <v>45881.09097222222</v>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
@@ -8215,12 +8215,12 @@
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S41" s="5" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="U41" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V41" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W41" s="5" t="inlineStr">
@@ -8250,11 +8250,11 @@
       </c>
       <c r="X41" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y41" s="5" t="n">
-        <v>530336503</v>
+        <v>2245530252</v>
       </c>
       <c r="Z41" s="5" t="inlineStr">
         <is>
@@ -8267,16 +8267,16 @@
         </is>
       </c>
       <c r="AB41" s="5" t="n">
-        <v>0</v>
+        <v>467.12</v>
       </c>
       <c r="AC41" s="5" t="n">
-        <v>0</v>
+        <v>44.27</v>
       </c>
       <c r="AD41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE41" s="5" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="AF41" s="5" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="AH41" s="5" t="n">
-        <v>0</v>
+        <v>30.83</v>
       </c>
       <c r="AI41" s="5" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK41" s="5" t="inlineStr">
@@ -8304,17 +8304,17 @@
       </c>
       <c r="AL41" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM41" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN41" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO41" s="5" t="inlineStr">
@@ -8335,21 +8335,21 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>22701963</v>
+        <v>22728562</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>23504111</v>
+        <v>23526137</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>ACC03</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>45876.68231481482</v>
+        <v>45881.42231481482</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>45876.68407407407</v>
+        <v>45881.42375</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>ONT1UQ</t>
+          <t>LA9576468SHXP</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>SILVA/SUELLEN</t>
+          <t>de Sousa Correia/Renato</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="M42" s="6" t="n">
-        <v>45875.24791666667</v>
+        <v>45881.41319444445</v>
       </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R42" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S42" s="5" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="U42" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V42" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>Blood Comunicacao e Eventos Ltda</t>
         </is>
       </c>
       <c r="W42" s="5" t="inlineStr">
@@ -8441,11 +8441,11 @@
       </c>
       <c r="X42" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y42" s="5" t="n">
-        <v>881669034</v>
+        <v>2245466812</v>
       </c>
       <c r="Z42" s="5" t="inlineStr">
         <is>
@@ -8458,16 +8458,16 @@
         </is>
       </c>
       <c r="AB42" s="5" t="n">
-        <v>0</v>
+        <v>215.12</v>
       </c>
       <c r="AC42" s="5" t="n">
-        <v>0</v>
+        <v>60.62</v>
       </c>
       <c r="AD42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE42" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF42" s="5" t="n">
         <v>0</v>
@@ -8476,7 +8476,7 @@
         <v>0</v>
       </c>
       <c r="AH42" s="5" t="n">
-        <v>0</v>
+        <v>15.31</v>
       </c>
       <c r="AI42" s="5" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="AJ42" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK42" s="5" t="inlineStr">
@@ -8495,17 +8495,17 @@
       </c>
       <c r="AL42" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM42" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN42" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO42" s="5" t="inlineStr">
@@ -8526,21 +8526,21 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>22701963</v>
+        <v>22732327</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>23504112</v>
+        <v>23529769</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>ACC04</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>45876.68231481482</v>
+        <v>45881.77775462963</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>45876.68407407407</v>
+        <v>45881.77976851852</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>ONT1UQ</t>
+          <t>XGJMGY</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>SANTOS/MARIA</t>
+          <t>MELO/Cláudia</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="M43" s="6" t="n">
-        <v>45875.24791666667</v>
+        <v>45880.48819444444</v>
       </c>
       <c r="N43" s="5" t="inlineStr">
         <is>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S43" s="5" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="U43" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo System Service</t>
         </is>
       </c>
       <c r="V43" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="W43" s="5" t="inlineStr">
@@ -8636,7 +8636,7 @@
         </is>
       </c>
       <c r="Y43" s="5" t="n">
-        <v>655926091</v>
+        <v>131492023</v>
       </c>
       <c r="Z43" s="5" t="inlineStr">
         <is>
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="AB43" s="5" t="n">
-        <v>0</v>
+        <v>359.92</v>
       </c>
       <c r="AC43" s="5" t="n">
-        <v>0</v>
+        <v>58.89</v>
       </c>
       <c r="AD43" s="5" t="n">
         <v>0</v>
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="AH43" s="5" t="n">
-        <v>0</v>
+        <v>43.19</v>
       </c>
       <c r="AI43" s="5" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AJ43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/08/2025</t>
         </is>
       </c>
       <c r="AK43" s="5" t="inlineStr">
@@ -8686,17 +8686,17 @@
       </c>
       <c r="AL43" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM43" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN43" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO43" s="5" t="inlineStr">
@@ -8717,10 +8717,10 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>22701964</v>
+        <v>22732986</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>23504113</v>
+        <v>23530385</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
@@ -8728,10 +8728,10 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>45876.68236111111</v>
+        <v>45881.83056712963</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>45876.68616898148</v>
+        <v>45881.83173611111</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>WRYNTH</t>
+          <t>SWHZRA</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Barros da Costa/Marília</t>
+          <t>MELO/Cláudia</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="M44" s="6" t="n">
-        <v>45876.07430555556</v>
+        <v>45881.50208333333</v>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
@@ -8788,12 +8788,12 @@
       </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R44" s="5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S44" s="5" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="U44" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo System Service</t>
         </is>
       </c>
       <c r="V44" s="5" t="inlineStr">
         <is>
-          <t>Associacao Colo de Deus e Santissima Virgem (a.c.d.s.v)</t>
+          <t>System Service</t>
         </is>
       </c>
       <c r="W44" s="5" t="inlineStr">
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y44" s="5" t="n">
-        <v>125955518</v>
+        <v>240455122</v>
       </c>
       <c r="Z44" s="5" t="inlineStr">
         <is>
@@ -8840,10 +8840,10 @@
         </is>
       </c>
       <c r="AB44" s="5" t="n">
-        <v>947.09</v>
+        <v>475.3</v>
       </c>
       <c r="AC44" s="5" t="n">
-        <v>92.53</v>
+        <v>33.64</v>
       </c>
       <c r="AD44" s="5" t="n">
         <v>0</v>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="AH44" s="5" t="n">
-        <v>123.12</v>
+        <v>57.04</v>
       </c>
       <c r="AI44" s="5" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AJ44" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Módulo Operações    -&gt; Configurações      -&gt; Configurações do sistema turismo        -&gt; Importação das vendas          -&gt; Entradas/Saídas  Para o </t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 12/08/2025</t>
         </is>
       </c>
       <c r="AK44" s="5" t="inlineStr">
@@ -8877,17 +8877,17 @@
       </c>
       <c r="AL44" s="5" t="inlineStr">
         <is>
-          <t>Forma de Pagamento indevida</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM44" s="5" t="inlineStr">
         <is>
-          <t>Forma PG. e REC.</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN44" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO44" s="5" t="inlineStr">
@@ -8901,1534 +8901,6 @@
         </is>
       </c>
       <c r="AQ44" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>22701979</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>23504123</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>ACC01</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>45876.68474537037</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>45876.68616898148</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>JIYUSM</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>EBOOKING</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>VICENTE DA SILVA/ELIZABETE</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="n">
-        <v>45876.18402777778</v>
-      </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="R45" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T45" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V45" s="5" t="inlineStr">
-        <is>
-          <t>Nayane</t>
-        </is>
-      </c>
-      <c r="W45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X45" s="5" t="inlineStr">
-        <is>
-          <t>Latam Airlines Brasil</t>
-        </is>
-      </c>
-      <c r="Y45" s="5" t="n">
-        <v>2244704749</v>
-      </c>
-      <c r="Z45" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA45" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB45" s="5" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="AC45" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AD45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI45" s="5" t="inlineStr">
-        <is>
-          <t>obs</t>
-        </is>
-      </c>
-      <c r="AJ45" s="5" t="inlineStr">
-        <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
-        </is>
-      </c>
-      <c r="AK45" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL45" s="5" t="inlineStr">
-        <is>
-          <t>Não identificado</t>
-        </is>
-      </c>
-      <c r="AM45" s="5" t="inlineStr">
-        <is>
-          <t>Análise Benner</t>
-        </is>
-      </c>
-      <c r="AN45" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="AO45" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP45" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ45" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>22701594</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>23503746</v>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>ACC01</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>45876.63767361111</v>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>45876.6442824074</v>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>LA9574257CKOF</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>EBOOKING</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Guerreiro Mason/Ricardo</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="n">
-        <v>45876.05694444444</v>
-      </c>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="R46" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="S46" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T46" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V46" s="5" t="inlineStr">
-        <is>
-          <t>Fortymil Industria de Plasticos Ltda</t>
-        </is>
-      </c>
-      <c r="W46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X46" s="5" t="inlineStr">
-        <is>
-          <t>Latam Airlines Brasil</t>
-        </is>
-      </c>
-      <c r="Y46" s="5" t="n">
-        <v>2244707942</v>
-      </c>
-      <c r="Z46" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA46" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB46" s="5" t="n">
-        <v>577.4400000000001</v>
-      </c>
-      <c r="AC46" s="5" t="n">
-        <v>116.64</v>
-      </c>
-      <c r="AD46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="5" t="n">
-        <v>57.74</v>
-      </c>
-      <c r="AF46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="5" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="AI46" s="5" t="inlineStr">
-        <is>
-          <t>obs</t>
-        </is>
-      </c>
-      <c r="AJ46" s="5" t="inlineStr">
-        <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
-        </is>
-      </c>
-      <c r="AK46" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL46" s="5" t="inlineStr">
-        <is>
-          <t>Não identificado</t>
-        </is>
-      </c>
-      <c r="AM46" s="5" t="inlineStr">
-        <is>
-          <t>Análise Benner</t>
-        </is>
-      </c>
-      <c r="AN46" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="AO46" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP46" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ46" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>22701432</v>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>23503600</v>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>ACC01</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>45876.60962962963</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>45876.61112268519</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>LA9578799IXZM</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>EBOOKING</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>Castelo Branco Mesquita/Ilanna</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="n">
-        <v>45876.50486111111</v>
-      </c>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="R47" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T47" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V47" s="5" t="inlineStr">
-        <is>
-          <t>Certare Engenharia e Consultoria</t>
-        </is>
-      </c>
-      <c r="W47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X47" s="5" t="inlineStr">
-        <is>
-          <t>Latam Airlines Brasil</t>
-        </is>
-      </c>
-      <c r="Y47" s="5" t="n">
-        <v>2244701000</v>
-      </c>
-      <c r="Z47" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA47" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB47" s="5" t="n">
-        <v>823.84</v>
-      </c>
-      <c r="AC47" s="5" t="n">
-        <v>101.01</v>
-      </c>
-      <c r="AD47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="5" t="n">
-        <v>82.38</v>
-      </c>
-      <c r="AF47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="5" t="n">
-        <v>54.37</v>
-      </c>
-      <c r="AI47" s="5" t="inlineStr">
-        <is>
-          <t>obs</t>
-        </is>
-      </c>
-      <c r="AJ47" s="5" t="inlineStr">
-        <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/08/2025</t>
-        </is>
-      </c>
-      <c r="AK47" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL47" s="5" t="inlineStr">
-        <is>
-          <t>Não identificado</t>
-        </is>
-      </c>
-      <c r="AM47" s="5" t="inlineStr">
-        <is>
-          <t>Análise Benner</t>
-        </is>
-      </c>
-      <c r="AN47" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="AO47" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP47" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ47" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n">
-        <v>22702374</v>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>23504524</v>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>ACC01</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>45876.72446759259</v>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>45876.7305787037</v>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>AEQMHY</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>FERNANDO LEITE</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="n">
-        <v>45875.72430555556</v>
-      </c>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="R48" s="5" t="inlineStr">
-        <is>
-          <t>Cartão convênio</t>
-        </is>
-      </c>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V48" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
-        </is>
-      </c>
-      <c r="W48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X48" s="5" t="inlineStr">
-        <is>
-          <t>Azul Linhas Aereas</t>
-        </is>
-      </c>
-      <c r="Y48" s="5" t="n">
-        <v>3023504523</v>
-      </c>
-      <c r="Z48" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB48" s="5" t="n">
-        <v>665.84</v>
-      </c>
-      <c r="AC48" s="5" t="n">
-        <v>91.56999999999999</v>
-      </c>
-      <c r="AD48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="5" t="n">
-        <v>332.92</v>
-      </c>
-      <c r="AI48" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ48" s="5" t="inlineStr">
-        <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
-        </is>
-      </c>
-      <c r="AK48" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL48" s="5" t="inlineStr">
-        <is>
-          <t>Falta de informação Gerencial</t>
-        </is>
-      </c>
-      <c r="AM48" s="5" t="inlineStr">
-        <is>
-          <t>Rateio de centro de custo/projeto</t>
-        </is>
-      </c>
-      <c r="AN48" s="5" t="inlineStr">
-        <is>
-          <t>Dados Gerenciais</t>
-        </is>
-      </c>
-      <c r="AO48" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP48" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ48" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>22702374</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>23504547</v>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>ACC02</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>45876.72446759259</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>45876.7305787037</v>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>AEQMHY</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>GILSON SILVA</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>45875.72430555556</v>
-      </c>
-      <c r="N49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q49" s="5" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="R49" s="5" t="inlineStr">
-        <is>
-          <t>Cartão convênio</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V49" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
-        </is>
-      </c>
-      <c r="W49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X49" s="5" t="inlineStr">
-        <is>
-          <t>Azul Linhas Aereas</t>
-        </is>
-      </c>
-      <c r="Y49" s="5" t="n">
-        <v>3023504548</v>
-      </c>
-      <c r="Z49" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB49" s="5" t="n">
-        <v>665.84</v>
-      </c>
-      <c r="AC49" s="5" t="n">
-        <v>91.56999999999999</v>
-      </c>
-      <c r="AD49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ49" s="5" t="inlineStr">
-        <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
-        </is>
-      </c>
-      <c r="AK49" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL49" s="5" t="inlineStr">
-        <is>
-          <t>Falta de informação Gerencial</t>
-        </is>
-      </c>
-      <c r="AM49" s="5" t="inlineStr">
-        <is>
-          <t>Rateio de centro de custo/projeto</t>
-        </is>
-      </c>
-      <c r="AN49" s="5" t="inlineStr">
-        <is>
-          <t>Dados Gerenciais</t>
-        </is>
-      </c>
-      <c r="AO49" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP49" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ49" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="n">
-        <v>22702374</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>23504550</v>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>ACC03</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>45876.72446759259</v>
-      </c>
-      <c r="E50" s="6" t="n">
-        <v>45876.7305787037</v>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>AEQMHY</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>FLAVIO SANTIAGO RAMOS</t>
-        </is>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="n">
-        <v>45875.72430555556</v>
-      </c>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q50" s="5" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="R50" s="5" t="inlineStr">
-        <is>
-          <t>Cartão convênio</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T50" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U50" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V50" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
-        </is>
-      </c>
-      <c r="W50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X50" s="5" t="inlineStr">
-        <is>
-          <t>Azul Linhas Aereas</t>
-        </is>
-      </c>
-      <c r="Y50" s="5" t="n">
-        <v>3023504555</v>
-      </c>
-      <c r="Z50" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB50" s="5" t="n">
-        <v>665.84</v>
-      </c>
-      <c r="AC50" s="5" t="n">
-        <v>91.56999999999999</v>
-      </c>
-      <c r="AD50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ50" s="5" t="inlineStr">
-        <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
-        </is>
-      </c>
-      <c r="AK50" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL50" s="5" t="inlineStr">
-        <is>
-          <t>Falta de informação Gerencial</t>
-        </is>
-      </c>
-      <c r="AM50" s="5" t="inlineStr">
-        <is>
-          <t>Rateio de centro de custo/projeto</t>
-        </is>
-      </c>
-      <c r="AN50" s="5" t="inlineStr">
-        <is>
-          <t>Dados Gerenciais</t>
-        </is>
-      </c>
-      <c r="AO50" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP50" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ50" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>22702374</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>23504552</v>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>ACC04</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>45876.72446759259</v>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>45876.7305787037</v>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>AEQMHY</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>GABRIEL ARMOND DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="M51" s="6" t="n">
-        <v>45875.72430555556</v>
-      </c>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="R51" s="5" t="inlineStr">
-        <is>
-          <t>Cartão convênio</t>
-        </is>
-      </c>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V51" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
-        </is>
-      </c>
-      <c r="W51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X51" s="5" t="inlineStr">
-        <is>
-          <t>Azul Linhas Aereas</t>
-        </is>
-      </c>
-      <c r="Y51" s="5" t="n">
-        <v>3023504557</v>
-      </c>
-      <c r="Z51" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB51" s="5" t="n">
-        <v>665.84</v>
-      </c>
-      <c r="AC51" s="5" t="n">
-        <v>91.56999999999999</v>
-      </c>
-      <c r="AD51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ51" s="5" t="inlineStr">
-        <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
-        </is>
-      </c>
-      <c r="AK51" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL51" s="5" t="inlineStr">
-        <is>
-          <t>Falta de informação Gerencial</t>
-        </is>
-      </c>
-      <c r="AM51" s="5" t="inlineStr">
-        <is>
-          <t>Rateio de centro de custo/projeto</t>
-        </is>
-      </c>
-      <c r="AN51" s="5" t="inlineStr">
-        <is>
-          <t>Dados Gerenciais</t>
-        </is>
-      </c>
-      <c r="AO51" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP51" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ51" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>22702374</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>23504554</v>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>ACC05</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>45876.72446759259</v>
-      </c>
-      <c r="E52" s="6" t="n">
-        <v>45876.7305787037</v>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>AEQMHY</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>JOSE LUIS BRITO DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Cardoso</t>
-        </is>
-      </c>
-      <c r="M52" s="6" t="n">
-        <v>45875.72430555556</v>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>Invoice</t>
-        </is>
-      </c>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>Cartão convênio</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V52" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
-        </is>
-      </c>
-      <c r="W52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X52" s="5" t="inlineStr">
-        <is>
-          <t>Azul Linhas Aereas</t>
-        </is>
-      </c>
-      <c r="Y52" s="5" t="n">
-        <v>3023504558</v>
-      </c>
-      <c r="Z52" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB52" s="5" t="n">
-        <v>665.84</v>
-      </c>
-      <c r="AC52" s="5" t="n">
-        <v>91.56999999999999</v>
-      </c>
-      <c r="AD52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ52" s="5" t="inlineStr">
-        <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
-        </is>
-      </c>
-      <c r="AK52" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL52" s="5" t="inlineStr">
-        <is>
-          <t>Falta de informação Gerencial</t>
-        </is>
-      </c>
-      <c r="AM52" s="5" t="inlineStr">
-        <is>
-          <t>Rateio de centro de custo/projeto</t>
-        </is>
-      </c>
-      <c r="AN52" s="5" t="inlineStr">
-        <is>
-          <t>Dados Gerenciais</t>
-        </is>
-      </c>
-      <c r="AO52" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP52" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ52" s="5" t="inlineStr">
         <is>
           <t>Operações - KONTRIP</t>
         </is>

--- a/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
+++ b/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ23"/>
+  <dimension ref="A1:AQ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,10 +695,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>22909375</v>
+        <v>23080902</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>23682579</v>
+        <v>23832217</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>45911.63607638889</v>
+        <v>45939.81798611111</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>45911.63839120371</v>
+        <v>45939.81917824074</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>HGREKE</t>
+          <t>WCDAHC</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Joaquim Araujo/Antonio</t>
+          <t>Kobo Arruda/Viviane</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>45911.50347222222</v>
+        <v>45939.31666666667</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>Cda</t>
+          <t>Total Carnes e Derivados</t>
         </is>
       </c>
       <c r="W2" s="5" t="inlineStr">
@@ -801,11 +801,11 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>2145214886</v>
+        <v>2254301906</v>
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>1054.59</v>
+        <v>1280.28</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>51.66</v>
+        <v>450</v>
       </c>
       <c r="AD2" s="5" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>94.91</v>
+        <v>40</v>
       </c>
       <c r="AI2" s="5" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK2" s="5" t="inlineStr">
@@ -886,10 +886,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>22909351</v>
+        <v>23081304</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23682559</v>
+        <v>23832603</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>45911.63337962963</v>
+        <v>45939.83322916667</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>45911.63466435186</v>
+        <v>45939.83416666667</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>CONUCR</t>
+          <t>LA9577296IGEK</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>SADER/MARCELO</t>
+          <t>Araujo Sousa/Denival</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>45911.50208333333</v>
+        <v>45939.47222222222</v>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>Cda</t>
+          <t>Perimetral Montagem Ltda</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
@@ -992,11 +992,11 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>2145214845</v>
+        <v>2254306200</v>
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
@@ -1009,16 +1009,16 @@
         </is>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>2273.89</v>
+        <v>1119.92</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>112.28</v>
+        <v>59.46</v>
       </c>
       <c r="AD3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE3" s="5" t="n">
-        <v>0</v>
+        <v>111.99</v>
       </c>
       <c r="AF3" s="5" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>204.65</v>
+        <v>73.91</v>
       </c>
       <c r="AI3" s="5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="AJ3" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK3" s="5" t="inlineStr">
@@ -1077,10 +1077,10 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>22912227</v>
+        <v>23080569</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>23685269</v>
+        <v>23831910</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>45911.95170138889</v>
+        <v>45939.794375</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>45911.95275462963</v>
+        <v>45939.79615740741</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>KRJOTN</t>
+          <t>LA9573454KJSA</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Ribeiro/Aldo</t>
+          <t>MOREIRA CAMPOS/RODRIGO</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>45911.44652777778</v>
+        <v>45939.27430555555</v>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>Pessoa e Pessoa Advogados Associados</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
@@ -1183,11 +1183,11 @@
       </c>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>2145247985</v>
+        <v>2254295402</v>
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
@@ -1200,16 +1200,16 @@
         </is>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>489.65</v>
+        <v>1134.32</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>44.27</v>
+        <v>49.71</v>
       </c>
       <c r="AD4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE4" s="5" t="n">
-        <v>0</v>
+        <v>113.43</v>
       </c>
       <c r="AF4" s="5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>44.07</v>
+        <v>74.87</v>
       </c>
       <c r="AI4" s="5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AJ4" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC01)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK4" s="5" t="inlineStr">
@@ -1237,17 +1237,17 @@
       </c>
       <c r="AL4" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM4" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN4" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO4" s="5" t="inlineStr">
@@ -1268,10 +1268,10 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>22909965</v>
+        <v>23080570</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>23683184</v>
+        <v>23831911</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>45911.70832175926</v>
+        <v>45939.79438657407</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>45911.70954861111</v>
+        <v>45939.79616898148</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>COMIVJ</t>
+          <t>LA9577885KGXX</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>BLENDO FERREIRA SILVA/WILLIAN</t>
+          <t>MOREIRA CAMPOS/RODRIGO</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>45911.20763888889</v>
+        <v>45939.27430555555</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>Rcs Tecnologia S/a</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W5" s="5" t="inlineStr">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="X5" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>2145198044</v>
+        <v>2254295499</v>
       </c>
       <c r="Z5" s="5" t="inlineStr">
         <is>
@@ -1391,16 +1391,16 @@
         </is>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>2100.73</v>
+        <v>2799.2</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>32.87</v>
+        <v>34.11</v>
       </c>
       <c r="AD5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>0</v>
+        <v>279.92</v>
       </c>
       <c r="AF5" s="5" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>16.67</v>
+        <v>184.75</v>
       </c>
       <c r="AI5" s="5" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AJ5" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK5" s="5" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>22910005</v>
+        <v>23079906</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>23683224</v>
+        <v>23831269</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>45911.715625</v>
+        <v>45939.70849537037</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>45911.71751157408</v>
+        <v>45939.70951388889</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>JHVCDE</t>
+          <t>AKPTMJ</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>ARAGAO MACEDO/ROGER</t>
+          <t>SILVA/CARLOS</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>45911.21319444444</v>
+        <v>45939.14722222222</v>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>Grant Thornton Auditores Independentes</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W6" s="5" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>2145225407</v>
+        <v>2147053435</v>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>2966.21</v>
+        <v>687.05</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>99.81999999999999</v>
+        <v>51.67</v>
       </c>
       <c r="AD6" s="5" t="n">
         <v>0</v>
@@ -1600,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>156.11</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="AI6" s="5" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AJ6" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK6" s="5" t="inlineStr">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>22909453</v>
+        <v>23080330</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>23682661</v>
+        <v>23831677</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>45911.64583333334</v>
+        <v>45939.75549768518</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>45911.64748842592</v>
+        <v>45939.75674768518</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>DKPNID</t>
+          <t>XGRVNY</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Schwind/Luís</t>
+          <t>leal/maria</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>45911.12013888889</v>
+        <v>45939.2375</v>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Basso e Pancotte Ltda</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
@@ -1756,11 +1756,11 @@
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>660876</v>
+        <v>692643443</v>
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>637.14</v>
+        <v>408.67</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>47.02</v>
+        <v>34.11</v>
       </c>
       <c r="AD7" s="5" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>229.37</v>
+        <v>20.43</v>
       </c>
       <c r="AI7" s="5" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AJ7" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 660876 já sendo utilizado para este fornecedor.</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK7" s="5" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr">
@@ -1841,21 +1841,21 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>22909453</v>
+        <v>23077346</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>23682662</v>
+        <v>23828750</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45911.64583333334</v>
+        <v>45939.45822916667</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>45911.64748842592</v>
+        <v>45939.45974537037</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>DKPNID</t>
+          <t>yagnqp</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Bonvini/Bianca</t>
+          <t>DA ROCHA ZANOT/ALESSANDRA</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>45911.12013888889</v>
+        <v>45939.45694444444</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>Basso e Pancotte Ltda</t>
+          <t>Grant Thornton Auditores Independentes</t>
         </is>
       </c>
       <c r="W8" s="5" t="inlineStr">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>660876</v>
+        <v>2147022229</v>
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>637.14</v>
+        <v>1413.07</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>47.02</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="5" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI8" s="5" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AJ8" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 660876 já sendo utilizado para este fornecedor.</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK8" s="5" t="inlineStr">
@@ -2001,17 +2001,17 @@
       </c>
       <c r="AL8" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM8" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN8" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO8" s="5" t="inlineStr">
@@ -2032,21 +2032,21 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>22909453</v>
+        <v>23077563</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>23682663</v>
+        <v>23828950</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ACC03</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>45911.64583333334</v>
+        <v>45939.48603009259</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>45911.64748842592</v>
+        <v>45939.48840277778</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>DKPNID</t>
+          <t>LA9576070TAXM</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Harami/Priscila</t>
+          <t>REZENDE/IRAM</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>45911.12013888889</v>
+        <v>45939.46736111111</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>Basso e Pancotte Ltda</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W9" s="5" t="inlineStr">
@@ -2138,11 +2138,11 @@
       </c>
       <c r="X9" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>660876</v>
+        <v>2254211035</v>
       </c>
       <c r="Z9" s="5" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AB9" s="5" t="n">
-        <v>637.14</v>
+        <v>2171.12</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>47.02</v>
+        <v>32.87</v>
       </c>
       <c r="AD9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>0</v>
+        <v>217.11</v>
       </c>
       <c r="AF9" s="5" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>0</v>
+        <v>143.29</v>
       </c>
       <c r="AI9" s="5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AJ9" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 660876 já sendo utilizado para este fornecedor.</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK9" s="5" t="inlineStr">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="AL9" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM9" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN9" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO9" s="5" t="inlineStr">
@@ -2223,21 +2223,21 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>22909453</v>
+        <v>23077512</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>23682664</v>
+        <v>23828905</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ACC04</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>45911.64583333334</v>
+        <v>45939.47908564815</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>45911.64748842592</v>
+        <v>45939.48043981481</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>DKPNID</t>
+          <t>UL7QKZ</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Schwind/Amanda</t>
+          <t>GUIMARAES/GUSTAVO</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>45911.12013888889</v>
+        <v>45939.45138888889</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>Basso e Pancotte Ltda</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2329,11 +2329,11 @@
       </c>
       <c r="X10" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>827692</v>
+        <v>860843023</v>
       </c>
       <c r="Z10" s="5" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="AB10" s="5" t="n">
-        <v>637.14</v>
+        <v>749.17</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>47.02</v>
+        <v>33.56</v>
       </c>
       <c r="AD10" s="5" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="5" t="n">
-        <v>0</v>
+        <v>37.46</v>
       </c>
       <c r="AI10" s="5" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AJ10" s="5" t="inlineStr">
         <is>
-          <t>Verificação de bilhetes: Bilhete 660876 já sendo utilizado para este fornecedor.</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK10" s="5" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="AL10" s="5" t="inlineStr">
         <is>
-          <t>Bilhete duplicado</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM10" s="5" t="inlineStr">
         <is>
-          <t>Bilhete Já Contabilizado</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN10" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO10" s="5" t="inlineStr">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>22861685</v>
+        <v>23079151</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>23641631</v>
+        <v>23830527</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -2425,24 +2425,24 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>45903.61025462963</v>
+        <v>45939.61383101852</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>45903.61174768519</v>
+        <v>45939.61511574074</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>CCIMEA</t>
+          <t>VQSWTX</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Venceslau dos Santos/Alisson</t>
+          <t>POLTRONIERI/MARCELLO</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>45903.51736111111</v>
+        <v>45939.11319444444</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="U11" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mercurio York</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
+          <t>Cinesystem S.a.</t>
         </is>
       </c>
       <c r="W11" s="5" t="inlineStr">
@@ -2520,11 +2520,11 @@
       </c>
       <c r="X11" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>2144712008</v>
+        <v>546952371</v>
       </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>1483.11</v>
+        <v>1002.75</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>44.27</v>
+        <v>450</v>
       </c>
       <c r="AD11" s="5" t="n">
         <v>0</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI11" s="5" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AJ11" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC01)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK11" s="5" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="AL11" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM11" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN11" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO11" s="5" t="inlineStr">
@@ -2605,10 +2605,10 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>22861689</v>
+        <v>23079979</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>23641636</v>
+        <v>23831337</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -2616,24 +2616,24 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>45903.61160879629</v>
+        <v>45939.71254629629</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>45903.61373842593</v>
+        <v>45939.71363425926</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>CVENDX</t>
+          <t>DLKNNG</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Vilela/Lidiany</t>
+          <t>DAMASCENO/ABRAAO</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>45903.51527777778</v>
+        <v>45939.19652777778</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="U12" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mercurio York</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
+          <t>M3. Business Group Ltda</t>
         </is>
       </c>
       <c r="W12" s="5" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="X12" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>2144711372</v>
+        <v>998521164</v>
       </c>
       <c r="Z12" s="5" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="AB12" s="5" t="n">
-        <v>954.8099999999999</v>
+        <v>2653.15</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>44.27</v>
+        <v>96.13</v>
       </c>
       <c r="AD12" s="5" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="5" t="n">
-        <v>0</v>
+        <v>132.66</v>
       </c>
       <c r="AI12" s="5" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="AJ12" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC01)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK12" s="5" t="inlineStr">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="AL12" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM12" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN12" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO12" s="5" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>22862473</v>
+        <v>23078240</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>23642350</v>
+        <v>23829621</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -2807,24 +2807,24 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>45903.72704861111</v>
+        <v>45939.56243055555</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>45903.72773148148</v>
+        <v>45939.56340277778</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>HRLZLB</t>
+          <t>EUEPYS</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>ANGE ARAUJO/ENY</t>
+          <t>ANTONIO DA SILVA SANTOS LIMA/MARCO</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>45903.20902777778</v>
+        <v>45939.06180555555</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="U13" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mercurio York</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
+          <t>Broadtec Tecnologia e Servicos Ltda</t>
         </is>
       </c>
       <c r="W13" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>2144726580</v>
+        <v>2146905230</v>
       </c>
       <c r="Z13" s="5" t="inlineStr">
         <is>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>539.01</v>
+        <v>545.96</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>60.62</v>
+        <v>878.22</v>
       </c>
       <c r="AD13" s="5" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI13" s="5" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AJ13" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK13" s="5" t="inlineStr">
@@ -2956,17 +2956,17 @@
       </c>
       <c r="AL13" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO13" s="5" t="inlineStr">
@@ -2987,35 +2987,35 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>22862473</v>
+        <v>23078383</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23642351</v>
+        <v>23829756</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>45903.72704861111</v>
+        <v>45939.56799768518</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>45903.72773148148</v>
+        <v>45939.56938657408</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>HRLZLB</t>
+          <t>JRUOAE</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>OLIVEIRA/PRISCILA</t>
+          <t>MENEZES DA SILVA/ROBSON</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>45903.20902777778</v>
+        <v>45939.06666666667</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="U14" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mercurio York</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
+          <t>Broadtec Tecnologia e Servicos Ltda</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>2144726581</v>
+        <v>2146895657</v>
       </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
@@ -3110,10 +3110,10 @@
         </is>
       </c>
       <c r="AB14" s="5" t="n">
-        <v>539.01</v>
+        <v>545.96</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>60.62</v>
+        <v>878.22</v>
       </c>
       <c r="AD14" s="5" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI14" s="5" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AJ14" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK14" s="5" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="AL14" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM14" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN14" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO14" s="5" t="inlineStr">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>22874109</v>
+        <v>23077812</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>23652657</v>
+        <v>23829194</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -3189,24 +3189,24 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>45905.4492824074</v>
+        <v>45939.52912037037</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>45905.45436342592</v>
+        <v>45939.52975694444</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>LA9575496KNXE</t>
+          <t>TM3IPW</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Rios/Aline</t>
+          <t>Alcântara/Pedro</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>45905.44166666667</v>
+        <v>45939.46527777778</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="U15" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mercurio York</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
+          <t>Viva Studio Oral</t>
         </is>
       </c>
       <c r="W15" s="5" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="X15" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>2249116391</v>
+        <v>605774081</v>
       </c>
       <c r="Z15" s="5" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>1873.44</v>
+        <v>863.58</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>77.14</v>
+        <v>99.97</v>
       </c>
       <c r="AD15" s="5" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>0</v>
+        <v>103.63</v>
       </c>
       <c r="AI15" s="5" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="AJ15" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK15" s="5" t="inlineStr">
@@ -3338,17 +3338,17 @@
       </c>
       <c r="AL15" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM15" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN15" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO15" s="5" t="inlineStr">
@@ -3369,35 +3369,35 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>22874109</v>
+        <v>23079350</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>23652659</v>
+        <v>23830724</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>45905.4492824074</v>
+        <v>45939.63207175926</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>45905.45436342592</v>
+        <v>45939.63369212963</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>06 a 08 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>LA9575496KNXE</t>
+          <t>MRNXIL</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Luz Santos/Uendeo</t>
+          <t>botelho/roberto</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>45905.44166666667</v>
+        <v>45939.10902777778</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="U16" s="5" t="inlineStr">
         <is>
-          <t>Grupo Mercurio York</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
+          <t>Daten Tecnologia</t>
         </is>
       </c>
       <c r="W16" s="5" t="inlineStr">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>2249116392</v>
+        <v>2254242120</v>
       </c>
       <c r="Z16" s="5" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>1873.44</v>
+        <v>0.01</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>77.14</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="5" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="AJ16" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo não preenchido! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 09/10/2025</t>
         </is>
       </c>
       <c r="AK16" s="5" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="AL16" s="5" t="inlineStr">
         <is>
-          <t>Centro de custo</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM16" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN16" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO16" s="5" t="inlineStr">
@@ -3560,21 +3560,21 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>22911619</v>
+        <v>23079146</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>23684774</v>
+        <v>23830533</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>45911.82673611111</v>
+        <v>45939.61219907407</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>45911.82756944445</v>
+        <v>45939.61859953704</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -3588,31 +3588,31 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>LA9571454MECM</t>
+          <t>TQH66H</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>EBOOKING</t>
+          <t>MANUAL</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Ribeiro Marques Moura/Adriana</t>
+          <t>JEAN GOMES DA SILVA</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Kontrip</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Kontrip</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>45911.31458333333</v>
+        <v>45938.61180555556</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>Grant Thornton Auditores Independentes</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W17" s="5" t="inlineStr">
@@ -3666,11 +3666,11 @@
       </c>
       <c r="X17" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>2250076385</v>
+        <v>3023830532</v>
       </c>
       <c r="Z17" s="5" t="inlineStr">
         <is>
@@ -3683,16 +3683,16 @@
         </is>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>823.84</v>
+        <v>2202.12</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>120.57</v>
+        <v>46.36</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>82.38</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="5" t="n">
         <v>0</v>
@@ -3701,16 +3701,16 @@
         <v>0</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>36.25</v>
+        <v>264.25</v>
       </c>
       <c r="AI17" s="5" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t xml:space="preserve">35Ocorreu a seguinte exceção ao gerar a ordem de venda: Ocorreu a seguinte exceção ao inserir o item da ordem de venda:  Faltou informar rateio de </t>
         </is>
       </c>
       <c r="AK17" s="5" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="AL17" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AM17" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Rateio de centro de custo/projeto</t>
         </is>
       </c>
       <c r="AN17" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados Gerenciais</t>
         </is>
       </c>
       <c r="AO17" s="5" t="inlineStr">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>22908935</v>
+        <v>23078778</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>23682176</v>
+        <v>23830152</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>45911.5708912037</v>
+        <v>45939.5825</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>45911.57164351852</v>
+        <v>45939.58415509259</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>UBVDEP</t>
+          <t>FSYKDL</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>RODRIGUES MAUES ALVES/DEBORA</t>
+          <t>Dias/Eloa</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>45911.06944444445</v>
+        <v>45939.07847222222</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo Mercurio York</t>
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>Mobiauto Edicao de Anuncios On Line Ltda</t>
+          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
         </is>
       </c>
       <c r="W18" s="5" t="inlineStr">
@@ -3857,11 +3857,11 @@
       </c>
       <c r="X18" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y18" s="5" t="n">
-        <v>2250011889</v>
+        <v>2147036576</v>
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>258</v>
+        <v>3759.86</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>450</v>
+        <v>113.34</v>
       </c>
       <c r="AD18" s="5" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="5" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AJ18" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK18" s="5" t="inlineStr">
@@ -3911,17 +3911,17 @@
       </c>
       <c r="AL18" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM18" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN18" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO18" s="5" t="inlineStr">
@@ -3942,10 +3942,10 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>22909200</v>
+        <v>23078887</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>23682403</v>
+        <v>23830258</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>45911.61798611111</v>
+        <v>45939.58658564815</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>45911.61986111111</v>
+        <v>45939.58788194445</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>LA9574225TCIL</t>
+          <t>IDDCOZ</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Vasconcelos/Maíra</t>
+          <t>Mota/Luiza</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>45910.44583333333</v>
+        <v>45939.08194444444</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -4033,12 +4033,12 @@
       </c>
       <c r="U19" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo Mercurio York</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>Mega Logistica Transporte Por Navegacao S/a</t>
+          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
         </is>
       </c>
       <c r="W19" s="5" t="inlineStr">
@@ -4048,11 +4048,11 @@
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y19" s="5" t="n">
-        <v>2250024175</v>
+        <v>2147037099</v>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>1894.32</v>
+        <v>1912.28</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>33.64</v>
+        <v>52.72</v>
       </c>
       <c r="AD19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>189.43</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="5" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>250.05</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="5" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AJ19" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 10/09/2025</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK19" s="5" t="inlineStr">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="AL19" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM19" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN19" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO19" s="5" t="inlineStr">
@@ -4133,21 +4133,21 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>22909200</v>
+        <v>23069422</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23682404</v>
+        <v>23821363</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>45911.61798611111</v>
+        <v>45938.42263888889</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>45911.61986111111</v>
+        <v>45938.4233912037</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>LA9574225TCIL</t>
+          <t>AVZBXY</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Carvalho/Eduardo</t>
+          <t>BARRETO/LUCIANA</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>45910.44583333333</v>
+        <v>45938.41805555556</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -4224,12 +4224,12 @@
       </c>
       <c r="U20" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo Mercurio York</t>
         </is>
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>Mega Logistica Transporte Por Navegacao S/a</t>
+          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
         </is>
       </c>
       <c r="W20" s="5" t="inlineStr">
@@ -4239,11 +4239,11 @@
       </c>
       <c r="X20" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y20" s="5" t="n">
-        <v>2250024176</v>
+        <v>2146940840</v>
       </c>
       <c r="Z20" s="5" t="inlineStr">
         <is>
@@ -4256,16 +4256,16 @@
         </is>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>1894.32</v>
+        <v>512.61</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>33.64</v>
+        <v>49.71</v>
       </c>
       <c r="AD20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>189.43</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="5" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AJ20" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 10/09/2025</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK20" s="5" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="AL20" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM20" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN20" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO20" s="5" t="inlineStr">
@@ -4324,10 +4324,10 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>22909804</v>
+        <v>23069453</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>23683039</v>
+        <v>23821404</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>45911.69021990741</v>
+        <v>45938.42708333334</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>45911.6922337963</v>
+        <v>45938.42769675926</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>LA9573321XRQH</t>
+          <t>LH164F</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>SILVA/DANIEL</t>
+          <t>BARRETO/LUCIANA</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>45911.42777777778</v>
+        <v>45938.42222222222</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="U21" s="5" t="inlineStr">
         <is>
-          <t>Grupo Softbox</t>
+          <t>Grupo Mercurio York</t>
         </is>
       </c>
       <c r="V21" s="5" t="inlineStr">
         <is>
-          <t>Luizalabs</t>
+          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
         </is>
       </c>
       <c r="W21" s="5" t="inlineStr">
@@ -4430,11 +4430,11 @@
       </c>
       <c r="X21" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>2250042719</v>
+        <v>733025258</v>
       </c>
       <c r="Z21" s="5" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
         </is>
       </c>
       <c r="AB21" s="5" t="n">
-        <v>1405.44</v>
+        <v>703.42</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>74.59999999999999</v>
+        <v>46.36</v>
       </c>
       <c r="AD21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>140.54</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="5" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="5" t="n">
-        <v>92.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="5" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="AJ21" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK21" s="5" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="AL21" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM21" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN21" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO21" s="5" t="inlineStr">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>22910566</v>
+        <v>23079031</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>23683752</v>
+        <v>23830396</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>45911.76108796296</v>
+        <v>45939.59543981482</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>45911.76306712963</v>
+        <v>45939.59658564815</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>UJ2VYS</t>
+          <t>GHOQOV</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Rodrigues Pinto/Cristian</t>
+          <t>ANGE ARAUJO/ENY</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>45911.25902777778</v>
+        <v>45939.08888888889</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="U22" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo Mercurio York</t>
         </is>
       </c>
       <c r="V22" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Agencia Mercurio York Viagens e Turismo Ltda</t>
         </is>
       </c>
       <c r="W22" s="5" t="inlineStr">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="X22" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y22" s="5" t="n">
-        <v>852567250</v>
+        <v>2147038510</v>
       </c>
       <c r="Z22" s="5" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="AB22" s="5" t="n">
-        <v>583</v>
+        <v>3759.86</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>0</v>
+        <v>113.34</v>
       </c>
       <c r="AD22" s="5" t="n">
         <v>0</v>
@@ -4656,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="AH22" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="5" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AJ22" s="5" t="inlineStr">
         <is>
-          <t>Pnr já existente. A duplicidade de rloc é permitida apenas 6 meses após o último pnr emitido</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK22" s="5" t="inlineStr">
@@ -4675,17 +4675,17 @@
       </c>
       <c r="AL22" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de RLOC</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM22" s="5" t="inlineStr">
         <is>
-          <t>Campo RLOC</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN22" s="5" t="inlineStr">
         <is>
-          <t>Duplicidade de Contabilização</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO22" s="5" t="inlineStr">
@@ -4699,197 +4699,6 @@
         </is>
       </c>
       <c r="AQ22" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>22909199</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>23682402</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>ACC01</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>45911.61663194445</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>45911.61732638889</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>0 a 02 dias</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>PGLMHI</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>EBOOKING</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>FONTELES/WEYDSON</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Kontrip</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>45911.53680555556</v>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="R23" s="5" t="inlineStr">
-        <is>
-          <t>Cartão de crédito</t>
-        </is>
-      </c>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>Aéreo</t>
-        </is>
-      </c>
-      <c r="T23" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>Grupo Kontrip</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="inlineStr">
-        <is>
-          <t>Instituto de Tecnologia Educacional</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X23" s="5" t="inlineStr">
-        <is>
-          <t>Azul Linhas Aereas</t>
-        </is>
-      </c>
-      <c r="Y23" s="5" t="n">
-        <v>863366431</v>
-      </c>
-      <c r="Z23" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA23" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB23" s="5" t="n">
-        <v>1421.17</v>
-      </c>
-      <c r="AC23" s="5" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="5" t="n">
-        <v>113.69</v>
-      </c>
-      <c r="AI23" s="5" t="inlineStr">
-        <is>
-          <t>obs</t>
-        </is>
-      </c>
-      <c r="AJ23" s="5" t="inlineStr">
-        <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 11/09/2025</t>
-        </is>
-      </c>
-      <c r="AK23" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL23" s="5" t="inlineStr">
-        <is>
-          <t>Não identificado</t>
-        </is>
-      </c>
-      <c r="AM23" s="5" t="inlineStr">
-        <is>
-          <t>Análise Benner</t>
-        </is>
-      </c>
-      <c r="AN23" s="5" t="inlineStr">
-        <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="AO23" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP23" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ23" s="5" t="inlineStr">
         <is>
           <t>Operações - KONTRIP</t>
         </is>

--- a/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
+++ b/Integration-Quality/EMPRESAS/Relatorio - KONTRIP VIAGENS.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,9 +41,6 @@
     <font>
       <b val="1"/>
       <color rgb="00591F6A"/>
-    </font>
-    <font>
-      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -93,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -109,9 +106,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -479,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ21"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,10 +695,10 @@
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
-        <v>24507872</v>
+        <v>24599778</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>25322150</v>
+        <v>25425830</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
@@ -712,24 +706,24 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>46139.80263888889</v>
+        <v>46157.62378472222</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>46139.80475694445</v>
+        <v>46157.62619212963</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>03 a 05 dias</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>0 a 02 dias</t>
+          <t>03 a 05 dias</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>MYHCPS</t>
+          <t>YYTUDZ</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -739,7 +733,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>MOREIRA DA SILVA/EDUARDO</t>
+          <t>CONCEIÇÃO DOS SANTOS/JOEL</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -753,7 +747,7 @@
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>46139.30208333334</v>
+        <v>46157.12222222222</v>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
@@ -792,12 +786,12 @@
       </c>
       <c r="U2" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Grupo Sacs</t>
         </is>
       </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>M3. Business Group Ltda</t>
+          <t>Sacs Construcao e Montagem Ltda</t>
         </is>
       </c>
       <c r="W2" s="5" t="inlineStr">
@@ -807,11 +801,11 @@
       </c>
       <c r="X2" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y2" s="5" t="n">
-        <v>2302657077</v>
+        <v>2286891563</v>
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
@@ -824,10 +818,10 @@
         </is>
       </c>
       <c r="AB2" s="5" t="n">
-        <v>3548.07</v>
+        <v>1134.96</v>
       </c>
       <c r="AC2" s="5" t="n">
-        <v>88.2</v>
+        <v>86.36</v>
       </c>
       <c r="AD2" s="5" t="n">
         <v>0</v>
@@ -842,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="AH2" s="5" t="n">
-        <v>324.35</v>
+        <v>111.76</v>
       </c>
       <c r="AI2" s="5" t="inlineStr">
         <is>
@@ -851,7 +845,7 @@
       </c>
       <c r="AJ2" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 27/04/2026</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK2" s="5" t="inlineStr">
@@ -892,10 +886,10 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
-        <v>24494682</v>
+        <v>24598779</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>25306200</v>
+        <v>25424773</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
@@ -903,10 +897,10 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>46136.61430555556</v>
+        <v>46157.48453703704</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>46137.081875</v>
+        <v>46157.48613425926</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -920,34 +914,36 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>EREAEB</t>
+          <t>WEGNJR</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>WOOBA</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>AGUIAR LINDENBERG/CARLOS MR</t>
+          <t>HENRIK PROENÇA FERNA/IGOR</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>46136.60927083333</v>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>1670</v>
+        <v>46157.48333333333</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
@@ -966,7 +962,7 @@
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
@@ -981,12 +977,12 @@
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>Grupo Rede Gazeta</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
         <is>
-          <t>Tv Gazeta</t>
+          <t>Innova Educacao Comercio De Produtos Educacionais Ltda</t>
         </is>
       </c>
       <c r="W3" s="5" t="inlineStr">
@@ -996,11 +992,11 @@
       </c>
       <c r="X3" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>2302468462</v>
+        <v>2286874083</v>
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
@@ -1013,10 +1009,10 @@
         </is>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>283.4</v>
+        <v>1469.9</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>62.14</v>
+        <v>450</v>
       </c>
       <c r="AD3" s="5" t="n">
         <v>0</v>
@@ -1031,16 +1027,16 @@
         <v>0</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>25.51</v>
+        <v>40</v>
       </c>
       <c r="AI3" s="5" t="inlineStr">
         <is>
-          <t>Reserva importada do Sistema WOOBA. Id: 4598</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ3" s="5" t="inlineStr">
         <is>
-          <t>Empenho/departamento não preenchido! (ACC02) Matrícula não preenchida! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK3" s="5" t="inlineStr">
@@ -1050,17 +1046,17 @@
       </c>
       <c r="AL3" s="5" t="inlineStr">
         <is>
-          <t>Mais de um campo não preenchido</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM3" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN3" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO3" s="5" t="inlineStr">
@@ -1081,21 +1077,21 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>24494682</v>
+        <v>24544417</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>25306201</v>
+        <v>25367756</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>46136.61430555556</v>
+        <v>46148.63471064815</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>46137.081875</v>
+        <v>46157.41923611111</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -1104,39 +1100,41 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>09 a 15 dias</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>EREAEB</t>
+          <t>AJJ47Z01</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>WOOBA</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>AGUIAR LINDENBERG/CAROLINA MRS</t>
+          <t>TEIXEIRA DA SILVA/NILTON</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>46136.60927083333</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>1670</v>
+        <v>46148.13402777778</v>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
@@ -1155,7 +1153,7 @@
       </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr">
@@ -1165,17 +1163,17 @@
       </c>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>S</t>
         </is>
       </c>
       <c r="U4" s="5" t="inlineStr">
         <is>
-          <t>Grupo Rede Gazeta</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr">
         <is>
-          <t>Tv Gazeta</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W4" s="5" t="inlineStr">
@@ -1185,11 +1183,11 @@
       </c>
       <c r="X4" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>2302468463</v>
+        <v>389040422</v>
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
@@ -1202,10 +1200,10 @@
         </is>
       </c>
       <c r="AB4" s="5" t="n">
-        <v>283.4</v>
+        <v>119.88</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>62.14</v>
+        <v>122.52</v>
       </c>
       <c r="AD4" s="5" t="n">
         <v>0</v>
@@ -1220,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="AH4" s="5" t="n">
-        <v>25.51</v>
+        <v>11.99</v>
       </c>
       <c r="AI4" s="5" t="inlineStr">
         <is>
-          <t>Reserva importada do Sistema WOOBA. Id: 4598</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ4" s="5" t="inlineStr">
         <is>
-          <t>Empenho/departamento não preenchido! (ACC02) Matrícula não preenchida! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 06/05/2026</t>
         </is>
       </c>
       <c r="AK4" s="5" t="inlineStr">
@@ -1239,17 +1237,17 @@
       </c>
       <c r="AL4" s="5" t="inlineStr">
         <is>
-          <t>Mais de um campo não preenchido</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM4" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN4" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO4" s="5" t="inlineStr">
@@ -1270,10 +1268,10 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>24405792</v>
+        <v>24605123</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25206427</v>
+        <v>25431958</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -1281,48 +1279,48 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>46118.43357638889</v>
+        <v>46158.55533564815</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>46126.354375</v>
+        <v>46158.55716435185</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>09 a 15 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>16 a 23 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>LPHLSM</t>
+          <t>CQC3WX</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>ONEIDE FRANCISCO BASSO</t>
+          <t>LIMA ROCHA/GERSON</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>46114.43333333333</v>
+        <v>46158.05347222222</v>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
@@ -1361,12 +1359,12 @@
       </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
-          <t>Grupo Zupper</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V5" s="5" t="inlineStr">
         <is>
-          <t>Basso e Pancotte</t>
+          <t>Red Engenharia Industrial Especializada Ltda</t>
         </is>
       </c>
       <c r="W5" s="5" t="inlineStr">
@@ -1376,11 +1374,11 @@
       </c>
       <c r="X5" s="5" t="inlineStr">
         <is>
-          <t>Gol Linhas Aereas</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>2301086081</v>
+        <v>464342178</v>
       </c>
       <c r="Z5" s="5" t="inlineStr">
         <is>
@@ -1393,10 +1391,10 @@
         </is>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>2724.34</v>
+        <v>2089.35</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="5" t="n">
         <v>0</v>
@@ -1411,16 +1409,16 @@
         <v>0</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>245.19</v>
+        <v>40</v>
       </c>
       <c r="AI5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ5" s="5" t="inlineStr">
         <is>
-          <t>Could not convert variant of type (Null) into type (OleStr)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 16/05/2026</t>
         </is>
       </c>
       <c r="AK5" s="5" t="inlineStr">
@@ -1461,10 +1459,10 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>24494683</v>
+        <v>24605228</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>25306202</v>
+        <v>25432067</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -1472,51 +1470,53 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>46136.6143287037</v>
+        <v>46158.56228009259</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>46137.08188657407</v>
+        <v>46158.56333333333</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>IVQEVB</t>
+          <t>IGDZGY</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>WOOBA</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>AGUIAR LINDENBERG/CARLOS MR</t>
+          <t>FERNANDES/PATRICK</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>46136.61043981482</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>1671</v>
+        <v>46158.06111111111</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S6" s="5" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
-          <t>Grupo Rede Gazeta</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
         <is>
-          <t>Tv Gazeta</t>
+          <t>Red Engenharia Industrial Especializada Ltda</t>
         </is>
       </c>
       <c r="W6" s="5" t="inlineStr">
@@ -1565,11 +1565,11 @@
       </c>
       <c r="X6" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y6" s="5" t="n">
-        <v>2283969580</v>
+        <v>731623659</v>
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>675.5599999999999</v>
+        <v>2100.54</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>54.09</v>
+        <v>450</v>
       </c>
       <c r="AD6" s="5" t="n">
         <v>0</v>
@@ -1600,16 +1600,16 @@
         <v>0</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>74.31</v>
+        <v>40</v>
       </c>
       <c r="AI6" s="5" t="inlineStr">
         <is>
-          <t>Reserva importada do Sistema WOOBA. Id: 4600</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ6" s="5" t="inlineStr">
         <is>
-          <t>Empenho/departamento não preenchido! (ACC02) Matrícula não preenchida! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 16/05/2026</t>
         </is>
       </c>
       <c r="AK6" s="5" t="inlineStr">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="AL6" s="5" t="inlineStr">
         <is>
-          <t>Mais de um campo não preenchido</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM6" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN6" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO6" s="5" t="inlineStr">
@@ -1650,62 +1650,64 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>24494683</v>
+        <v>24605018</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>25306203</v>
+        <v>25431828</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>46136.6143287037</v>
+        <v>46158.53730324074</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>46137.08188657407</v>
+        <v>46158.53851851852</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>0 a 02 dias</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>IVQEVB</t>
+          <t>MNBXNW</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>WOOBA</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>AGUIAR LINDENBERG/CAROLINA MRS</t>
+          <t>Teotonio Junior/Epaminondas</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Toou</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>46136.61043981482</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>1671</v>
+        <v>46158.53611111111</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
@@ -1724,7 +1726,7 @@
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Cartão AMEX</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
@@ -1739,12 +1741,12 @@
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>Grupo Rede Gazeta</t>
+          <t>Grupo Kontrip</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Tv Gazeta</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
@@ -1754,11 +1756,11 @@
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>2283969581</v>
+        <v>2303902227</v>
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
@@ -1771,10 +1773,10 @@
         </is>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>675.5599999999999</v>
+        <v>2155.06</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>54.09</v>
+        <v>33.64</v>
       </c>
       <c r="AD7" s="5" t="n">
         <v>0</v>
@@ -1789,16 +1791,16 @@
         <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>74.31</v>
+        <v>387.92</v>
       </c>
       <c r="AI7" s="5" t="inlineStr">
         <is>
-          <t>Reserva importada do Sistema WOOBA. Id: 4600</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="inlineStr">
         <is>
-          <t>Empenho/departamento não preenchido! (ACC02) Matrícula não preenchida! (ACC02)</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 16/05/2026</t>
         </is>
       </c>
       <c r="AK7" s="5" t="inlineStr">
@@ -1808,17 +1810,17 @@
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>Mais de um campo não preenchido</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Dados do Fornecedor</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr">
@@ -1839,21 +1841,21 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>24507657</v>
+        <v>24605018</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>25321844</v>
+        <v>25431829</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ACC01</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>46139.76956018519</v>
+        <v>46158.53730324074</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>46139.77182870371</v>
+        <v>46158.53851851852</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1867,7 +1869,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>LA9576012ODBA</t>
+          <t>MNBXNW</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1877,7 +1879,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Abdallah Mourad/Himad</t>
+          <t>Augusto Rocha e Silva/Filipe</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1891,7 +1893,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>46139.11805555555</v>
+        <v>46158.53611111111</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -1935,7 +1937,7 @@
       </c>
       <c r="V8" s="5" t="inlineStr">
         <is>
-          <t>Cda</t>
+          <t>Kontrip - Vendas Cartao de Credito</t>
         </is>
       </c>
       <c r="W8" s="5" t="inlineStr">
@@ -1945,11 +1947,11 @@
       </c>
       <c r="X8" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y8" s="5" t="n">
-        <v>2284367251</v>
+        <v>2303902228</v>
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
@@ -1962,16 +1964,16 @@
         </is>
       </c>
       <c r="AB8" s="5" t="n">
-        <v>724.88</v>
+        <v>2155.06</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>112.56</v>
+        <v>33.64</v>
       </c>
       <c r="AD8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>72.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="5" t="n">
         <v>0</v>
@@ -1980,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>51.83</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="5" t="inlineStr">
         <is>
@@ -1989,7 +1991,7 @@
       </c>
       <c r="AJ8" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 27/04/2026</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 16/05/2026</t>
         </is>
       </c>
       <c r="AK8" s="5" t="inlineStr">
@@ -2030,21 +2032,21 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>24494720</v>
+        <v>24601662</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>25306270</v>
+        <v>25428031</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>46136.61736111111</v>
+        <v>46157.81648148148</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>46136.62313657408</v>
+        <v>46157.81768518518</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2058,31 +2060,31 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>6EWFOD</t>
+          <t>CGL5YI</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>VANESSA CHAVES</t>
+          <t>MARIA DUARTE ALVES/JESSICA</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>46135.61736111111</v>
+        <v>46157.31458333333</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -2126,7 +2128,7 @@
       </c>
       <c r="V9" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Lpe Engenharia e Consultoria Ltda</t>
         </is>
       </c>
       <c r="W9" s="5" t="inlineStr">
@@ -2136,11 +2138,11 @@
       </c>
       <c r="X9" s="5" t="inlineStr">
         <is>
-          <t>Latam Airlines Brasil</t>
+          <t>Azul Linhas Aereas</t>
         </is>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>2283882921</v>
+        <v>137324207</v>
       </c>
       <c r="Z9" s="5" t="inlineStr">
         <is>
@@ -2153,16 +2155,16 @@
         </is>
       </c>
       <c r="AB9" s="5" t="n">
-        <v>993.24</v>
+        <v>507.15</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>60.54</v>
+        <v>48.63</v>
       </c>
       <c r="AD9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>99.31999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="5" t="n">
         <v>0</v>
@@ -2171,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>71.02</v>
+        <v>32.14</v>
       </c>
       <c r="AI9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ9" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK9" s="5" t="inlineStr">
@@ -2190,17 +2192,17 @@
       </c>
       <c r="AL9" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM9" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN9" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO9" s="5" t="inlineStr">
@@ -2221,21 +2223,21 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>24493854</v>
+        <v>24601071</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>25305308</v>
+        <v>25427420</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>46136.50267361111</v>
+        <v>46157.79983796296</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>46136.50651620371</v>
+        <v>46157.80114583333</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2249,31 +2251,31 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>AJM35Z</t>
+          <t>FAJPZW</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>PAULO HENRIQUE FERREIRA VAZZOLER</t>
+          <t>MARIA DUARTE ALVES/JESSICA</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>46133.50208333333</v>
+        <v>46157.29861111111</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -2317,7 +2319,7 @@
       </c>
       <c r="V10" s="5" t="inlineStr">
         <is>
-          <t>Kontrip - Vendas Cartao de Credito</t>
+          <t>Lpe Engenharia e Consultoria Ltda</t>
         </is>
       </c>
       <c r="W10" s="5" t="inlineStr">
@@ -2327,11 +2329,11 @@
       </c>
       <c r="X10" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n">
-        <v>3025305307</v>
+        <v>228688497</v>
       </c>
       <c r="Z10" s="5" t="inlineStr">
         <is>
@@ -2344,10 +2346,10 @@
         </is>
       </c>
       <c r="AB10" s="5" t="n">
-        <v>412.12</v>
+        <v>559.17</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>48.75</v>
+        <v>62.14</v>
       </c>
       <c r="AD10" s="5" t="n">
         <v>0</v>
@@ -2362,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="AH10" s="5" t="n">
-        <v>41.21</v>
+        <v>42.22</v>
       </c>
       <c r="AI10" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK10" s="5" t="inlineStr">
@@ -2381,17 +2383,17 @@
       </c>
       <c r="AL10" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM10" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN10" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO10" s="5" t="inlineStr">
@@ -2412,10 +2414,10 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>24419465</v>
+        <v>24601282</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>25221482</v>
+        <v>25427630</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -2423,24 +2425,24 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>46120.66405092592</v>
+        <v>46157.80396990741</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>46123.73384259259</v>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
+        <v>46157.80489583333</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>03 a 05 dias</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>03 a 05 dias</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>MMTY6D01</t>
+          <t>OG284Y</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2450,7 +2452,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>SANTOS DE OLIVEIRA PITANGA/CAIQUE</t>
+          <t>MARIA DUARTE ALVES/JESSICA</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
@@ -2464,7 +2466,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>46120.1625</v>
+        <v>46157.30347222222</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -2498,7 +2500,7 @@
       </c>
       <c r="T11" s="5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U11" s="5" t="inlineStr">
@@ -2508,7 +2510,7 @@
       </c>
       <c r="V11" s="5" t="inlineStr">
         <is>
-          <t>Wps Brasil Ltda</t>
+          <t>Lpe Engenharia e Consultoria Ltda</t>
         </is>
       </c>
       <c r="W11" s="5" t="inlineStr">
@@ -2522,7 +2524,7 @@
         </is>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>495316528</v>
+        <v>538633897</v>
       </c>
       <c r="Z11" s="5" t="inlineStr">
         <is>
@@ -2535,10 +2537,10 @@
         </is>
       </c>
       <c r="AB11" s="5" t="n">
-        <v>1202.79</v>
+        <v>586.16</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>113.26</v>
+        <v>48.63</v>
       </c>
       <c r="AD11" s="5" t="n">
         <v>0</v>
@@ -2553,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>108.25</v>
+        <v>39.25</v>
       </c>
       <c r="AI11" s="5" t="inlineStr">
         <is>
@@ -2562,7 +2564,7 @@
       </c>
       <c r="AJ11" s="5" t="inlineStr">
         <is>
-          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 08/04/2026</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK11" s="5" t="inlineStr">
@@ -2603,10 +2605,10 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>24493797</v>
+        <v>24601487</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>25305242</v>
+        <v>25427840</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -2614,10 +2616,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>46136.49399305556</v>
+        <v>46157.80961805556</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>46136.49840277778</v>
+        <v>46157.81137731481</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -2631,31 +2633,31 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WJK7MS</t>
+          <t>FDNIBJ</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>VIVIAN LUTGARD ZACCONI AQUINO</t>
+          <t>MARIA DUARTE ALVES/JESSICA</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>46132.49375</v>
+        <v>46157.30833333333</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -2699,7 +2701,7 @@
       </c>
       <c r="V12" s="5" t="inlineStr">
         <is>
-          <t>E-rural Atividades de Internet</t>
+          <t>Lpe Engenharia e Consultoria Ltda</t>
         </is>
       </c>
       <c r="W12" s="5" t="inlineStr">
@@ -2709,11 +2711,11 @@
       </c>
       <c r="X12" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>3025305241</v>
+        <v>228688516</v>
       </c>
       <c r="Z12" s="5" t="inlineStr">
         <is>
@@ -2726,10 +2728,10 @@
         </is>
       </c>
       <c r="AB12" s="5" t="n">
-        <v>410</v>
+        <v>462.28</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>32.87</v>
+        <v>62.14</v>
       </c>
       <c r="AD12" s="5" t="n">
         <v>0</v>
@@ -2744,16 +2746,16 @@
         <v>0</v>
       </c>
       <c r="AH12" s="5" t="n">
-        <v>82</v>
+        <v>34.35</v>
       </c>
       <c r="AI12" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ12" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK12" s="5" t="inlineStr">
@@ -2763,17 +2765,17 @@
       </c>
       <c r="AL12" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM12" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN12" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO12" s="5" t="inlineStr">
@@ -2794,21 +2796,21 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>24493797</v>
+        <v>24598641</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>25305244</v>
+        <v>25424592</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ACC02</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>46136.49399305556</v>
+        <v>46157.45399305555</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>46136.49840277778</v>
+        <v>46157.45474537037</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -2822,31 +2824,31 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> WJK7MS</t>
+          <t>JZVCLK</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>MATHEUS SEROA</t>
+          <t>Henrique Peres dos Santos/Iago</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>46132.49375</v>
+        <v>46157.45208333333</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -2890,7 +2892,7 @@
       </c>
       <c r="V13" s="5" t="inlineStr">
         <is>
-          <t>E-rural Atividades de Internet</t>
+          <t>Lobov Cientifica</t>
         </is>
       </c>
       <c r="W13" s="5" t="inlineStr">
@@ -2900,11 +2902,11 @@
       </c>
       <c r="X13" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>3025305241</v>
+        <v>2286866372</v>
       </c>
       <c r="Z13" s="5" t="inlineStr">
         <is>
@@ -2917,10 +2919,10 @@
         </is>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>410</v>
+        <v>1020.89</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>32.87</v>
+        <v>500</v>
       </c>
       <c r="AD13" s="5" t="n">
         <v>0</v>
@@ -2935,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 15/05/2026</t>
         </is>
       </c>
       <c r="AK13" s="5" t="inlineStr">
@@ -2954,17 +2956,17 @@
       </c>
       <c r="AL13" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM13" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN13" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO13" s="5" t="inlineStr">
@@ -2985,21 +2987,21 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>24494430</v>
+        <v>24578818</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>25305913</v>
+        <v>25402494</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>46136.5408912037</v>
+        <v>46154.61798611111</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>46136.54615740741</v>
+        <v>46155.53385416666</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -3008,36 +3010,36 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>03 a 05 dias</t>
+          <t>06 a 08 dias</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>AGFPPI</t>
+          <t>ETMIMA02</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>JOSE LUIZ DE MOURA FALEIROS JUNIOR</t>
+          <t>Zampirollo Neto/Octavio</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>46135.54027777778</v>
+        <v>46149.11736111111</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -3081,7 +3083,7 @@
       </c>
       <c r="V14" s="5" t="inlineStr">
         <is>
-          <t>Faculdade Baiana de Direito</t>
+          <t>Grant Thornton Auditores Independentes</t>
         </is>
       </c>
       <c r="W14" s="5" t="inlineStr">
@@ -3091,11 +3093,11 @@
       </c>
       <c r="X14" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y14" s="5" t="n">
-        <v>3025305912</v>
+        <v>2286408382</v>
       </c>
       <c r="Z14" s="5" t="inlineStr">
         <is>
@@ -3108,10 +3110,10 @@
         </is>
       </c>
       <c r="AB14" s="5" t="n">
-        <v>1082.34</v>
+        <v>838.88</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>86.28</v>
+        <v>450</v>
       </c>
       <c r="AD14" s="5" t="n">
         <v>0</v>
@@ -3126,16 +3128,16 @@
         <v>0</v>
       </c>
       <c r="AH14" s="5" t="n">
-        <v>108.23</v>
+        <v>40</v>
       </c>
       <c r="AI14" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="inlineStr">
         <is>
-          <t>36Faltou informar rateio de centro de custo/projeto abaixo da accounting</t>
+          <t>Não foi possível encontrar configuração válida para Administradora de código 1 e Data Emissão 07/05/2026</t>
         </is>
       </c>
       <c r="AK14" s="5" t="inlineStr">
@@ -3145,17 +3147,17 @@
       </c>
       <c r="AL14" s="5" t="inlineStr">
         <is>
-          <t>Falta de informação Gerencial</t>
+          <t>Não identificado</t>
         </is>
       </c>
       <c r="AM14" s="5" t="inlineStr">
         <is>
-          <t>Rateio de centro de custo/projeto</t>
+          <t>Análise Benner</t>
         </is>
       </c>
       <c r="AN14" s="5" t="inlineStr">
         <is>
-          <t>Dados Gerenciais</t>
+          <t>Sistema</t>
         </is>
       </c>
       <c r="AO14" s="5" t="inlineStr">
@@ -3176,21 +3178,21 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>24494198</v>
+        <v>24600478</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>25305685</v>
+        <v>25426738</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>46136.52075231481</v>
+        <v>46157.72592592592</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>46136.52525462963</v>
+        <v>46157.729375</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -3204,7 +3206,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>IMC7VW</t>
+          <t>LA9573774CAIL</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -3214,21 +3216,21 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>ANDERSON BEZERRA DE OLIVEIRA</t>
+          <t>MIGUEL DE DEUS</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>46135.52013888889</v>
+        <v>46156.72569444445</v>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
@@ -3272,7 +3274,7 @@
       </c>
       <c r="V15" s="5" t="inlineStr">
         <is>
-          <t>Red Engenharia Industrial Especializada Ltda</t>
+          <t>2ms - Engenharia</t>
         </is>
       </c>
       <c r="W15" s="5" t="inlineStr">
@@ -3282,11 +3284,11 @@
       </c>
       <c r="X15" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y15" s="5" t="n">
-        <v>3025305683</v>
+        <v>2286703454</v>
       </c>
       <c r="Z15" s="5" t="inlineStr">
         <is>
@@ -3299,16 +3301,16 @@
         </is>
       </c>
       <c r="AB15" s="5" t="n">
-        <v>3893.62</v>
+        <v>515.96</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>107.89</v>
+        <v>62.14</v>
       </c>
       <c r="AD15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>0</v>
+        <v>51.59</v>
       </c>
       <c r="AF15" s="5" t="n">
         <v>0</v>
@@ -3317,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="5" t="n">
-        <v>389.36</v>
+        <v>73.78</v>
       </c>
       <c r="AI15" s="5" t="inlineStr">
         <is>
@@ -3367,21 +3369,21 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>24493870</v>
+        <v>24600478</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25305316</v>
+        <v>25426741</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC02</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>46136.50516203704</v>
+        <v>46157.72592592592</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>46136.50883101852</v>
+        <v>46157.729375</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -3395,7 +3397,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>BQRKTH</t>
+          <t>LA9573774CAIL</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3405,21 +3407,21 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>MIZAEL LIMA DOS REIS</t>
+          <t>SILVIA SANTOS</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Juliana Cardoso</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>46134.50486111111</v>
+        <v>46156.72569444445</v>
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
@@ -3463,7 +3465,7 @@
       </c>
       <c r="V16" s="5" t="inlineStr">
         <is>
-          <t>Marques e Bezerra Ltda</t>
+          <t>2ms - Engenharia</t>
         </is>
       </c>
       <c r="W16" s="5" t="inlineStr">
@@ -3473,11 +3475,11 @@
       </c>
       <c r="X16" s="5" t="inlineStr">
         <is>
-          <t>Azul Linhas Aereas</t>
+          <t>Latam Airlines Brasil</t>
         </is>
       </c>
       <c r="Y16" s="5" t="n">
-        <v>3025305315</v>
+        <v>2286703455</v>
       </c>
       <c r="Z16" s="5" t="inlineStr">
         <is>
@@ -3490,16 +3492,16 @@
         </is>
       </c>
       <c r="AB16" s="5" t="n">
-        <v>1873.62</v>
+        <v>515.96</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>55.17</v>
+        <v>62.14</v>
       </c>
       <c r="AD16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>0</v>
+        <v>51.59</v>
       </c>
       <c r="AF16" s="5" t="n">
         <v>0</v>
@@ -3508,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="5" t="n">
-        <v>187.36</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="5" t="inlineStr">
         <is>
@@ -3558,10 +3560,10 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>24493523</v>
+        <v>24599775</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>25304914</v>
+        <v>25425828</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -3569,10 +3571,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>46136.43653935185</v>
+        <v>46157.62344907408</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>46136.44121527778</v>
+        <v>46157.62644675926</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -3584,31 +3586,33 @@
           <t>03 a 05 dias</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>2119553175</v>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>OMWVPM</t>
+        </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>MAX SENA DO O</t>
+          <t>VAN LEIJDEN/GUILHERME</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>46134.43611111111</v>
+        <v>46157.07361111111</v>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
@@ -3627,17 +3631,17 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr">
         <is>
-          <t>Pagamento direto</t>
+          <t>Faturado</t>
         </is>
       </c>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Aéreo</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
@@ -3647,12 +3651,12 @@
       </c>
       <c r="U17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V17" s="5" t="inlineStr">
         <is>
-          <t>Jmn Nantes Servicos Financeiros Ltda</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W17" s="5" t="inlineStr">
@@ -3662,12 +3666,12 @@
       </c>
       <c r="X17" s="5" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Gol Linhas Aereas</t>
         </is>
       </c>
       <c r="Y17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OMWVPM</t>
         </is>
       </c>
       <c r="Z17" s="5" t="inlineStr">
@@ -3681,10 +3685,10 @@
         </is>
       </c>
       <c r="AB17" s="5" t="n">
-        <v>1351</v>
+        <v>610.5</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>0</v>
+        <v>52.72</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
@@ -3699,16 +3703,16 @@
         <v>0</v>
       </c>
       <c r="AH17" s="5" t="n">
-        <v>0</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="AI17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="inlineStr">
         <is>
-          <t>Necessário cadastrar um contrato para o cliente ""</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK17" s="5" t="inlineStr">
@@ -3718,12 +3722,12 @@
       </c>
       <c r="AL17" s="5" t="inlineStr">
         <is>
-          <t>Contrato de fornecedor</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM17" s="5" t="inlineStr">
         <is>
-          <t>Análise Cadastro</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN17" s="5" t="inlineStr">
@@ -3749,10 +3753,10 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>24493444</v>
+        <v>24599722</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>25304820</v>
+        <v>25425769</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -3760,10 +3764,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>46136.41921296297</v>
+        <v>46157.60678240741</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>46136.42413194444</v>
+        <v>46157.60888888889</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -3775,31 +3779,33 @@
           <t>03 a 05 dias</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
-        <v>2119553171</v>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>YKRRWP</t>
+        </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>MAX SENA DO O</t>
+          <t>VAN LEIJDEN/GUILHERME</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>46134.41875</v>
+        <v>46157.06944444445</v>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
@@ -3818,17 +3824,17 @@
       </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R18" s="5" t="inlineStr">
         <is>
-          <t>Pagamento direto</t>
+          <t>Faturado</t>
         </is>
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Aéreo</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
@@ -3838,12 +3844,12 @@
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr">
         <is>
-          <t>Jmn Nantes Servicos Financeiros Ltda</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W18" s="5" t="inlineStr">
@@ -3853,13 +3859,11 @@
       </c>
       <c r="X18" s="5" t="inlineStr">
         <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="Y18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>704562481</v>
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
@@ -3872,10 +3876,10 @@
         </is>
       </c>
       <c r="AB18" s="5" t="n">
-        <v>355</v>
+        <v>144</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>17.75</v>
+        <v>120.44</v>
       </c>
       <c r="AD18" s="5" t="n">
         <v>0</v>
@@ -3890,16 +3894,16 @@
         <v>0</v>
       </c>
       <c r="AH18" s="5" t="n">
-        <v>0</v>
+        <v>17.28</v>
       </c>
       <c r="AI18" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="inlineStr">
         <is>
-          <t>Necessário cadastrar um contrato para o cliente ""</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK18" s="5" t="inlineStr">
@@ -3909,12 +3913,12 @@
       </c>
       <c r="AL18" s="5" t="inlineStr">
         <is>
-          <t>Contrato de fornecedor</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM18" s="5" t="inlineStr">
         <is>
-          <t>Análise Cadastro</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN18" s="5" t="inlineStr">
@@ -3940,57 +3944,59 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>24418477</v>
+        <v>24599727</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>25220450</v>
+        <v>25425774</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACC01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>46120.55074074074</v>
+        <v>46157.60819444444</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>46120.55611111111</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>2119510634</v>
+        <v>46157.60957175926</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>03 a 05 dias</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>03 a 05 dias</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>UN2CUW</t>
+        </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>EBOOKING</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>JOAO RENATO CUNHA DA SILVA</t>
+          <t>VAN LEIJDEN/GUILHERME</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Kontrip</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>46119.55069444444</v>
+        <v>46157.07569444444</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -4009,17 +4015,17 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Múltiplos</t>
+          <t>Invoice</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr">
         <is>
-          <t>Múltiplos</t>
+          <t>Faturado</t>
         </is>
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Aéreo</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
@@ -4029,12 +4035,12 @@
       </c>
       <c r="U19" s="5" t="inlineStr">
         <is>
-          <t>Grupo Kontrip</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V19" s="5" t="inlineStr">
         <is>
-          <t>Cogny Solutions Ltda</t>
+          <t>Tap Air Portugal</t>
         </is>
       </c>
       <c r="W19" s="5" t="inlineStr">
@@ -4044,13 +4050,11 @@
       </c>
       <c r="X19" s="5" t="inlineStr">
         <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="Y19" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Azul Linhas Aereas</t>
+        </is>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>802886655</v>
       </c>
       <c r="Z19" s="5" t="inlineStr">
         <is>
@@ -4063,10 +4067,10 @@
         </is>
       </c>
       <c r="AB19" s="5" t="n">
-        <v>951.88</v>
+        <v>108</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>43.55</v>
+        <v>106.1</v>
       </c>
       <c r="AD19" s="5" t="n">
         <v>0</v>
@@ -4081,16 +4085,16 @@
         <v>0</v>
       </c>
       <c r="AH19" s="5" t="n">
-        <v>0</v>
+        <v>12.96</v>
       </c>
       <c r="AI19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="inlineStr">
         <is>
-          <t>A soma das tarifas dos registros múltiplos ultrapassa a tarifa da accounting</t>
+          <t>Centro de custo não preenchido! (ACC01)</t>
         </is>
       </c>
       <c r="AK19" s="5" t="inlineStr">
@@ -4100,17 +4104,17 @@
       </c>
       <c r="AL19" s="5" t="inlineStr">
         <is>
-          <t>Não identificado</t>
+          <t>Centro de custo</t>
         </is>
       </c>
       <c r="AM19" s="5" t="inlineStr">
         <is>
-          <t>Análise Benner</t>
+          <t>Falta de informação Gerencial</t>
         </is>
       </c>
       <c r="AN19" s="5" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Dados do Fornecedor</t>
         </is>
       </c>
       <c r="AO19" s="5" t="inlineStr">
@@ -4131,10 +4135,10 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>24411669</v>
+        <v>24596497</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>25212946</v>
+        <v>25422131</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -4142,53 +4146,51 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>46119.44847222222</v>
+        <v>46156.82958333333</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>46121.62430555555</v>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>16 a 23 dias</t>
+        <v>46157.08439814814</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>03 a 05 dias</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>03 a 05 dias</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>MV1MCEMYDABR</t>
+          <t>FAPDBO</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>MANUAL</t>
+          <t>WOOBA</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>MAX SENA DO O</t>
+          <t>CAMANO DE MESQUITA BARROS/LUCAS MR</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Toou</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Emilly Tavares Santos</t>
+          <t>Toou</t>
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>46118.44791666666</v>
-      </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46156.82847222222</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>2340</v>
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
@@ -4202,17 +4204,17 @@
       </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>Pagamento direto</t>
+          <t>Cartão de crédito</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Carro</t>
+          <t>Aéreo</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
@@ -4222,12 +4224,12 @@
       </c>
       <c r="U20" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Independente</t>
         </is>
       </c>
       <c r="V20" s="5" t="inlineStr">
         <is>
-          <t>Jmn Nantes Servicos Financeiros Ltda</t>
+          <t>Projetech Locacao</t>
         </is>
       </c>
       <c r="W20" s="5" t="inlineStr">
@@ -4237,13 +4239,11 @@
       </c>
       <c r="X20" s="5" t="inlineStr">
         <is>
-          <t>Movida - Br - Sp - Sao Paulo - Itaim Bibi</t>
-        </is>
-      </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Latam Airlines Brasil</t>
+        </is>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>2286806156</v>
       </c>
       <c r="Z20" s="5" t="inlineStr">
         <is>
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="AB20" s="5" t="n">
-        <v>660.03</v>
+        <v>814.5599999999999</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>0</v>
+        <v>72.03</v>
       </c>
       <c r="AD20" s="5" t="n">
         <v>0</v>
@@ -4274,11 +4274,11 @@
         <v>0</v>
       </c>
       <c r="AH20" s="5" t="n">
-        <v>0</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AI20" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Reserva importada do Sistema WOOBA. Id: 5966</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="inlineStr">
@@ -4317,199 +4317,6 @@
         </is>
       </c>
       <c r="AQ20" s="5" t="inlineStr">
-        <is>
-          <t>Operações - KONTRIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="n">
-        <v>24495479</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>25307271</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>ACC01</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>46136.7365625</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>46136.75099537037</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>03 a 05 dias</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>MV1JTTDQJ1BR</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>RUBENS OSTERNACK FILHO</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Emilly Tavares Santos</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>Emilly Tavares Santos</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>46128.73611111111</v>
-      </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>OFF LINE</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>Outros</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
-        <is>
-          <t>Pagamento direto</t>
-        </is>
-      </c>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>Carro</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="inlineStr">
-        <is>
-          <t>Jmn Nantes Servicos Financeiros Ltda</t>
-        </is>
-      </c>
-      <c r="W21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X21" s="5" t="inlineStr">
-        <is>
-          <t>Movida - Br - Sp - Sao Paulo - Itaim Bibi - Matriz</t>
-        </is>
-      </c>
-      <c r="Y21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z21" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AA21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB21" s="5" t="n">
-        <v>909.36</v>
-      </c>
-      <c r="AC21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AJ21" s="5" t="inlineStr">
-        <is>
-          <t>Necessário cadastrar um contrato para o cliente ""</t>
-        </is>
-      </c>
-      <c r="AK21" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP</t>
-        </is>
-      </c>
-      <c r="AL21" s="5" t="inlineStr">
-        <is>
-          <t>Contrato de fornecedor</t>
-        </is>
-      </c>
-      <c r="AM21" s="5" t="inlineStr">
-        <is>
-          <t>Análise Cadastro</t>
-        </is>
-      </c>
-      <c r="AN21" s="5" t="inlineStr">
-        <is>
-          <t>Dados do Fornecedor</t>
-        </is>
-      </c>
-      <c r="AO21" s="5" t="inlineStr">
-        <is>
-          <t>Qualidade dos dados</t>
-        </is>
-      </c>
-      <c r="AP21" s="5" t="inlineStr">
-        <is>
-          <t>KONTRIP VIAGENS</t>
-        </is>
-      </c>
-      <c r="AQ21" s="5" t="inlineStr">
         <is>
           <t>Operações - KONTRIP</t>
         </is>
